--- a/ebegu-server/src/main/resources/reporting/TagesschuleAnmeldungen.xlsx
+++ b/ebegu-server/src/main/resources/reporting/TagesschuleAnmeldungen.xlsx
@@ -1,246 +1,246 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java\kibon-app\ebegu-server\src\main\resources\reporting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aese\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9BF895-EE4C-4A85-839D-B9FB7E63CAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C554214-8E04-4432-AE4F-0B2C48C31FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$8:$S$16</definedName>
-    <definedName name="angemeldet1">Data!$U$11</definedName>
-    <definedName name="angemeldet10">Data!$AD$11</definedName>
-    <definedName name="angemeldet100">Data!$DX$11</definedName>
-    <definedName name="angemeldet11">Data!$AE$11</definedName>
-    <definedName name="angemeldet12">Data!$AF$11</definedName>
-    <definedName name="angemeldet13">Data!$AG$11</definedName>
-    <definedName name="angemeldet14">Data!$AH$11</definedName>
-    <definedName name="angemeldet15">Data!$AI$11</definedName>
-    <definedName name="angemeldet16">Data!$AJ$11</definedName>
-    <definedName name="angemeldet17">Data!$AK$11</definedName>
-    <definedName name="angemeldet18">Data!$AL$11</definedName>
-    <definedName name="angemeldet19">Data!$AM$11</definedName>
-    <definedName name="angemeldet2">Data!$V$11</definedName>
-    <definedName name="angemeldet20">Data!$AN$11</definedName>
-    <definedName name="angemeldet21">Data!$AQ$11</definedName>
-    <definedName name="angemeldet22">Data!$AR$11</definedName>
-    <definedName name="angemeldet23">Data!$AS$11</definedName>
-    <definedName name="angemeldet24">Data!$AT$11</definedName>
-    <definedName name="angemeldet25">Data!$AU$11</definedName>
-    <definedName name="angemeldet26">Data!$AV$11</definedName>
-    <definedName name="angemeldet27">Data!$AW$11</definedName>
-    <definedName name="angemeldet28">Data!$AX$11</definedName>
-    <definedName name="angemeldet29">Data!$AY$11</definedName>
-    <definedName name="angemeldet3">Data!$W$11</definedName>
-    <definedName name="angemeldet30">Data!$AZ$11</definedName>
-    <definedName name="angemeldet31">Data!$BA$11</definedName>
-    <definedName name="angemeldet32">Data!$BB$11</definedName>
-    <definedName name="angemeldet33">Data!$BC$11</definedName>
-    <definedName name="angemeldet34">Data!$BD$11</definedName>
-    <definedName name="angemeldet35">Data!$BE$11</definedName>
-    <definedName name="angemeldet36">Data!$BF$11</definedName>
-    <definedName name="angemeldet37">Data!$BG$11</definedName>
-    <definedName name="angemeldet38">Data!$BH$11</definedName>
-    <definedName name="angemeldet39">Data!$BI$11</definedName>
-    <definedName name="angemeldet4">Data!$X$11</definedName>
-    <definedName name="angemeldet40">Data!$BJ$11</definedName>
-    <definedName name="angemeldet41">Data!$BM$11</definedName>
-    <definedName name="angemeldet42">Data!$BN$11</definedName>
-    <definedName name="angemeldet43">Data!$BO$11</definedName>
-    <definedName name="angemeldet44">Data!$BP$11</definedName>
-    <definedName name="angemeldet45">Data!$BQ$11</definedName>
-    <definedName name="angemeldet46">Data!$BR$11</definedName>
-    <definedName name="angemeldet47">Data!$BS$11</definedName>
-    <definedName name="angemeldet48">Data!$BT$11</definedName>
-    <definedName name="angemeldet49">Data!$BU$11</definedName>
-    <definedName name="angemeldet5">Data!$Y$11</definedName>
-    <definedName name="angemeldet50">Data!$BV$11</definedName>
-    <definedName name="angemeldet51">Data!$BW$11</definedName>
-    <definedName name="angemeldet52">Data!$BX$11</definedName>
-    <definedName name="angemeldet53">Data!$BY$11</definedName>
-    <definedName name="angemeldet54">Data!$BZ$11</definedName>
-    <definedName name="angemeldet55">Data!$CA$11</definedName>
-    <definedName name="angemeldet56">Data!$CB$11</definedName>
-    <definedName name="angemeldet57">Data!$CC$11</definedName>
-    <definedName name="angemeldet58">Data!$CD$11</definedName>
-    <definedName name="angemeldet59">Data!$CE$11</definedName>
-    <definedName name="angemeldet6">Data!$Z$11</definedName>
-    <definedName name="angemeldet60">Data!$CF$11</definedName>
-    <definedName name="angemeldet61">Data!$CI$11</definedName>
-    <definedName name="angemeldet62">Data!$CJ$11</definedName>
-    <definedName name="angemeldet63">Data!$CK$11</definedName>
-    <definedName name="angemeldet64">Data!$CL$11</definedName>
-    <definedName name="angemeldet65">Data!$CM$11</definedName>
-    <definedName name="angemeldet66">Data!$CN$11</definedName>
-    <definedName name="angemeldet67">Data!$CO$11</definedName>
-    <definedName name="angemeldet68">Data!$CP$11</definedName>
-    <definedName name="angemeldet69">Data!$CQ$11</definedName>
-    <definedName name="angemeldet7">Data!$AA$11</definedName>
-    <definedName name="angemeldet70">Data!$CR$11</definedName>
-    <definedName name="angemeldet71">Data!$CS$11</definedName>
-    <definedName name="angemeldet72">Data!$CT$11</definedName>
-    <definedName name="angemeldet73">Data!$CU$11</definedName>
-    <definedName name="angemeldet74">Data!$CV$11</definedName>
-    <definedName name="angemeldet75">Data!$CW$11</definedName>
-    <definedName name="angemeldet76">Data!$CX$11</definedName>
-    <definedName name="angemeldet77">Data!$CY$11</definedName>
-    <definedName name="angemeldet78">Data!$CZ$11</definedName>
-    <definedName name="angemeldet79">Data!$DA$11</definedName>
-    <definedName name="angemeldet8">Data!$AB$11</definedName>
-    <definedName name="angemeldet80">Data!$DB$11</definedName>
-    <definedName name="angemeldet81">Data!$DE$11</definedName>
-    <definedName name="angemeldet82">Data!$DF$11</definedName>
-    <definedName name="angemeldet83">Data!$DG$11</definedName>
-    <definedName name="angemeldet84">Data!$DH$11</definedName>
-    <definedName name="angemeldet85">Data!$DI$11</definedName>
-    <definedName name="angemeldet86">Data!$DJ$11</definedName>
-    <definedName name="angemeldet87">Data!$DK$11</definedName>
-    <definedName name="angemeldet88">Data!$DL$11</definedName>
-    <definedName name="angemeldet89">Data!$DM$11</definedName>
-    <definedName name="angemeldet9">Data!$AC$11</definedName>
-    <definedName name="angemeldet90">Data!$DN$11</definedName>
-    <definedName name="angemeldet91">Data!$DO$11</definedName>
-    <definedName name="angemeldet92">Data!$DP$11</definedName>
-    <definedName name="angemeldet93">Data!$DQ$11</definedName>
-    <definedName name="angemeldet94">Data!$DR$11</definedName>
-    <definedName name="angemeldet95">Data!$DS$11</definedName>
-    <definedName name="angemeldet96">Data!$DT$11</definedName>
-    <definedName name="angemeldet97">Data!$DU$11</definedName>
-    <definedName name="angemeldet98">Data!$DV$11</definedName>
-    <definedName name="angemeldet99">Data!$DW$11</definedName>
-    <definedName name="freigegebenKategorie">Data!$T$15</definedName>
-    <definedName name="nichtFreigegeben1">Data!$U$15</definedName>
-    <definedName name="nichtFreigegeben10">Data!$AD$15</definedName>
-    <definedName name="nichtFreigegeben100">Data!$DX$15</definedName>
-    <definedName name="nichtFreigegeben11">Data!$AE$15</definedName>
-    <definedName name="nichtFreigegeben12">Data!$AF$15</definedName>
-    <definedName name="nichtFreigegeben13">Data!$AG$15</definedName>
-    <definedName name="nichtFreigegeben14">Data!$AH$15</definedName>
-    <definedName name="nichtFreigegeben15">Data!$AI$15</definedName>
-    <definedName name="nichtFreigegeben16">Data!$AJ$15</definedName>
-    <definedName name="nichtFreigegeben17">Data!$AK$15</definedName>
-    <definedName name="nichtFreigegeben18">Data!$AL$15</definedName>
-    <definedName name="nichtFreigegeben19">Data!$AM$15</definedName>
-    <definedName name="nichtFreigegeben2">Data!$V$15</definedName>
-    <definedName name="nichtFreigegeben20">Data!$AN$15</definedName>
-    <definedName name="nichtFreigegeben21">Data!$AQ$15</definedName>
-    <definedName name="nichtFreigegeben22">Data!$AR$15</definedName>
-    <definedName name="nichtFreigegeben23">Data!$AS$15</definedName>
-    <definedName name="nichtFreigegeben24">Data!$AT$15</definedName>
-    <definedName name="nichtFreigegeben25">Data!$AU$15</definedName>
-    <definedName name="nichtFreigegeben26">Data!$AV$15</definedName>
-    <definedName name="nichtFreigegeben27">Data!$AW$15</definedName>
-    <definedName name="nichtFreigegeben28">Data!$AX$15</definedName>
-    <definedName name="nichtFreigegeben29">Data!$AY$15</definedName>
-    <definedName name="nichtFreigegeben3">Data!$W$15</definedName>
-    <definedName name="nichtFreigegeben30">Data!$AZ$15</definedName>
-    <definedName name="nichtFreigegeben31">Data!$BA$15</definedName>
-    <definedName name="nichtFreigegeben32">Data!$BB$15</definedName>
-    <definedName name="nichtFreigegeben33">Data!$BC$15</definedName>
-    <definedName name="nichtFreigegeben34">Data!$BD$15</definedName>
-    <definedName name="nichtFreigegeben35">Data!$BE$15</definedName>
-    <definedName name="nichtFreigegeben36">Data!$BF$15</definedName>
-    <definedName name="nichtFreigegeben37">Data!$BG$15</definedName>
-    <definedName name="nichtFreigegeben38">Data!$BH$15</definedName>
-    <definedName name="nichtFreigegeben39">Data!$BI$15</definedName>
-    <definedName name="nichtFreigegeben4">Data!$X$15</definedName>
-    <definedName name="nichtFreigegeben40">Data!$BJ$15</definedName>
-    <definedName name="nichtFreigegeben41">Data!$BM$15</definedName>
-    <definedName name="nichtFreigegeben42">Data!$BN$15</definedName>
-    <definedName name="nichtFreigegeben43">Data!$BO$15</definedName>
-    <definedName name="nichtFreigegeben44">Data!$BP$15</definedName>
-    <definedName name="nichtFreigegeben45">Data!$BQ$15</definedName>
-    <definedName name="nichtFreigegeben46">Data!$BR$15</definedName>
-    <definedName name="nichtFreigegeben47">Data!$BS$15</definedName>
-    <definedName name="nichtFreigegeben48">Data!$BT$15</definedName>
-    <definedName name="nichtFreigegeben49">Data!$BU$15</definedName>
-    <definedName name="nichtFreigegeben5">Data!$Y$15</definedName>
-    <definedName name="nichtFreigegeben50">Data!$BV$15</definedName>
-    <definedName name="nichtFreigegeben51">Data!$BW$15</definedName>
-    <definedName name="nichtFreigegeben52">Data!$BX$15</definedName>
-    <definedName name="nichtFreigegeben53">Data!$BY$15</definedName>
-    <definedName name="nichtFreigegeben54">Data!$BZ$15</definedName>
-    <definedName name="nichtFreigegeben55">Data!$CA$15</definedName>
-    <definedName name="nichtFreigegeben56">Data!$CB$15</definedName>
-    <definedName name="nichtFreigegeben57">Data!$CC$15</definedName>
-    <definedName name="nichtFreigegeben58">Data!$CD$15</definedName>
-    <definedName name="nichtFreigegeben59">Data!$CE$15</definedName>
-    <definedName name="nichtFreigegeben6">Data!$Z$15</definedName>
-    <definedName name="nichtFreigegeben60">Data!$CF$15</definedName>
-    <definedName name="nichtFreigegeben61">Data!$CI$15</definedName>
-    <definedName name="nichtFreigegeben62">Data!$CJ$15</definedName>
-    <definedName name="nichtFreigegeben63">Data!$CK$15</definedName>
-    <definedName name="nichtFreigegeben64">Data!$CL$15</definedName>
-    <definedName name="nichtFreigegeben65">Data!$CM$15</definedName>
-    <definedName name="nichtFreigegeben66">Data!$CN$15</definedName>
-    <definedName name="nichtFreigegeben67">Data!$CO$15</definedName>
-    <definedName name="nichtFreigegeben68">Data!$CP$15</definedName>
-    <definedName name="nichtFreigegeben69">Data!$CQ$15</definedName>
-    <definedName name="nichtFreigegeben7">Data!$AA$15</definedName>
-    <definedName name="nichtFreigegeben70">Data!$CR$15</definedName>
-    <definedName name="nichtFreigegeben71">Data!$CS$15</definedName>
-    <definedName name="nichtFreigegeben72">Data!$CT$15</definedName>
-    <definedName name="nichtFreigegeben73">Data!$CU$15</definedName>
-    <definedName name="nichtFreigegeben74">Data!$CV$15</definedName>
-    <definedName name="nichtFreigegeben75">Data!$CW$15</definedName>
-    <definedName name="nichtFreigegeben76">Data!$CX$15</definedName>
-    <definedName name="nichtFreigegeben77">Data!$CY$15</definedName>
-    <definedName name="nichtFreigegeben78">Data!$CZ$15</definedName>
-    <definedName name="nichtFreigegeben79">Data!$DA$15</definedName>
-    <definedName name="nichtFreigegeben8">Data!$AB$15</definedName>
-    <definedName name="nichtFreigegeben80">Data!$DB$15</definedName>
-    <definedName name="nichtFreigegeben81">Data!$DE$15</definedName>
-    <definedName name="nichtFreigegeben82">Data!$DF$15</definedName>
-    <definedName name="nichtFreigegeben83">Data!$DG$15</definedName>
-    <definedName name="nichtFreigegeben84">Data!$DH$15</definedName>
-    <definedName name="nichtFreigegeben85">Data!$DI$15</definedName>
-    <definedName name="nichtFreigegeben86">Data!$DJ$15</definedName>
-    <definedName name="nichtFreigegeben87">Data!$DK$15</definedName>
-    <definedName name="nichtFreigegeben88">Data!$DL$15</definedName>
-    <definedName name="nichtFreigegeben89">Data!$DM$15</definedName>
-    <definedName name="nichtFreigegeben9">Data!$AC$15</definedName>
-    <definedName name="nichtFreigegeben90">Data!$DN$15</definedName>
-    <definedName name="nichtFreigegeben91">Data!$DO$15</definedName>
-    <definedName name="nichtFreigegeben92">Data!$DP$15</definedName>
-    <definedName name="nichtFreigegeben93">Data!$DQ$15</definedName>
-    <definedName name="nichtFreigegeben94">Data!$DR$15</definedName>
-    <definedName name="nichtFreigegeben95">Data!$DS$15</definedName>
-    <definedName name="nichtFreigegeben96">Data!$DT$15</definedName>
-    <definedName name="nichtFreigegeben97">Data!$DU$15</definedName>
-    <definedName name="nichtFreigegeben98">Data!$DV$15</definedName>
-    <definedName name="nichtFreigegeben99">Data!$DW$15</definedName>
-    <definedName name="statusKategorie">Data!$T$11</definedName>
-    <definedName name="summeStundenDi">Data!$BK$11</definedName>
-    <definedName name="summeStundenDo">Data!$DC$11</definedName>
-    <definedName name="summeStundenFr">Data!$DY$11</definedName>
-    <definedName name="summeStundenMi">Data!$CG$11</definedName>
-    <definedName name="summeStundenMo">Data!$AO$11</definedName>
-    <definedName name="summeStundenWoche">Data!$EA$11</definedName>
-    <definedName name="summeVerpflegungDi">Data!$BL$11</definedName>
-    <definedName name="summeVerpflegungDo">Data!$DD$11</definedName>
-    <definedName name="summeVerpflegungFr">Data!$DZ$11</definedName>
-    <definedName name="summeVerpflegungMi">Data!$CH$11</definedName>
-    <definedName name="summeVerpflegungMo">Data!$AP$11</definedName>
-    <definedName name="summeVerpflegungNF1">Data!$AP$15</definedName>
-    <definedName name="summeVerpflegungNF2">Data!$BL$15</definedName>
-    <definedName name="summeVerpflegungNF3">Data!$CH$15</definedName>
-    <definedName name="summeVerpflegungNF4">Data!$DD$15</definedName>
-    <definedName name="summeVerpflegungNF5">Data!$DZ$15</definedName>
-    <definedName name="summeVerpflegungWoche">Data!$EB$11</definedName>
-    <definedName name="summStundenNF1">Data!$AO$15</definedName>
-    <definedName name="summStundenNF2">Data!$BK$15</definedName>
-    <definedName name="summStundenNF3">Data!$CG$15</definedName>
-    <definedName name="summStundenNF4">Data!$DC$15</definedName>
-    <definedName name="summStundenNF5">Data!$DY$15</definedName>
+    <definedName name="angemeldet1">Data!$V$11</definedName>
+    <definedName name="angemeldet10">Data!$AE$11</definedName>
+    <definedName name="angemeldet100">Data!$DY$11</definedName>
+    <definedName name="angemeldet11">Data!$AF$11</definedName>
+    <definedName name="angemeldet12">Data!$AG$11</definedName>
+    <definedName name="angemeldet13">Data!$AH$11</definedName>
+    <definedName name="angemeldet14">Data!$AI$11</definedName>
+    <definedName name="angemeldet15">Data!$AJ$11</definedName>
+    <definedName name="angemeldet16">Data!$AK$11</definedName>
+    <definedName name="angemeldet17">Data!$AL$11</definedName>
+    <definedName name="angemeldet18">Data!$AM$11</definedName>
+    <definedName name="angemeldet19">Data!$AN$11</definedName>
+    <definedName name="angemeldet2">Data!$W$11</definedName>
+    <definedName name="angemeldet20">Data!$AO$11</definedName>
+    <definedName name="angemeldet21">Data!$AR$11</definedName>
+    <definedName name="angemeldet22">Data!$AS$11</definedName>
+    <definedName name="angemeldet23">Data!$AT$11</definedName>
+    <definedName name="angemeldet24">Data!$AU$11</definedName>
+    <definedName name="angemeldet25">Data!$AV$11</definedName>
+    <definedName name="angemeldet26">Data!$AW$11</definedName>
+    <definedName name="angemeldet27">Data!$AX$11</definedName>
+    <definedName name="angemeldet28">Data!$AY$11</definedName>
+    <definedName name="angemeldet29">Data!$AZ$11</definedName>
+    <definedName name="angemeldet3">Data!$X$11</definedName>
+    <definedName name="angemeldet30">Data!$BA$11</definedName>
+    <definedName name="angemeldet31">Data!$BB$11</definedName>
+    <definedName name="angemeldet32">Data!$BC$11</definedName>
+    <definedName name="angemeldet33">Data!$BD$11</definedName>
+    <definedName name="angemeldet34">Data!$BE$11</definedName>
+    <definedName name="angemeldet35">Data!$BF$11</definedName>
+    <definedName name="angemeldet36">Data!$BG$11</definedName>
+    <definedName name="angemeldet37">Data!$BH$11</definedName>
+    <definedName name="angemeldet38">Data!$BI$11</definedName>
+    <definedName name="angemeldet39">Data!$BJ$11</definedName>
+    <definedName name="angemeldet4">Data!$Y$11</definedName>
+    <definedName name="angemeldet40">Data!$BK$11</definedName>
+    <definedName name="angemeldet41">Data!$BN$11</definedName>
+    <definedName name="angemeldet42">Data!$BO$11</definedName>
+    <definedName name="angemeldet43">Data!$BP$11</definedName>
+    <definedName name="angemeldet44">Data!$BQ$11</definedName>
+    <definedName name="angemeldet45">Data!$BR$11</definedName>
+    <definedName name="angemeldet46">Data!$BS$11</definedName>
+    <definedName name="angemeldet47">Data!$BT$11</definedName>
+    <definedName name="angemeldet48">Data!$BU$11</definedName>
+    <definedName name="angemeldet49">Data!$BV$11</definedName>
+    <definedName name="angemeldet5">Data!$Z$11</definedName>
+    <definedName name="angemeldet50">Data!$BW$11</definedName>
+    <definedName name="angemeldet51">Data!$BX$11</definedName>
+    <definedName name="angemeldet52">Data!$BY$11</definedName>
+    <definedName name="angemeldet53">Data!$BZ$11</definedName>
+    <definedName name="angemeldet54">Data!$CA$11</definedName>
+    <definedName name="angemeldet55">Data!$CB$11</definedName>
+    <definedName name="angemeldet56">Data!$CC$11</definedName>
+    <definedName name="angemeldet57">Data!$CD$11</definedName>
+    <definedName name="angemeldet58">Data!$CE$11</definedName>
+    <definedName name="angemeldet59">Data!$CF$11</definedName>
+    <definedName name="angemeldet6">Data!$AA$11</definedName>
+    <definedName name="angemeldet60">Data!$CG$11</definedName>
+    <definedName name="angemeldet61">Data!$CJ$11</definedName>
+    <definedName name="angemeldet62">Data!$CK$11</definedName>
+    <definedName name="angemeldet63">Data!$CL$11</definedName>
+    <definedName name="angemeldet64">Data!$CM$11</definedName>
+    <definedName name="angemeldet65">Data!$CN$11</definedName>
+    <definedName name="angemeldet66">Data!$CO$11</definedName>
+    <definedName name="angemeldet67">Data!$CP$11</definedName>
+    <definedName name="angemeldet68">Data!$CQ$11</definedName>
+    <definedName name="angemeldet69">Data!$CR$11</definedName>
+    <definedName name="angemeldet7">Data!$AB$11</definedName>
+    <definedName name="angemeldet70">Data!$CS$11</definedName>
+    <definedName name="angemeldet71">Data!$CT$11</definedName>
+    <definedName name="angemeldet72">Data!$CU$11</definedName>
+    <definedName name="angemeldet73">Data!$CV$11</definedName>
+    <definedName name="angemeldet74">Data!$CW$11</definedName>
+    <definedName name="angemeldet75">Data!$CX$11</definedName>
+    <definedName name="angemeldet76">Data!$CY$11</definedName>
+    <definedName name="angemeldet77">Data!$CZ$11</definedName>
+    <definedName name="angemeldet78">Data!$DA$11</definedName>
+    <definedName name="angemeldet79">Data!$DB$11</definedName>
+    <definedName name="angemeldet8">Data!$AC$11</definedName>
+    <definedName name="angemeldet80">Data!$DC$11</definedName>
+    <definedName name="angemeldet81">Data!$DF$11</definedName>
+    <definedName name="angemeldet82">Data!$DG$11</definedName>
+    <definedName name="angemeldet83">Data!$DH$11</definedName>
+    <definedName name="angemeldet84">Data!$DI$11</definedName>
+    <definedName name="angemeldet85">Data!$DJ$11</definedName>
+    <definedName name="angemeldet86">Data!$DK$11</definedName>
+    <definedName name="angemeldet87">Data!$DL$11</definedName>
+    <definedName name="angemeldet88">Data!$DM$11</definedName>
+    <definedName name="angemeldet89">Data!$DN$11</definedName>
+    <definedName name="angemeldet9">Data!$AD$11</definedName>
+    <definedName name="angemeldet90">Data!$DO$11</definedName>
+    <definedName name="angemeldet91">Data!$DP$11</definedName>
+    <definedName name="angemeldet92">Data!$DQ$11</definedName>
+    <definedName name="angemeldet93">Data!$DR$11</definedName>
+    <definedName name="angemeldet94">Data!$DS$11</definedName>
+    <definedName name="angemeldet95">Data!$DT$11</definedName>
+    <definedName name="angemeldet96">Data!$DU$11</definedName>
+    <definedName name="angemeldet97">Data!$DV$11</definedName>
+    <definedName name="angemeldet98">Data!$DW$11</definedName>
+    <definedName name="angemeldet99">Data!$DX$11</definedName>
+    <definedName name="freigegebenKategorie">Data!$U$15</definedName>
+    <definedName name="nichtFreigegeben1">Data!$V$15</definedName>
+    <definedName name="nichtFreigegeben10">Data!$AE$15</definedName>
+    <definedName name="nichtFreigegeben100">Data!$DY$15</definedName>
+    <definedName name="nichtFreigegeben11">Data!$AF$15</definedName>
+    <definedName name="nichtFreigegeben12">Data!$AG$15</definedName>
+    <definedName name="nichtFreigegeben13">Data!$AH$15</definedName>
+    <definedName name="nichtFreigegeben14">Data!$AI$15</definedName>
+    <definedName name="nichtFreigegeben15">Data!$AJ$15</definedName>
+    <definedName name="nichtFreigegeben16">Data!$AK$15</definedName>
+    <definedName name="nichtFreigegeben17">Data!$AL$15</definedName>
+    <definedName name="nichtFreigegeben18">Data!$AM$15</definedName>
+    <definedName name="nichtFreigegeben19">Data!$AN$15</definedName>
+    <definedName name="nichtFreigegeben2">Data!$W$15</definedName>
+    <definedName name="nichtFreigegeben20">Data!$AO$15</definedName>
+    <definedName name="nichtFreigegeben21">Data!$AR$15</definedName>
+    <definedName name="nichtFreigegeben22">Data!$AS$15</definedName>
+    <definedName name="nichtFreigegeben23">Data!$AT$15</definedName>
+    <definedName name="nichtFreigegeben24">Data!$AU$15</definedName>
+    <definedName name="nichtFreigegeben25">Data!$AV$15</definedName>
+    <definedName name="nichtFreigegeben26">Data!$AW$15</definedName>
+    <definedName name="nichtFreigegeben27">Data!$AX$15</definedName>
+    <definedName name="nichtFreigegeben28">Data!$AY$15</definedName>
+    <definedName name="nichtFreigegeben29">Data!$AZ$15</definedName>
+    <definedName name="nichtFreigegeben3">Data!$X$15</definedName>
+    <definedName name="nichtFreigegeben30">Data!$BA$15</definedName>
+    <definedName name="nichtFreigegeben31">Data!$BB$15</definedName>
+    <definedName name="nichtFreigegeben32">Data!$BC$15</definedName>
+    <definedName name="nichtFreigegeben33">Data!$BD$15</definedName>
+    <definedName name="nichtFreigegeben34">Data!$BE$15</definedName>
+    <definedName name="nichtFreigegeben35">Data!$BF$15</definedName>
+    <definedName name="nichtFreigegeben36">Data!$BG$15</definedName>
+    <definedName name="nichtFreigegeben37">Data!$BH$15</definedName>
+    <definedName name="nichtFreigegeben38">Data!$BI$15</definedName>
+    <definedName name="nichtFreigegeben39">Data!$BJ$15</definedName>
+    <definedName name="nichtFreigegeben4">Data!$Y$15</definedName>
+    <definedName name="nichtFreigegeben40">Data!$BK$15</definedName>
+    <definedName name="nichtFreigegeben41">Data!$BN$15</definedName>
+    <definedName name="nichtFreigegeben42">Data!$BO$15</definedName>
+    <definedName name="nichtFreigegeben43">Data!$BP$15</definedName>
+    <definedName name="nichtFreigegeben44">Data!$BQ$15</definedName>
+    <definedName name="nichtFreigegeben45">Data!$BR$15</definedName>
+    <definedName name="nichtFreigegeben46">Data!$BS$15</definedName>
+    <definedName name="nichtFreigegeben47">Data!$BT$15</definedName>
+    <definedName name="nichtFreigegeben48">Data!$BU$15</definedName>
+    <definedName name="nichtFreigegeben49">Data!$BV$15</definedName>
+    <definedName name="nichtFreigegeben5">Data!$Z$15</definedName>
+    <definedName name="nichtFreigegeben50">Data!$BW$15</definedName>
+    <definedName name="nichtFreigegeben51">Data!$BX$15</definedName>
+    <definedName name="nichtFreigegeben52">Data!$BY$15</definedName>
+    <definedName name="nichtFreigegeben53">Data!$BZ$15</definedName>
+    <definedName name="nichtFreigegeben54">Data!$CA$15</definedName>
+    <definedName name="nichtFreigegeben55">Data!$CB$15</definedName>
+    <definedName name="nichtFreigegeben56">Data!$CC$15</definedName>
+    <definedName name="nichtFreigegeben57">Data!$CD$15</definedName>
+    <definedName name="nichtFreigegeben58">Data!$CE$15</definedName>
+    <definedName name="nichtFreigegeben59">Data!$CF$15</definedName>
+    <definedName name="nichtFreigegeben6">Data!$AA$15</definedName>
+    <definedName name="nichtFreigegeben60">Data!$CG$15</definedName>
+    <definedName name="nichtFreigegeben61">Data!$CJ$15</definedName>
+    <definedName name="nichtFreigegeben62">Data!$CK$15</definedName>
+    <definedName name="nichtFreigegeben63">Data!$CL$15</definedName>
+    <definedName name="nichtFreigegeben64">Data!$CM$15</definedName>
+    <definedName name="nichtFreigegeben65">Data!$CN$15</definedName>
+    <definedName name="nichtFreigegeben66">Data!$CO$15</definedName>
+    <definedName name="nichtFreigegeben67">Data!$CP$15</definedName>
+    <definedName name="nichtFreigegeben68">Data!$CQ$15</definedName>
+    <definedName name="nichtFreigegeben69">Data!$CR$15</definedName>
+    <definedName name="nichtFreigegeben7">Data!$AB$15</definedName>
+    <definedName name="nichtFreigegeben70">Data!$CS$15</definedName>
+    <definedName name="nichtFreigegeben71">Data!$CT$15</definedName>
+    <definedName name="nichtFreigegeben72">Data!$CU$15</definedName>
+    <definedName name="nichtFreigegeben73">Data!$CV$15</definedName>
+    <definedName name="nichtFreigegeben74">Data!$CW$15</definedName>
+    <definedName name="nichtFreigegeben75">Data!$CX$15</definedName>
+    <definedName name="nichtFreigegeben76">Data!$CY$15</definedName>
+    <definedName name="nichtFreigegeben77">Data!$CZ$15</definedName>
+    <definedName name="nichtFreigegeben78">Data!$DA$15</definedName>
+    <definedName name="nichtFreigegeben79">Data!$DB$15</definedName>
+    <definedName name="nichtFreigegeben8">Data!$AC$15</definedName>
+    <definedName name="nichtFreigegeben80">Data!$DC$15</definedName>
+    <definedName name="nichtFreigegeben81">Data!$DF$15</definedName>
+    <definedName name="nichtFreigegeben82">Data!$DG$15</definedName>
+    <definedName name="nichtFreigegeben83">Data!$DH$15</definedName>
+    <definedName name="nichtFreigegeben84">Data!$DI$15</definedName>
+    <definedName name="nichtFreigegeben85">Data!$DJ$15</definedName>
+    <definedName name="nichtFreigegeben86">Data!$DK$15</definedName>
+    <definedName name="nichtFreigegeben87">Data!$DL$15</definedName>
+    <definedName name="nichtFreigegeben88">Data!$DM$15</definedName>
+    <definedName name="nichtFreigegeben89">Data!$DN$15</definedName>
+    <definedName name="nichtFreigegeben9">Data!$AD$15</definedName>
+    <definedName name="nichtFreigegeben90">Data!$DO$15</definedName>
+    <definedName name="nichtFreigegeben91">Data!$DP$15</definedName>
+    <definedName name="nichtFreigegeben92">Data!$DQ$15</definedName>
+    <definedName name="nichtFreigegeben93">Data!$DR$15</definedName>
+    <definedName name="nichtFreigegeben94">Data!$DS$15</definedName>
+    <definedName name="nichtFreigegeben95">Data!$DT$15</definedName>
+    <definedName name="nichtFreigegeben96">Data!$DU$15</definedName>
+    <definedName name="nichtFreigegeben97">Data!$DV$15</definedName>
+    <definedName name="nichtFreigegeben98">Data!$DW$15</definedName>
+    <definedName name="nichtFreigegeben99">Data!$DX$15</definedName>
+    <definedName name="statusKategorie">Data!$U$11</definedName>
+    <definedName name="summeStundenDi">Data!$BL$11</definedName>
+    <definedName name="summeStundenDo">Data!$DD$11</definedName>
+    <definedName name="summeStundenFr">Data!$DZ$11</definedName>
+    <definedName name="summeStundenMi">Data!$CH$11</definedName>
+    <definedName name="summeStundenMo">Data!$AP$11</definedName>
+    <definedName name="summeStundenWoche">Data!$EB$11</definedName>
+    <definedName name="summeVerpflegungDi">Data!$BM$11</definedName>
+    <definedName name="summeVerpflegungDo">Data!$DE$11</definedName>
+    <definedName name="summeVerpflegungFr">Data!$EA$11</definedName>
+    <definedName name="summeVerpflegungMi">Data!$CI$11</definedName>
+    <definedName name="summeVerpflegungMo">Data!$AQ$11</definedName>
+    <definedName name="summeVerpflegungNF1">Data!$AQ$15</definedName>
+    <definedName name="summeVerpflegungNF2">Data!$BM$15</definedName>
+    <definedName name="summeVerpflegungNF3">Data!$CI$15</definedName>
+    <definedName name="summeVerpflegungNF4">Data!$DE$15</definedName>
+    <definedName name="summeVerpflegungNF5">Data!$EA$15</definedName>
+    <definedName name="summeVerpflegungWoche">Data!$EC$11</definedName>
+    <definedName name="summStundenNF1">Data!$AP$15</definedName>
+    <definedName name="summStundenNF2">Data!$BL$15</definedName>
+    <definedName name="summStundenNF3">Data!$CH$15</definedName>
+    <definedName name="summStundenNF4">Data!$DD$15</definedName>
+    <definedName name="summStundenNF5">Data!$DZ$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="96">
   <si>
     <t>{statusTitle}</t>
   </si>
@@ -544,6 +544,12 @@
   </si>
   <si>
     <t>{abholungTagesschule}</t>
+  </si>
+  <si>
+    <t>{planKlasse}</t>
+  </si>
+  <si>
+    <t>{planKlasseTitle}</t>
   </si>
 </sst>
 </file>
@@ -807,7 +813,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -935,109 +941,121 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1414,29 +1432,29 @@
   <sheetPr codeName="Tabelle1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:EG39"/>
+  <dimension ref="A1:EH39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.7109375"/>
-    <col min="3" max="16" width="17.5703125" style="1" customWidth="1"/>
+    <col min="3" max="16" width="17.42578125" style="1" customWidth="1"/>
     <col min="17" max="18" width="17"/>
-    <col min="19" max="19" width="33.140625" customWidth="1"/>
-    <col min="20" max="20" width="33.140625" hidden="1" customWidth="1"/>
-    <col min="21" max="25" width="13.28515625" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" customWidth="1"/>
-    <col min="27" max="40" width="10.5703125"/>
-    <col min="43" max="62" width="10.5703125"/>
-    <col min="65" max="84" width="10.5703125"/>
-    <col min="87" max="106" width="10.5703125"/>
-    <col min="109" max="127" width="10.5703125"/>
-    <col min="128" max="128" width="10" customWidth="1"/>
-    <col min="131" max="132" width="10.5703125"/>
-    <col min="133" max="133" width="50" customWidth="1"/>
-    <col min="134" max="134" width="22.7109375" customWidth="1"/>
-    <col min="137" max="993" width="10.5703125"/>
+    <col min="19" max="20" width="33.140625" customWidth="1"/>
+    <col min="21" max="21" width="33.140625" hidden="1" customWidth="1"/>
+    <col min="22" max="26" width="13.28515625" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" customWidth="1"/>
+    <col min="28" max="41" width="10.42578125"/>
+    <col min="44" max="63" width="10.42578125"/>
+    <col min="66" max="85" width="10.42578125"/>
+    <col min="88" max="107" width="10.42578125"/>
+    <col min="110" max="128" width="10.42578125"/>
+    <col min="129" max="129" width="10" customWidth="1"/>
+    <col min="132" max="133" width="10.42578125"/>
+    <col min="134" max="134" width="50" customWidth="1"/>
+    <col min="135" max="135" width="22.7109375" customWidth="1"/>
+    <col min="138" max="994" width="10.42578125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:137" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:138" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1464,8 +1482,9 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:137" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1493,8 +1512,9 @@
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:137" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -1520,8 +1540,9 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:137" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -1547,8 +1568,9 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:137" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:138" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>47</v>
       </c>
@@ -1683,8 +1705,9 @@
       <c r="DX5" s="2"/>
       <c r="DY5" s="2"/>
       <c r="DZ5" s="2"/>
+      <c r="EA5" s="2"/>
     </row>
-    <row r="6" spans="1:137" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
@@ -1699,9 +1722,6 @@
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
-      <c r="U6" t="s">
-        <v>12</v>
-      </c>
       <c r="V6" t="s">
         <v>12</v>
       </c>
@@ -1759,8 +1779,8 @@
       <c r="AN6" t="s">
         <v>12</v>
       </c>
-      <c r="AQ6" t="s">
-        <v>13</v>
+      <c r="AO6" t="s">
+        <v>12</v>
       </c>
       <c r="AR6" t="s">
         <v>13</v>
@@ -1819,8 +1839,8 @@
       <c r="BJ6" t="s">
         <v>13</v>
       </c>
-      <c r="BM6" t="s">
-        <v>14</v>
+      <c r="BK6" t="s">
+        <v>13</v>
       </c>
       <c r="BN6" t="s">
         <v>14</v>
@@ -1879,8 +1899,8 @@
       <c r="CF6" t="s">
         <v>14</v>
       </c>
-      <c r="CI6" t="s">
-        <v>15</v>
+      <c r="CG6" t="s">
+        <v>14</v>
       </c>
       <c r="CJ6" t="s">
         <v>15</v>
@@ -1939,8 +1959,8 @@
       <c r="DB6" t="s">
         <v>15</v>
       </c>
-      <c r="DE6" t="s">
-        <v>16</v>
+      <c r="DC6" t="s">
+        <v>15</v>
       </c>
       <c r="DF6" t="s">
         <v>16</v>
@@ -1999,202 +2019,206 @@
       <c r="DX6" t="s">
         <v>16</v>
       </c>
+      <c r="DY6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="7" spans="1:137" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+    <row r="7" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="68" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="69"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="68" t="s">
+      <c r="E7" s="62"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="68" t="s">
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="69"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="69"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="74" t="s">
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="R7" s="74" t="s">
+      <c r="R7" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="S7" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="T7" s="14"/>
-      <c r="U7" s="60" t="s">
+      <c r="S7" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="U7" s="14"/>
+      <c r="V7" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="V7" s="61"/>
-      <c r="W7" s="61"/>
-      <c r="X7" s="61"/>
-      <c r="Y7" s="61"/>
-      <c r="Z7" s="61"/>
-      <c r="AA7" s="61"/>
-      <c r="AB7" s="61"/>
-      <c r="AC7" s="61"/>
-      <c r="AD7" s="61"/>
-      <c r="AE7" s="61"/>
-      <c r="AF7" s="61"/>
-      <c r="AG7" s="61"/>
-      <c r="AH7" s="61"/>
-      <c r="AI7" s="61"/>
-      <c r="AJ7" s="61"/>
-      <c r="AK7" s="61"/>
-      <c r="AL7" s="61"/>
-      <c r="AM7" s="61"/>
-      <c r="AN7" s="61"/>
-      <c r="AO7" s="61"/>
-      <c r="AP7" s="62"/>
-      <c r="AQ7" s="60" t="s">
+      <c r="W7" s="88"/>
+      <c r="X7" s="88"/>
+      <c r="Y7" s="88"/>
+      <c r="Z7" s="88"/>
+      <c r="AA7" s="88"/>
+      <c r="AB7" s="88"/>
+      <c r="AC7" s="88"/>
+      <c r="AD7" s="88"/>
+      <c r="AE7" s="88"/>
+      <c r="AF7" s="88"/>
+      <c r="AG7" s="88"/>
+      <c r="AH7" s="88"/>
+      <c r="AI7" s="88"/>
+      <c r="AJ7" s="88"/>
+      <c r="AK7" s="88"/>
+      <c r="AL7" s="88"/>
+      <c r="AM7" s="88"/>
+      <c r="AN7" s="88"/>
+      <c r="AO7" s="88"/>
+      <c r="AP7" s="88"/>
+      <c r="AQ7" s="89"/>
+      <c r="AR7" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="AR7" s="61"/>
-      <c r="AS7" s="61"/>
-      <c r="AT7" s="61"/>
-      <c r="AU7" s="61"/>
-      <c r="AV7" s="61"/>
-      <c r="AW7" s="61"/>
-      <c r="AX7" s="61"/>
-      <c r="AY7" s="61"/>
-      <c r="AZ7" s="61"/>
-      <c r="BA7" s="61"/>
-      <c r="BB7" s="61"/>
-      <c r="BC7" s="61"/>
-      <c r="BD7" s="61"/>
-      <c r="BE7" s="61"/>
-      <c r="BF7" s="61"/>
-      <c r="BG7" s="61"/>
-      <c r="BH7" s="61"/>
-      <c r="BI7" s="61"/>
-      <c r="BJ7" s="61"/>
-      <c r="BK7" s="61"/>
-      <c r="BL7" s="62"/>
-      <c r="BM7" s="60" t="s">
+      <c r="AS7" s="88"/>
+      <c r="AT7" s="88"/>
+      <c r="AU7" s="88"/>
+      <c r="AV7" s="88"/>
+      <c r="AW7" s="88"/>
+      <c r="AX7" s="88"/>
+      <c r="AY7" s="88"/>
+      <c r="AZ7" s="88"/>
+      <c r="BA7" s="88"/>
+      <c r="BB7" s="88"/>
+      <c r="BC7" s="88"/>
+      <c r="BD7" s="88"/>
+      <c r="BE7" s="88"/>
+      <c r="BF7" s="88"/>
+      <c r="BG7" s="88"/>
+      <c r="BH7" s="88"/>
+      <c r="BI7" s="88"/>
+      <c r="BJ7" s="88"/>
+      <c r="BK7" s="88"/>
+      <c r="BL7" s="88"/>
+      <c r="BM7" s="89"/>
+      <c r="BN7" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="BN7" s="61"/>
-      <c r="BO7" s="61"/>
-      <c r="BP7" s="61"/>
-      <c r="BQ7" s="61"/>
-      <c r="BR7" s="61"/>
-      <c r="BS7" s="61"/>
-      <c r="BT7" s="61"/>
-      <c r="BU7" s="61"/>
-      <c r="BV7" s="61"/>
-      <c r="BW7" s="61"/>
-      <c r="BX7" s="61"/>
-      <c r="BY7" s="61"/>
-      <c r="BZ7" s="61"/>
-      <c r="CA7" s="61"/>
-      <c r="CB7" s="61"/>
-      <c r="CC7" s="61"/>
-      <c r="CD7" s="61"/>
-      <c r="CE7" s="61"/>
-      <c r="CF7" s="61"/>
-      <c r="CG7" s="61"/>
-      <c r="CH7" s="62"/>
-      <c r="CI7" s="60" t="s">
+      <c r="BO7" s="88"/>
+      <c r="BP7" s="88"/>
+      <c r="BQ7" s="88"/>
+      <c r="BR7" s="88"/>
+      <c r="BS7" s="88"/>
+      <c r="BT7" s="88"/>
+      <c r="BU7" s="88"/>
+      <c r="BV7" s="88"/>
+      <c r="BW7" s="88"/>
+      <c r="BX7" s="88"/>
+      <c r="BY7" s="88"/>
+      <c r="BZ7" s="88"/>
+      <c r="CA7" s="88"/>
+      <c r="CB7" s="88"/>
+      <c r="CC7" s="88"/>
+      <c r="CD7" s="88"/>
+      <c r="CE7" s="88"/>
+      <c r="CF7" s="88"/>
+      <c r="CG7" s="88"/>
+      <c r="CH7" s="88"/>
+      <c r="CI7" s="89"/>
+      <c r="CJ7" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="CJ7" s="61"/>
-      <c r="CK7" s="61"/>
-      <c r="CL7" s="61"/>
-      <c r="CM7" s="61"/>
-      <c r="CN7" s="61"/>
-      <c r="CO7" s="61"/>
-      <c r="CP7" s="61"/>
-      <c r="CQ7" s="61"/>
-      <c r="CR7" s="61"/>
-      <c r="CS7" s="61"/>
-      <c r="CT7" s="61"/>
-      <c r="CU7" s="61"/>
-      <c r="CV7" s="61"/>
-      <c r="CW7" s="61"/>
-      <c r="CX7" s="61"/>
-      <c r="CY7" s="61"/>
-      <c r="CZ7" s="61"/>
-      <c r="DA7" s="61"/>
-      <c r="DB7" s="61"/>
-      <c r="DC7" s="61"/>
-      <c r="DD7" s="62"/>
-      <c r="DE7" s="60" t="s">
+      <c r="CK7" s="88"/>
+      <c r="CL7" s="88"/>
+      <c r="CM7" s="88"/>
+      <c r="CN7" s="88"/>
+      <c r="CO7" s="88"/>
+      <c r="CP7" s="88"/>
+      <c r="CQ7" s="88"/>
+      <c r="CR7" s="88"/>
+      <c r="CS7" s="88"/>
+      <c r="CT7" s="88"/>
+      <c r="CU7" s="88"/>
+      <c r="CV7" s="88"/>
+      <c r="CW7" s="88"/>
+      <c r="CX7" s="88"/>
+      <c r="CY7" s="88"/>
+      <c r="CZ7" s="88"/>
+      <c r="DA7" s="88"/>
+      <c r="DB7" s="88"/>
+      <c r="DC7" s="88"/>
+      <c r="DD7" s="88"/>
+      <c r="DE7" s="89"/>
+      <c r="DF7" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="DF7" s="61"/>
-      <c r="DG7" s="61"/>
-      <c r="DH7" s="61"/>
-      <c r="DI7" s="61"/>
-      <c r="DJ7" s="61"/>
-      <c r="DK7" s="61"/>
-      <c r="DL7" s="61"/>
-      <c r="DM7" s="61"/>
-      <c r="DN7" s="61"/>
-      <c r="DO7" s="61"/>
-      <c r="DP7" s="61"/>
-      <c r="DQ7" s="61"/>
-      <c r="DR7" s="61"/>
-      <c r="DS7" s="61"/>
-      <c r="DT7" s="61"/>
-      <c r="DU7" s="61"/>
-      <c r="DV7" s="61"/>
-      <c r="DW7" s="61"/>
-      <c r="DX7" s="61"/>
-      <c r="DY7" s="61"/>
-      <c r="DZ7" s="62"/>
-      <c r="EA7" s="88" t="s">
+      <c r="DG7" s="88"/>
+      <c r="DH7" s="88"/>
+      <c r="DI7" s="88"/>
+      <c r="DJ7" s="88"/>
+      <c r="DK7" s="88"/>
+      <c r="DL7" s="88"/>
+      <c r="DM7" s="88"/>
+      <c r="DN7" s="88"/>
+      <c r="DO7" s="88"/>
+      <c r="DP7" s="88"/>
+      <c r="DQ7" s="88"/>
+      <c r="DR7" s="88"/>
+      <c r="DS7" s="88"/>
+      <c r="DT7" s="88"/>
+      <c r="DU7" s="88"/>
+      <c r="DV7" s="88"/>
+      <c r="DW7" s="88"/>
+      <c r="DX7" s="88"/>
+      <c r="DY7" s="88"/>
+      <c r="DZ7" s="88"/>
+      <c r="EA7" s="89"/>
+      <c r="EB7" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="EB7" s="88"/>
-      <c r="EC7" s="52" t="s">
+      <c r="EC7" s="77"/>
+      <c r="ED7" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="ED7" s="89" t="s">
+      <c r="EE7" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="EE7" s="82" t="s">
+      <c r="EF7" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="EF7" s="83"/>
-      <c r="EG7" s="11"/>
+      <c r="EG7" s="72"/>
+      <c r="EH7" s="11"/>
     </row>
-    <row r="8" spans="1:137" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="73"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="77"/>
-      <c r="P8" s="78"/>
+    <row r="8" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="64"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="91"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="92"/>
       <c r="Q8" s="79"/>
       <c r="R8" s="79"/>
       <c r="S8" s="79"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="T8" s="59"/>
+      <c r="U8" s="15"/>
       <c r="V8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2252,15 +2276,15 @@
       <c r="AN8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AO8" s="64" t="s">
+      <c r="AO8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP8" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="AP8" s="64" t="s">
+      <c r="AQ8" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="AQ8" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="AR8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2318,15 +2342,15 @@
       <c r="BJ8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BK8" s="64" t="s">
+      <c r="BK8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="BL8" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="BL8" s="64" t="s">
+      <c r="BM8" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="BM8" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="BN8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2384,15 +2408,15 @@
       <c r="CF8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="CG8" s="64" t="s">
+      <c r="CG8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="CH8" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="CH8" s="64" t="s">
+      <c r="CI8" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="CI8" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="CJ8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2450,15 +2474,15 @@
       <c r="DB8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="DC8" s="64" t="s">
+      <c r="DC8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="DD8" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="DD8" s="64" t="s">
+      <c r="DE8" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="DE8" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="DF8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2513,82 +2537,83 @@
       <c r="DW8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="DX8" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="DY8" s="64" t="s">
+      <c r="DX8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="DY8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="DZ8" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="DZ8" s="64" t="s">
+      <c r="EA8" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="EA8" s="64" t="s">
+      <c r="EB8" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="EB8" s="64" t="s">
+      <c r="EC8" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="EC8" s="53"/>
-      <c r="ED8" s="90"/>
-      <c r="EE8" s="84"/>
-      <c r="EF8" s="85"/>
+      <c r="ED8" s="53"/>
+      <c r="EE8" s="81"/>
+      <c r="EF8" s="73"/>
+      <c r="EG8" s="74"/>
     </row>
-    <row r="9" spans="1:137" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
+    <row r="9" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E9" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="F9" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="74" t="s">
+      <c r="H9" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="74" t="s">
+      <c r="I9" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="74" t="s">
+      <c r="J9" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="74" t="s">
+      <c r="K9" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="L9" s="74" t="s">
+      <c r="L9" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="74" t="s">
+      <c r="M9" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="74" t="s">
+      <c r="N9" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="O9" s="74" t="s">
+      <c r="O9" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="P9" s="74" t="s">
+      <c r="P9" s="67" t="s">
         <v>72</v>
       </c>
       <c r="Q9" s="79"/>
       <c r="R9" s="79"/>
       <c r="S9" s="79"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="32" t="s">
-        <v>46</v>
-      </c>
+      <c r="T9" s="59"/>
+      <c r="U9" s="15"/>
       <c r="V9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2646,11 +2671,11 @@
       <c r="AN9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="AO9" s="65"/>
-      <c r="AP9" s="65"/>
-      <c r="AQ9" s="32" t="s">
-        <v>46</v>
-      </c>
+      <c r="AO9" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP9" s="85"/>
+      <c r="AQ9" s="85"/>
       <c r="AR9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2708,11 +2733,11 @@
       <c r="BJ9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="BK9" s="65"/>
-      <c r="BL9" s="65"/>
-      <c r="BM9" s="32" t="s">
-        <v>46</v>
-      </c>
+      <c r="BK9" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="BL9" s="85"/>
+      <c r="BM9" s="85"/>
       <c r="BN9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2770,11 +2795,11 @@
       <c r="CF9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="CG9" s="65"/>
-      <c r="CH9" s="65"/>
-      <c r="CI9" s="32" t="s">
-        <v>46</v>
-      </c>
+      <c r="CG9" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="CH9" s="85"/>
+      <c r="CI9" s="85"/>
       <c r="CJ9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2832,11 +2857,11 @@
       <c r="DB9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="DC9" s="65"/>
-      <c r="DD9" s="65"/>
-      <c r="DE9" s="32" t="s">
-        <v>46</v>
-      </c>
+      <c r="DC9" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="DD9" s="85"/>
+      <c r="DE9" s="85"/>
       <c r="DF9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2894,39 +2919,40 @@
       <c r="DX9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="DY9" s="65"/>
-      <c r="DZ9" s="65"/>
-      <c r="EA9" s="79"/>
+      <c r="DY9" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="DZ9" s="85"/>
+      <c r="EA9" s="85"/>
       <c r="EB9" s="79"/>
-      <c r="EC9" s="51"/>
-      <c r="ED9" s="90"/>
-      <c r="EE9" s="84"/>
-      <c r="EF9" s="85"/>
+      <c r="EC9" s="79"/>
+      <c r="ED9" s="51"/>
+      <c r="EE9" s="81"/>
+      <c r="EF9" s="73"/>
+      <c r="EG9" s="74"/>
     </row>
-    <row r="10" spans="1:137" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="75"/>
-      <c r="N10" s="75"/>
-      <c r="O10" s="75"/>
-      <c r="P10" s="75"/>
-      <c r="Q10" s="75"/>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="16" t="s">
-        <v>49</v>
-      </c>
+    <row r="10" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="68"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="58"/>
+      <c r="U10" s="15"/>
       <c r="V10" s="16" t="s">
         <v>49</v>
       </c>
@@ -2984,11 +3010,11 @@
       <c r="AN10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="AO10" s="66"/>
-      <c r="AP10" s="66"/>
-      <c r="AQ10" s="16" t="s">
-        <v>49</v>
-      </c>
+      <c r="AO10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP10" s="86"/>
+      <c r="AQ10" s="86"/>
       <c r="AR10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3046,11 +3072,11 @@
       <c r="BJ10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="BK10" s="66"/>
-      <c r="BL10" s="66"/>
-      <c r="BM10" s="16" t="s">
-        <v>49</v>
-      </c>
+      <c r="BK10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="BL10" s="86"/>
+      <c r="BM10" s="86"/>
       <c r="BN10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3108,11 +3134,11 @@
       <c r="CF10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="CG10" s="66"/>
-      <c r="CH10" s="66"/>
-      <c r="CI10" s="16" t="s">
-        <v>49</v>
-      </c>
+      <c r="CG10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="CH10" s="86"/>
+      <c r="CI10" s="86"/>
       <c r="CJ10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3170,11 +3196,11 @@
       <c r="DB10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="DC10" s="66"/>
-      <c r="DD10" s="66"/>
-      <c r="DE10" s="16" t="s">
-        <v>49</v>
-      </c>
+      <c r="DC10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="DD10" s="86"/>
+      <c r="DE10" s="86"/>
       <c r="DF10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3232,16 +3258,19 @@
       <c r="DX10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="DY10" s="66"/>
-      <c r="DZ10" s="66"/>
-      <c r="EA10" s="75"/>
-      <c r="EB10" s="75"/>
-      <c r="EC10" s="50"/>
-      <c r="ED10" s="91"/>
-      <c r="EE10" s="86"/>
-      <c r="EF10" s="87"/>
+      <c r="DY10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="DZ10" s="86"/>
+      <c r="EA10" s="86"/>
+      <c r="EB10" s="68"/>
+      <c r="EC10" s="68"/>
+      <c r="ED10" s="50"/>
+      <c r="EE10" s="82"/>
+      <c r="EF10" s="75"/>
+      <c r="EG10" s="76"/>
     </row>
-    <row r="11" spans="1:137" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>2</v>
       </c>
@@ -3299,13 +3328,13 @@
       <c r="S11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="T11" s="6" t="e">
+      <c r="T11" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="U11" s="6" t="e">
         <f>VLOOKUP(S11,$A$18:$B$29,2,FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="U11" s="19" t="s">
-        <v>8</v>
-      </c>
       <c r="V11" s="19" t="s">
         <v>8</v>
       </c>
@@ -3363,19 +3392,19 @@
       <c r="AN11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="AO11" s="31">
-        <f>SUMIF(U11:AN11,1,U$9:AN$9)
-+SUMIF(U11:AN11,2,U$9:AN$9)*0.5
-+SUMIF(U11:AN11,3,U$9:AN$9)</f>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="20">
-        <f>SUMIF(U11:AN11,1,U$10:AN$10)
-+SUMIF(U11:AN11,2,U$10:AN$10)*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>8</v>
+      <c r="AO11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP11" s="31">
+        <f>SUMIF(V11:AO11,1,V$9:AO$9)
++SUMIF(V11:AO11,2,V$9:AO$9)*0.5
++SUMIF(V11:AO11,3,V$9:AO$9)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="20">
+        <f>SUMIF(V11:AO11,1,V$10:AO$10)
++SUMIF(V11:AO11,2,V$10:AO$10)*0.5</f>
+        <v>0</v>
       </c>
       <c r="AR11" s="19" t="s">
         <v>8</v>
@@ -3434,19 +3463,19 @@
       <c r="BJ11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="BK11" s="31">
-        <f>SUMIF(AQ11:BJ11,1,AQ$9:BJ$9)
-+SUMIF(AQ11:BJ11,2,AQ$9:BJ$9)*0.5
-+SUMIF(AQ11:BJ11,3,AQ$9:BJ$9)</f>
-        <v>0</v>
-      </c>
-      <c r="BL11" s="20">
-        <f>SUMIF(AQ11:BJ11,1,AQ$10:BJ$10)
-+SUMIF(AQ11:BJ11,2,AQ$10:BJ$10)*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="BM11" s="19" t="s">
-        <v>8</v>
+      <c r="BK11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL11" s="31">
+        <f>SUMIF(AR11:BK11,1,AR$9:BK$9)
++SUMIF(AR11:BK11,2,AR$9:BK$9)*0.5
++SUMIF(AR11:BK11,3,AR$9:BK$9)</f>
+        <v>0</v>
+      </c>
+      <c r="BM11" s="20">
+        <f>SUMIF(AR11:BK11,1,AR$10:BK$10)
++SUMIF(AR11:BK11,2,AR$10:BK$10)*0.5</f>
+        <v>0</v>
       </c>
       <c r="BN11" s="19" t="s">
         <v>8</v>
@@ -3505,19 +3534,19 @@
       <c r="CF11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="CG11" s="31">
-        <f>SUMIF(BM11:CF11,1,BM$9:CF$9)
-+SUMIF(BM11:CF11,2,BM$9:CF$9)*0.5
-+SUMIF(BM11:CF11,3,BM$9:CF$9)</f>
-        <v>0</v>
-      </c>
-      <c r="CH11" s="20">
-        <f>SUMIF(BM11:CF11,1,BM$10:CF$10)
-+SUMIF(BM11:CF11,2,BM$10:CF$10)*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="CI11" s="19" t="s">
-        <v>8</v>
+      <c r="CG11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="CH11" s="31">
+        <f>SUMIF(BN11:CG11,1,BN$9:CG$9)
++SUMIF(BN11:CG11,2,BN$9:CG$9)*0.5
++SUMIF(BN11:CG11,3,BN$9:CG$9)</f>
+        <v>0</v>
+      </c>
+      <c r="CI11" s="20">
+        <f>SUMIF(BN11:CG11,1,BN$10:CG$10)
++SUMIF(BN11:CG11,2,BN$10:CG$10)*0.5</f>
+        <v>0</v>
       </c>
       <c r="CJ11" s="19" t="s">
         <v>8</v>
@@ -3576,19 +3605,19 @@
       <c r="DB11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="DC11" s="31">
-        <f>SUMIF(CI11:DB11,1,CI$9:DB$9)
-+SUMIF(CI11:DB11,2,CI$9:DB$9)*0.5
-+SUMIF(CI11:DB11,3,CI$9:DB$9)</f>
-        <v>0</v>
-      </c>
-      <c r="DD11" s="20">
-        <f>SUMIF(CI11:DB11,1,CI$10:DB$10)
-+SUMIF(CI11:DB11,2,CI$10:DB$10)*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="DE11" s="19" t="s">
-        <v>8</v>
+      <c r="DC11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="DD11" s="31">
+        <f>SUMIF(CJ11:DC11,1,CJ$9:DC$9)
++SUMIF(CJ11:DC11,2,CJ$9:DC$9)*0.5
++SUMIF(CJ11:DC11,3,CJ$9:DC$9)</f>
+        <v>0</v>
+      </c>
+      <c r="DE11" s="20">
+        <f>SUMIF(CJ11:DC11,1,CJ$10:DC$10)
++SUMIF(CJ11:DC11,2,CJ$10:DC$10)*0.5</f>
+        <v>0</v>
       </c>
       <c r="DF11" s="19" t="s">
         <v>8</v>
@@ -3647,1477 +3676,1483 @@
       <c r="DX11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="DY11" s="31">
-        <f>SUMIF(DE11:DX11,1,DE$9:DX$9)
-+SUMIF(DE11:DX11,2,DE$9:DX$9)*0.5
-+SUMIF(DE11:DX11,3,DE$9:DX$9)</f>
-        <v>0</v>
-      </c>
-      <c r="DZ11" s="20">
-        <f>SUMIF(DE11:DX11,1,DE$10:DX$10)
-+SUMIF(DE11:DX11,2,DE$10:DX$10)*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="EA11" s="31">
-        <f>SUM(DY11,AO11,BK11,CG11,DC11)</f>
-        <v>0</v>
-      </c>
-      <c r="EB11" s="21">
+      <c r="DY11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="DZ11" s="31">
+        <f>SUMIF(DF11:DY11,1,DF$9:DY$9)
++SUMIF(DF11:DY11,2,DF$9:DY$9)*0.5
++SUMIF(DF11:DY11,3,DF$9:DY$9)</f>
+        <v>0</v>
+      </c>
+      <c r="EA11" s="20">
+        <f>SUMIF(DF11:DY11,1,DF$10:DY$10)
++SUMIF(DF11:DY11,2,DF$10:DY$10)*0.5</f>
+        <v>0</v>
+      </c>
+      <c r="EB11" s="31">
         <f>SUM(DZ11,AP11,BL11,CH11,DD11)</f>
         <v>0</v>
       </c>
-      <c r="EC11" s="21" t="s">
+      <c r="EC11" s="21">
+        <f>SUM(EA11,AQ11,BM11,CI11,DE11)</f>
+        <v>0</v>
+      </c>
+      <c r="ED11" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="ED11" s="48" t="s">
+      <c r="EE11" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="EE11" s="92" t="s">
+      <c r="EF11" s="83" t="s">
         <v>77</v>
       </c>
-      <c r="EF11" s="93"/>
-      <c r="EG11" s="35" t="s">
+      <c r="EG11" s="84"/>
+      <c r="EH11" s="35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:137" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
+    <row r="12" spans="1:138" x14ac:dyDescent="0.25">
+      <c r="A12" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="59"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="94"/>
+      <c r="N12" s="94"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="95"/>
       <c r="S12" s="13">
         <f>COUNTIF(statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
       <c r="T12" s="13"/>
-      <c r="U12" s="13">
+      <c r="U12" s="13"/>
+      <c r="V12" s="13">
         <f>COUNTIFS(angemeldet1,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <f>COUNTIFS(angemeldet2,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <f>COUNTIFS(angemeldet3,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <f>COUNTIFS(angemeldet4,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <f>COUNTIFS(angemeldet5,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <f>COUNTIFS(angemeldet6,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <f>COUNTIFS(angemeldet7,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <f>COUNTIFS(angemeldet8,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <f>COUNTIFS(angemeldet9,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <f>COUNTIFS(angemeldet10,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <f>COUNTIFS(angemeldet11,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
         <f>COUNTIFS(angemeldet12,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AH12" s="13">
         <f>COUNTIFS(angemeldet13,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AI12" s="13">
         <f>COUNTIFS(angemeldet14,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AI12" s="13">
+      <c r="AJ12" s="13">
         <f>COUNTIFS(angemeldet15,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AJ12" s="13">
+      <c r="AK12" s="13">
         <f>COUNTIFS(angemeldet16,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AK12" s="13">
+      <c r="AL12" s="13">
         <f>COUNTIFS(angemeldet17,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AL12" s="13">
+      <c r="AM12" s="13">
         <f>COUNTIFS(angemeldet18,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="13">
+      <c r="AN12" s="13">
         <f>COUNTIFS(angemeldet19,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AN12" s="13">
+      <c r="AO12" s="13">
         <f>COUNTIFS(angemeldet20,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AO12" s="32">
+      <c r="AP12" s="32">
         <f>SUMIFS(summeStundenMo,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AP12" s="16">
+      <c r="AQ12" s="16">
         <f>SUMIFS(summeVerpflegungMo,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AQ12" s="13">
+      <c r="AR12" s="13">
         <f>COUNTIFS(angemeldet21,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AR12" s="13">
+      <c r="AS12" s="13">
         <f>COUNTIFS(angemeldet22,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AS12" s="13">
+      <c r="AT12" s="13">
         <f>COUNTIFS(angemeldet23,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AT12" s="13">
+      <c r="AU12" s="13">
         <f>COUNTIFS(angemeldet24,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AU12" s="13">
+      <c r="AV12" s="13">
         <f>COUNTIFS(angemeldet25,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AV12" s="13">
+      <c r="AW12" s="13">
         <f>COUNTIFS(angemeldet26,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AW12" s="13">
+      <c r="AX12" s="13">
         <f>COUNTIFS(angemeldet27,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AX12" s="13">
+      <c r="AY12" s="13">
         <f>COUNTIFS(angemeldet28,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AY12" s="13">
+      <c r="AZ12" s="13">
         <f>COUNTIFS(angemeldet29,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AZ12" s="13">
+      <c r="BA12" s="13">
         <f>COUNTIFS(angemeldet30,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BA12" s="13">
+      <c r="BB12" s="13">
         <f>COUNTIFS(angemeldet31,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BB12" s="13">
+      <c r="BC12" s="13">
         <f>COUNTIFS(angemeldet32,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BC12" s="13">
+      <c r="BD12" s="13">
         <f>COUNTIFS(angemeldet33,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BD12" s="13">
+      <c r="BE12" s="13">
         <f>COUNTIFS(angemeldet34,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BE12" s="13">
+      <c r="BF12" s="13">
         <f>COUNTIFS(angemeldet35,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BF12" s="13">
+      <c r="BG12" s="13">
         <f>COUNTIFS(angemeldet36,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BG12" s="13">
+      <c r="BH12" s="13">
         <f>COUNTIFS(angemeldet37,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BH12" s="13">
+      <c r="BI12" s="13">
         <f>COUNTIFS(angemeldet38,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BI12" s="13">
+      <c r="BJ12" s="13">
         <f>COUNTIFS(angemeldet39,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BJ12" s="13">
+      <c r="BK12" s="13">
         <f>COUNTIFS(angemeldet40,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BK12" s="32">
+      <c r="BL12" s="32">
         <f>SUMIFS(summeStundenDi,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BL12" s="16">
+      <c r="BM12" s="16">
         <f>SUMIFS(summeVerpflegungDi,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BM12" s="13">
+      <c r="BN12" s="13">
         <f>COUNTIFS(angemeldet41,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BN12" s="13">
+      <c r="BO12" s="13">
         <f>COUNTIFS(angemeldet42,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BO12" s="13">
+      <c r="BP12" s="13">
         <f>COUNTIFS(angemeldet43,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BP12" s="13">
+      <c r="BQ12" s="13">
         <f>COUNTIFS(angemeldet44,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BQ12" s="13">
+      <c r="BR12" s="13">
         <f>COUNTIFS(angemeldet45,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BR12" s="13">
+      <c r="BS12" s="13">
         <f>COUNTIFS(angemeldet46,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BS12" s="13">
+      <c r="BT12" s="13">
         <f>COUNTIFS(angemeldet47,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BT12" s="13">
+      <c r="BU12" s="13">
         <f>COUNTIFS(angemeldet48,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BU12" s="13">
+      <c r="BV12" s="13">
         <f>COUNTIFS(angemeldet49,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BV12" s="13">
+      <c r="BW12" s="13">
         <f>COUNTIFS(angemeldet50,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BW12" s="13">
+      <c r="BX12" s="13">
         <f>COUNTIFS(angemeldet51,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BX12" s="13">
+      <c r="BY12" s="13">
         <f>COUNTIFS(angemeldet52,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BY12" s="13">
+      <c r="BZ12" s="13">
         <f>COUNTIFS(angemeldet53,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BZ12" s="13">
+      <c r="CA12" s="13">
         <f>COUNTIFS(angemeldet54,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CA12" s="13">
+      <c r="CB12" s="13">
         <f>COUNTIFS(angemeldet55,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CB12" s="13">
+      <c r="CC12" s="13">
         <f>COUNTIFS(angemeldet56,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CC12" s="13">
+      <c r="CD12" s="13">
         <f>COUNTIFS(angemeldet57,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CD12" s="13">
+      <c r="CE12" s="13">
         <f>COUNTIFS(angemeldet58,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CE12" s="13">
+      <c r="CF12" s="13">
         <f>COUNTIFS(angemeldet59,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CF12" s="13">
+      <c r="CG12" s="13">
         <f>COUNTIFS(angemeldet60,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CG12" s="32">
+      <c r="CH12" s="32">
         <f>SUMIFS(summeStundenMi,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CH12" s="16">
+      <c r="CI12" s="16">
         <f>SUMIFS(summeVerpflegungMi,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CI12" s="13">
+      <c r="CJ12" s="13">
         <f>COUNTIFS(angemeldet61,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CJ12" s="13">
+      <c r="CK12" s="13">
         <f>COUNTIFS(angemeldet62,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CK12" s="13">
+      <c r="CL12" s="13">
         <f>COUNTIFS(angemeldet63,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CL12" s="13">
+      <c r="CM12" s="13">
         <f>COUNTIFS(angemeldet64,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CM12" s="13">
+      <c r="CN12" s="13">
         <f>COUNTIFS(angemeldet65,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CN12" s="13">
+      <c r="CO12" s="13">
         <f>COUNTIFS(angemeldet66,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CO12" s="13">
+      <c r="CP12" s="13">
         <f>COUNTIFS(angemeldet67,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CP12" s="13">
+      <c r="CQ12" s="13">
         <f>COUNTIFS(angemeldet68,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CQ12" s="13">
+      <c r="CR12" s="13">
         <f>COUNTIFS(angemeldet69,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CR12" s="13">
+      <c r="CS12" s="13">
         <f>COUNTIFS(angemeldet70,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CS12" s="13">
+      <c r="CT12" s="13">
         <f>COUNTIFS(angemeldet71,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CT12" s="13">
+      <c r="CU12" s="13">
         <f>COUNTIFS(angemeldet72,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CU12" s="13">
+      <c r="CV12" s="13">
         <f>COUNTIFS(angemeldet73,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CV12" s="13">
+      <c r="CW12" s="13">
         <f>COUNTIFS(angemeldet74,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CW12" s="13">
+      <c r="CX12" s="13">
         <f>COUNTIFS(angemeldet75,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CX12" s="13">
+      <c r="CY12" s="13">
         <f>COUNTIFS(angemeldet76,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CY12" s="13">
+      <c r="CZ12" s="13">
         <f>COUNTIFS(angemeldet77,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CZ12" s="13">
+      <c r="DA12" s="13">
         <f>COUNTIFS(angemeldet78,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DA12" s="13">
+      <c r="DB12" s="13">
         <f>COUNTIFS(angemeldet79,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DB12" s="13">
+      <c r="DC12" s="13">
         <f>COUNTIFS(angemeldet80,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DC12" s="32">
+      <c r="DD12" s="32">
         <f>SUMIFS(summeStundenDo,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DD12" s="16">
+      <c r="DE12" s="16">
         <f>SUMIFS(summeVerpflegungDo,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DE12" s="13">
+      <c r="DF12" s="13">
         <f>COUNTIFS(angemeldet81,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DF12" s="13">
+      <c r="DG12" s="13">
         <f>COUNTIFS(angemeldet82,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DG12" s="13">
+      <c r="DH12" s="13">
         <f>COUNTIFS(angemeldet83,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DH12" s="13">
+      <c r="DI12" s="13">
         <f>COUNTIFS(angemeldet84,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DI12" s="13">
+      <c r="DJ12" s="13">
         <f>COUNTIFS(angemeldet85,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DJ12" s="13">
+      <c r="DK12" s="13">
         <f>COUNTIFS(angemeldet86,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DK12" s="13">
+      <c r="DL12" s="13">
         <f>COUNTIFS(angemeldet87,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DL12" s="13">
+      <c r="DM12" s="13">
         <f>COUNTIFS(angemeldet88,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DM12" s="13">
+      <c r="DN12" s="13">
         <f>COUNTIFS(angemeldet89,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DN12" s="13">
+      <c r="DO12" s="13">
         <f>COUNTIFS(angemeldet90,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DO12" s="13">
+      <c r="DP12" s="13">
         <f>COUNTIFS(angemeldet91,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DP12" s="13">
+      <c r="DQ12" s="13">
         <f>COUNTIFS(angemeldet92,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DQ12" s="13">
+      <c r="DR12" s="13">
         <f>COUNTIFS(angemeldet93,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DR12" s="13">
+      <c r="DS12" s="13">
         <f>COUNTIFS(angemeldet94,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DS12" s="13">
+      <c r="DT12" s="13">
         <f>COUNTIFS(angemeldet95,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DT12" s="13">
+      <c r="DU12" s="13">
         <f>COUNTIFS(angemeldet96,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DU12" s="13">
+      <c r="DV12" s="13">
         <f>COUNTIFS(angemeldet97,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DV12" s="13">
+      <c r="DW12" s="13">
         <f>COUNTIFS(angemeldet98,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DW12" s="13">
+      <c r="DX12" s="13">
         <f>COUNTIFS(angemeldet99,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DX12" s="13">
+      <c r="DY12" s="13">
         <f>COUNTIFS(angemeldet100,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DY12" s="32">
+      <c r="DZ12" s="32">
         <f>SUMIFS(summeStundenFr,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DZ12" s="16">
+      <c r="EA12" s="16">
         <f>SUMIFS(summeVerpflegungFr,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="EA12" s="32">
+      <c r="EB12" s="32">
         <f>SUMIFS(summeStundenWoche,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="EB12" s="41">
+      <c r="EC12" s="41">
         <f>SUMIFS(summeVerpflegungWoche,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="EC12" s="54"/>
-      <c r="ED12" s="45"/>
-      <c r="EE12" s="39"/>
-      <c r="EF12" s="40"/>
+      <c r="ED12" s="54"/>
+      <c r="EE12" s="45"/>
+      <c r="EF12" s="39"/>
+      <c r="EG12" s="40"/>
     </row>
-    <row r="13" spans="1:137" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+    <row r="13" spans="1:138" x14ac:dyDescent="0.25">
+      <c r="A13" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="59"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="95"/>
       <c r="S13" s="13">
         <f>COUNTIF(statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
       <c r="T13" s="13"/>
-      <c r="U13" s="13">
+      <c r="U13" s="13"/>
+      <c r="V13" s="13">
         <f>COUNTIFS(angemeldet1,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="13">
+      <c r="W13" s="13">
         <f>COUNTIFS(angemeldet2,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="W13" s="13">
+      <c r="X13" s="13">
         <f>COUNTIFS(angemeldet3,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="X13" s="13">
+      <c r="Y13" s="13">
         <f>COUNTIFS(angemeldet4,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="13">
+      <c r="Z13" s="13">
         <f>COUNTIFS(angemeldet5,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="13">
+      <c r="AA13" s="13">
         <f>COUNTIFS(angemeldet6,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AA13" s="13">
+      <c r="AB13" s="13">
         <f>COUNTIFS(angemeldet7,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AB13" s="13">
+      <c r="AC13" s="13">
         <f>COUNTIFS(angemeldet8,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AC13" s="13">
+      <c r="AD13" s="13">
         <f>COUNTIFS(angemeldet9,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AD13" s="13">
+      <c r="AE13" s="13">
         <f>COUNTIFS(angemeldet10,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AE13" s="13">
+      <c r="AF13" s="13">
         <f>COUNTIFS(angemeldet11,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="13">
+      <c r="AG13" s="13">
         <f>COUNTIFS(angemeldet12,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AG13" s="13">
+      <c r="AH13" s="13">
         <f>COUNTIFS(angemeldet13,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AH13" s="13">
+      <c r="AI13" s="13">
         <f>COUNTIFS(angemeldet14,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AI13" s="13">
+      <c r="AJ13" s="13">
         <f>COUNTIFS(angemeldet15,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AJ13" s="13">
+      <c r="AK13" s="13">
         <f>COUNTIFS(angemeldet16,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AK13" s="13">
+      <c r="AL13" s="13">
         <f>COUNTIFS(angemeldet17,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AL13" s="13">
+      <c r="AM13" s="13">
         <f>COUNTIFS(angemeldet18,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AM13" s="13">
+      <c r="AN13" s="13">
         <f>COUNTIFS(angemeldet19,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AN13" s="13">
+      <c r="AO13" s="13">
         <f>COUNTIFS(angemeldet20,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AO13" s="32">
+      <c r="AP13" s="32">
         <f>SUMIFS(summeStundenMo,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AP13" s="16">
+      <c r="AQ13" s="16">
         <f>SUMIFS(summeVerpflegungMo,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="13">
+      <c r="AR13" s="13">
         <f>COUNTIFS(angemeldet21,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AR13" s="13">
+      <c r="AS13" s="13">
         <f>COUNTIFS(angemeldet22,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AS13" s="13">
+      <c r="AT13" s="13">
         <f>COUNTIFS(angemeldet23,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AT13" s="13">
+      <c r="AU13" s="13">
         <f>COUNTIFS(angemeldet24,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AU13" s="13">
+      <c r="AV13" s="13">
         <f>COUNTIFS(angemeldet25,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AV13" s="13">
+      <c r="AW13" s="13">
         <f>COUNTIFS(angemeldet26,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AW13" s="13">
+      <c r="AX13" s="13">
         <f>COUNTIFS(angemeldet27,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AX13" s="13">
+      <c r="AY13" s="13">
         <f>COUNTIFS(angemeldet28,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AY13" s="13">
+      <c r="AZ13" s="13">
         <f>COUNTIFS(angemeldet29,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AZ13" s="13">
+      <c r="BA13" s="13">
         <f>COUNTIFS(angemeldet30,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BA13" s="13">
+      <c r="BB13" s="13">
         <f>COUNTIFS(angemeldet31,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BB13" s="13">
+      <c r="BC13" s="13">
         <f>COUNTIFS(angemeldet32,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BC13" s="13">
+      <c r="BD13" s="13">
         <f>COUNTIFS(angemeldet33,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BD13" s="13">
+      <c r="BE13" s="13">
         <f>COUNTIFS(angemeldet34,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BE13" s="13">
+      <c r="BF13" s="13">
         <f>COUNTIFS(angemeldet35,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BF13" s="13">
+      <c r="BG13" s="13">
         <f>COUNTIFS(angemeldet36,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BG13" s="13">
+      <c r="BH13" s="13">
         <f>COUNTIFS(angemeldet37,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BH13" s="13">
+      <c r="BI13" s="13">
         <f>COUNTIFS(angemeldet38,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BI13" s="13">
+      <c r="BJ13" s="13">
         <f>COUNTIFS(angemeldet39,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BJ13" s="13">
+      <c r="BK13" s="13">
         <f>COUNTIFS(angemeldet40,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BK13" s="32">
+      <c r="BL13" s="32">
         <f>SUMIFS(summeStundenDi,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BL13" s="16">
+      <c r="BM13" s="16">
         <f>SUMIFS(summeVerpflegungDi,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BM13" s="13">
+      <c r="BN13" s="13">
         <f>COUNTIFS(angemeldet41,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BN13" s="13">
+      <c r="BO13" s="13">
         <f>COUNTIFS(angemeldet42,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BO13" s="13">
+      <c r="BP13" s="13">
         <f>COUNTIFS(angemeldet43,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BP13" s="13">
+      <c r="BQ13" s="13">
         <f>COUNTIFS(angemeldet44,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BQ13" s="13">
+      <c r="BR13" s="13">
         <f>COUNTIFS(angemeldet45,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BR13" s="13">
+      <c r="BS13" s="13">
         <f>COUNTIFS(angemeldet46,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BS13" s="13">
+      <c r="BT13" s="13">
         <f>COUNTIFS(angemeldet47,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BT13" s="13">
+      <c r="BU13" s="13">
         <f>COUNTIFS(angemeldet48,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BU13" s="13">
+      <c r="BV13" s="13">
         <f>COUNTIFS(angemeldet49,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BV13" s="13">
+      <c r="BW13" s="13">
         <f>COUNTIFS(angemeldet50,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BW13" s="13">
+      <c r="BX13" s="13">
         <f>COUNTIFS(angemeldet51,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BX13" s="13">
+      <c r="BY13" s="13">
         <f>COUNTIFS(angemeldet52,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BY13" s="13">
+      <c r="BZ13" s="13">
         <f>COUNTIFS(angemeldet53,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BZ13" s="13">
+      <c r="CA13" s="13">
         <f>COUNTIFS(angemeldet54,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CA13" s="13">
+      <c r="CB13" s="13">
         <f>COUNTIFS(angemeldet55,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CB13" s="13">
+      <c r="CC13" s="13">
         <f>COUNTIFS(angemeldet56,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CC13" s="13">
+      <c r="CD13" s="13">
         <f>COUNTIFS(angemeldet57,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CD13" s="13">
+      <c r="CE13" s="13">
         <f>COUNTIFS(angemeldet58,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CE13" s="13">
+      <c r="CF13" s="13">
         <f>COUNTIFS(angemeldet59,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CF13" s="13">
+      <c r="CG13" s="13">
         <f>COUNTIFS(angemeldet60,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CG13" s="32">
+      <c r="CH13" s="32">
         <f>SUMIFS(summeStundenMi,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CH13" s="16">
+      <c r="CI13" s="16">
         <f>SUMIFS(summeVerpflegungMi,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CI13" s="13">
+      <c r="CJ13" s="13">
         <f>COUNTIFS(angemeldet61,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CJ13" s="13">
+      <c r="CK13" s="13">
         <f>COUNTIFS(angemeldet62,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CK13" s="13">
+      <c r="CL13" s="13">
         <f>COUNTIFS(angemeldet63,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CL13" s="13">
+      <c r="CM13" s="13">
         <f>COUNTIFS(angemeldet64,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CM13" s="13">
+      <c r="CN13" s="13">
         <f>COUNTIFS(angemeldet65,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CN13" s="13">
+      <c r="CO13" s="13">
         <f>COUNTIFS(angemeldet66,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CO13" s="13">
+      <c r="CP13" s="13">
         <f>COUNTIFS(angemeldet67,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CP13" s="13">
+      <c r="CQ13" s="13">
         <f>COUNTIFS(angemeldet68,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CQ13" s="13">
+      <c r="CR13" s="13">
         <f>COUNTIFS(angemeldet69,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CR13" s="13">
+      <c r="CS13" s="13">
         <f>COUNTIFS(angemeldet70,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CS13" s="13">
+      <c r="CT13" s="13">
         <f>COUNTIFS(angemeldet71,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CT13" s="13">
+      <c r="CU13" s="13">
         <f>COUNTIFS(angemeldet72,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CU13" s="13">
+      <c r="CV13" s="13">
         <f>COUNTIFS(angemeldet73,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CV13" s="13">
+      <c r="CW13" s="13">
         <f>COUNTIFS(angemeldet74,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CW13" s="13">
+      <c r="CX13" s="13">
         <f>COUNTIFS(angemeldet75,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CX13" s="13">
+      <c r="CY13" s="13">
         <f>COUNTIFS(angemeldet76,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CY13" s="13">
+      <c r="CZ13" s="13">
         <f>COUNTIFS(angemeldet77,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CZ13" s="13">
+      <c r="DA13" s="13">
         <f>COUNTIFS(angemeldet78,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DA13" s="13">
+      <c r="DB13" s="13">
         <f>COUNTIFS(angemeldet79,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DB13" s="13">
+      <c r="DC13" s="13">
         <f>COUNTIFS(angemeldet80,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DC13" s="32">
+      <c r="DD13" s="32">
         <f>SUMIFS(summeStundenDo,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DD13" s="16">
+      <c r="DE13" s="16">
         <f>SUMIFS(summeVerpflegungDo,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DE13" s="13">
+      <c r="DF13" s="13">
         <f>COUNTIFS(angemeldet81,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DF13" s="13">
+      <c r="DG13" s="13">
         <f>COUNTIFS(angemeldet82,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DG13" s="13">
+      <c r="DH13" s="13">
         <f>COUNTIFS(angemeldet83,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DH13" s="13">
+      <c r="DI13" s="13">
         <f>COUNTIFS(angemeldet84,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DI13" s="13">
+      <c r="DJ13" s="13">
         <f>COUNTIFS(angemeldet85,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DJ13" s="13">
+      <c r="DK13" s="13">
         <f>COUNTIFS(angemeldet86,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DK13" s="13">
+      <c r="DL13" s="13">
         <f>COUNTIFS(angemeldet87,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DL13" s="13">
+      <c r="DM13" s="13">
         <f>COUNTIFS(angemeldet88,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DM13" s="13">
+      <c r="DN13" s="13">
         <f>COUNTIFS(angemeldet89,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DN13" s="13">
+      <c r="DO13" s="13">
         <f>COUNTIFS(angemeldet90,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DO13" s="13">
+      <c r="DP13" s="13">
         <f>COUNTIFS(angemeldet91,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DP13" s="13">
+      <c r="DQ13" s="13">
         <f>COUNTIFS(angemeldet92,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DQ13" s="13">
+      <c r="DR13" s="13">
         <f>COUNTIFS(angemeldet93,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DR13" s="13">
+      <c r="DS13" s="13">
         <f>COUNTIFS(angemeldet94,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DS13" s="13">
+      <c r="DT13" s="13">
         <f>COUNTIFS(angemeldet95,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DT13" s="13">
+      <c r="DU13" s="13">
         <f>COUNTIFS(angemeldet96,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DU13" s="13">
+      <c r="DV13" s="13">
         <f>COUNTIFS(angemeldet97,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DV13" s="13">
+      <c r="DW13" s="13">
         <f>COUNTIFS(angemeldet98,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DW13" s="13">
+      <c r="DX13" s="13">
         <f>COUNTIFS(angemeldet99,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DX13" s="13">
+      <c r="DY13" s="13">
         <f>COUNTIFS(angemeldet100,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DY13" s="32">
+      <c r="DZ13" s="32">
         <f>SUMIFS(summeStundenFr,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DZ13" s="16">
+      <c r="EA13" s="16">
         <f>SUMIFS(summeVerpflegungFr,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="EA13" s="32">
+      <c r="EB13" s="32">
         <f>SUMIFS(summeStundenWoche,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="EB13" s="42">
+      <c r="EC13" s="42">
         <f>SUMIFS(summeVerpflegungWoche,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="EC13" s="55"/>
-      <c r="ED13" s="46"/>
-      <c r="EE13" s="28"/>
-      <c r="EF13" s="44"/>
+      <c r="ED13" s="55"/>
+      <c r="EE13" s="46"/>
+      <c r="EF13" s="28"/>
+      <c r="EG13" s="44"/>
     </row>
-    <row r="14" spans="1:137" x14ac:dyDescent="0.25">
-      <c r="A14" s="57" t="s">
+    <row r="14" spans="1:138" x14ac:dyDescent="0.25">
+      <c r="A14" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="59"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="94"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="94"/>
+      <c r="N14" s="94"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="95"/>
       <c r="S14" s="13">
         <f>COUNTIF(statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
       <c r="T14" s="13"/>
-      <c r="U14" s="13">
+      <c r="U14" s="13"/>
+      <c r="V14" s="13">
         <f>COUNTIFS(angemeldet1,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <f>COUNTIFS(angemeldet2,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <f>COUNTIFS(angemeldet3,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <f>COUNTIFS(angemeldet4,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <f>COUNTIFS(angemeldet5,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <f>COUNTIFS(angemeldet6,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <f>COUNTIFS(angemeldet7,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <f>COUNTIFS(angemeldet8,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <f>COUNTIFS(angemeldet9,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <f>COUNTIFS(angemeldet10,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <f>COUNTIFS(angemeldet11,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <f>COUNTIFS(angemeldet12,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <f>COUNTIFS(angemeldet13,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <f>COUNTIFS(angemeldet14,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <f>COUNTIFS(angemeldet15,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <f>COUNTIFS(angemeldet16,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <f>COUNTIFS(angemeldet17,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <f>COUNTIFS(angemeldet18,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <f>COUNTIFS(angemeldet19,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <f>COUNTIFS(angemeldet20,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="33">
+      <c r="AP14" s="33">
         <f>SUMIFS(summeStundenMo,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AP14" s="23">
+      <c r="AQ14" s="23">
         <f>SUMIFS(summeVerpflegungMo,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AR14" s="13">
         <f>COUNTIFS(angemeldet21,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <f>COUNTIFS(angemeldet22,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <f>COUNTIFS(angemeldet23,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <f>COUNTIFS(angemeldet24,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <f>COUNTIFS(angemeldet25,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <f>COUNTIFS(angemeldet26,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <f>COUNTIFS(angemeldet27,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <f>COUNTIFS(angemeldet28,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <f>COUNTIFS(angemeldet29,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <f>COUNTIFS(angemeldet30,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BB14" s="13">
         <f>COUNTIFS(angemeldet31,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BC14" s="13">
         <f>COUNTIFS(angemeldet32,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <f>COUNTIFS(angemeldet33,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <f>COUNTIFS(angemeldet34,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <f>COUNTIFS(angemeldet35,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <f>COUNTIFS(angemeldet36,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <f>COUNTIFS(angemeldet37,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <f>COUNTIFS(angemeldet38,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <f>COUNTIFS(angemeldet39,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <f>COUNTIFS(angemeldet40,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="33">
+      <c r="BL14" s="33">
         <f>SUMIFS(summeStundenDi,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BL14" s="23">
+      <c r="BM14" s="23">
         <f>SUMIFS(summeVerpflegungDi,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BN14" s="13">
         <f>COUNTIFS(angemeldet41,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BN14" s="13">
+      <c r="BO14" s="13">
         <f>COUNTIFS(angemeldet42,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BO14" s="13">
+      <c r="BP14" s="13">
         <f>COUNTIFS(angemeldet43,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BQ14" s="13">
         <f>COUNTIFS(angemeldet44,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BQ14" s="13">
+      <c r="BR14" s="13">
         <f>COUNTIFS(angemeldet45,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BR14" s="13">
+      <c r="BS14" s="13">
         <f>COUNTIFS(angemeldet46,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BS14" s="13">
+      <c r="BT14" s="13">
         <f>COUNTIFS(angemeldet47,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BT14" s="13">
+      <c r="BU14" s="13">
         <f>COUNTIFS(angemeldet48,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BU14" s="13">
+      <c r="BV14" s="13">
         <f>COUNTIFS(angemeldet49,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BV14" s="13">
+      <c r="BW14" s="13">
         <f>COUNTIFS(angemeldet50,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BW14" s="13">
+      <c r="BX14" s="13">
         <f>COUNTIFS(angemeldet51,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BX14" s="13">
+      <c r="BY14" s="13">
         <f>COUNTIFS(angemeldet52,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BY14" s="13">
+      <c r="BZ14" s="13">
         <f>COUNTIFS(angemeldet53,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BZ14" s="13">
+      <c r="CA14" s="13">
         <f>COUNTIFS(angemeldet54,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CA14" s="13">
+      <c r="CB14" s="13">
         <f>COUNTIFS(angemeldet55,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CB14" s="13">
+      <c r="CC14" s="13">
         <f>COUNTIFS(angemeldet56,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CC14" s="13">
+      <c r="CD14" s="13">
         <f>COUNTIFS(angemeldet57,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CD14" s="13">
+      <c r="CE14" s="13">
         <f>COUNTIFS(angemeldet58,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CE14" s="13">
+      <c r="CF14" s="13">
         <f>COUNTIFS(angemeldet59,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CF14" s="13">
+      <c r="CG14" s="13">
         <f>COUNTIFS(angemeldet60,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CG14" s="33">
+      <c r="CH14" s="33">
         <f>SUMIFS(summeStundenMi,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CH14" s="23">
+      <c r="CI14" s="23">
         <f>SUMIFS(summeVerpflegungMi,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CI14" s="13">
+      <c r="CJ14" s="13">
         <f>COUNTIFS(angemeldet61,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CJ14" s="13">
+      <c r="CK14" s="13">
         <f>COUNTIFS(angemeldet62,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CK14" s="13">
+      <c r="CL14" s="13">
         <f>COUNTIFS(angemeldet63,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CL14" s="13">
+      <c r="CM14" s="13">
         <f>COUNTIFS(angemeldet64,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CM14" s="13">
+      <c r="CN14" s="13">
         <f>COUNTIFS(angemeldet65,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CN14" s="13">
+      <c r="CO14" s="13">
         <f>COUNTIFS(angemeldet66,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CO14" s="13">
+      <c r="CP14" s="13">
         <f>COUNTIFS(angemeldet67,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CP14" s="13">
+      <c r="CQ14" s="13">
         <f>COUNTIFS(angemeldet68,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CQ14" s="13">
+      <c r="CR14" s="13">
         <f>COUNTIFS(angemeldet69,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CR14" s="13">
+      <c r="CS14" s="13">
         <f>COUNTIFS(angemeldet70,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CS14" s="13">
+      <c r="CT14" s="13">
         <f>COUNTIFS(angemeldet71,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CT14" s="13">
+      <c r="CU14" s="13">
         <f>COUNTIFS(angemeldet72,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CU14" s="13">
+      <c r="CV14" s="13">
         <f>COUNTIFS(angemeldet73,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CV14" s="13">
+      <c r="CW14" s="13">
         <f>COUNTIFS(angemeldet74,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CW14" s="13">
+      <c r="CX14" s="13">
         <f>COUNTIFS(angemeldet75,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CX14" s="13">
+      <c r="CY14" s="13">
         <f>COUNTIFS(angemeldet76,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CY14" s="13">
+      <c r="CZ14" s="13">
         <f>COUNTIFS(angemeldet77,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CZ14" s="13">
+      <c r="DA14" s="13">
         <f>COUNTIFS(angemeldet78,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DA14" s="13">
+      <c r="DB14" s="13">
         <f>COUNTIFS(angemeldet79,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DB14" s="13">
+      <c r="DC14" s="13">
         <f>COUNTIFS(angemeldet80,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DC14" s="33">
+      <c r="DD14" s="33">
         <f>SUMIFS(summeStundenDo,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DD14" s="23">
+      <c r="DE14" s="23">
         <f>SUMIFS(summeVerpflegungDo,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DE14" s="13">
+      <c r="DF14" s="13">
         <f>COUNTIFS(angemeldet81,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DF14" s="13">
+      <c r="DG14" s="13">
         <f>COUNTIFS(angemeldet82,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DG14" s="13">
+      <c r="DH14" s="13">
         <f>COUNTIFS(angemeldet83,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DH14" s="13">
+      <c r="DI14" s="13">
         <f>COUNTIFS(angemeldet84,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DI14" s="13">
+      <c r="DJ14" s="13">
         <f>COUNTIFS(angemeldet85,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DJ14" s="13">
+      <c r="DK14" s="13">
         <f>COUNTIFS(angemeldet86,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DK14" s="13">
+      <c r="DL14" s="13">
         <f>COUNTIFS(angemeldet87,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DL14" s="13">
+      <c r="DM14" s="13">
         <f>COUNTIFS(angemeldet88,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DM14" s="13">
+      <c r="DN14" s="13">
         <f>COUNTIFS(angemeldet89,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DN14" s="13">
+      <c r="DO14" s="13">
         <f>COUNTIFS(angemeldet90,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DO14" s="13">
+      <c r="DP14" s="13">
         <f>COUNTIFS(angemeldet91,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DP14" s="13">
+      <c r="DQ14" s="13">
         <f>COUNTIFS(angemeldet92,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DQ14" s="13">
+      <c r="DR14" s="13">
         <f>COUNTIFS(angemeldet93,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DR14" s="13">
+      <c r="DS14" s="13">
         <f>COUNTIFS(angemeldet94,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DS14" s="13">
+      <c r="DT14" s="13">
         <f>COUNTIFS(angemeldet95,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DT14" s="13">
+      <c r="DU14" s="13">
         <f>COUNTIFS(angemeldet96,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DU14" s="13">
+      <c r="DV14" s="13">
         <f>COUNTIFS(angemeldet97,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DV14" s="13">
+      <c r="DW14" s="13">
         <f>COUNTIFS(angemeldet98,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DW14" s="13">
+      <c r="DX14" s="13">
         <f>COUNTIFS(angemeldet99,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DX14" s="13">
+      <c r="DY14" s="13">
         <f>COUNTIFS(angemeldet100,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DY14" s="33">
+      <c r="DZ14" s="33">
         <f>SUMIFS(summeStundenFr,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DZ14" s="23">
+      <c r="EA14" s="23">
         <f>SUMIFS(summeVerpflegungFr,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="EA14" s="33">
+      <c r="EB14" s="33">
         <f>SUMIFS(summeStundenWoche,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="EB14" s="43">
+      <c r="EC14" s="43">
         <f>SUMIFS(summeVerpflegungWoche,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="EC14" s="42"/>
-      <c r="ED14" s="47"/>
-      <c r="EE14" s="38"/>
-      <c r="EF14" s="36"/>
+      <c r="ED14" s="42"/>
+      <c r="EE14" s="47"/>
+      <c r="EF14" s="38"/>
+      <c r="EG14" s="36"/>
     </row>
-    <row r="15" spans="1:137" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:138" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>2</v>
       </c>
@@ -5175,13 +5210,13 @@
       <c r="S15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="T15" s="6" t="e">
+      <c r="T15" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="U15" s="6" t="e">
         <f>VLOOKUP(S15,$A$18:$B$29,2,FALSE)</f>
         <v>#N/A</v>
       </c>
-      <c r="U15" s="9" t="s">
-        <v>8</v>
-      </c>
       <c r="V15" s="9" t="s">
         <v>8</v>
       </c>
@@ -5236,15 +5271,15 @@
       <c r="AM15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="AN15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO15" s="26"/>
-      <c r="AP15" s="27"/>
-      <c r="AQ15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR15" s="9" t="s">
+      <c r="AN15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO15" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP15" s="26"/>
+      <c r="AQ15" s="27"/>
+      <c r="AR15" s="24" t="s">
         <v>8</v>
       </c>
       <c r="AS15" s="9" t="s">
@@ -5298,15 +5333,15 @@
       <c r="BI15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="BJ15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="BK15" s="26"/>
-      <c r="BL15" s="27"/>
-      <c r="BM15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="BN15" s="9" t="s">
+      <c r="BJ15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK15" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL15" s="26"/>
+      <c r="BM15" s="27"/>
+      <c r="BN15" s="24" t="s">
         <v>8</v>
       </c>
       <c r="BO15" s="9" t="s">
@@ -5360,15 +5395,15 @@
       <c r="CE15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="CF15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="CG15" s="26"/>
-      <c r="CH15" s="27"/>
-      <c r="CI15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="CJ15" s="9" t="s">
+      <c r="CF15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="CG15" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="CH15" s="26"/>
+      <c r="CI15" s="27"/>
+      <c r="CJ15" s="24" t="s">
         <v>8</v>
       </c>
       <c r="CK15" s="9" t="s">
@@ -5422,15 +5457,15 @@
       <c r="DA15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="DB15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="DC15" s="26"/>
-      <c r="DD15" s="27"/>
-      <c r="DE15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="DF15" s="9" t="s">
+      <c r="DB15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="DC15" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="DD15" s="26"/>
+      <c r="DE15" s="27"/>
+      <c r="DF15" s="24" t="s">
         <v>8</v>
       </c>
       <c r="DG15" s="9" t="s">
@@ -5484,485 +5519,489 @@
       <c r="DW15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="DX15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="DY15" s="26"/>
-      <c r="DZ15" s="27"/>
-      <c r="EA15" s="30"/>
-      <c r="EB15" s="37"/>
-      <c r="EC15" s="56" t="s">
+      <c r="DX15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="DY15" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="DZ15" s="26"/>
+      <c r="EA15" s="27"/>
+      <c r="EB15" s="30"/>
+      <c r="EC15" s="37"/>
+      <c r="ED15" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="ED15" s="48" t="s">
+      <c r="EE15" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="EE15" s="80" t="s">
+      <c r="EF15" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="EF15" s="81"/>
-      <c r="EG15" t="s">
+      <c r="EG15" s="70"/>
+      <c r="EH15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:137" x14ac:dyDescent="0.25">
-      <c r="A16" s="67" t="s">
+    <row r="16" spans="1:138" x14ac:dyDescent="0.25">
+      <c r="A16" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="67"/>
-      <c r="M16" s="67"/>
-      <c r="N16" s="67"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="67"/>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="67"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
+      <c r="M16" s="97"/>
+      <c r="N16" s="97"/>
+      <c r="O16" s="97"/>
+      <c r="P16" s="97"/>
+      <c r="Q16" s="97"/>
+      <c r="R16" s="97"/>
       <c r="S16" s="13">
         <f>COUNTIF(freigegebenKategorie,$B$34)</f>
         <v>0</v>
       </c>
       <c r="T16" s="13"/>
-      <c r="U16" s="13">
+      <c r="U16" s="13"/>
+      <c r="V16" s="13">
         <f>COUNTIF(nichtFreigegeben1,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="V16" s="13">
+      <c r="W16" s="13">
         <f>COUNTIF(nichtFreigegeben2,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <f>COUNTIF(nichtFreigegeben3,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <f>COUNTIF(nichtFreigegeben4,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <f>COUNTIF(nichtFreigegeben5,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <f>COUNTIF(nichtFreigegeben6,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <f>COUNTIF(nichtFreigegeben7,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <f>COUNTIF(nichtFreigegeben8,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AD16" s="13">
         <f>COUNTIF(nichtFreigegeben9,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AE16" s="13">
         <f>COUNTIF(nichtFreigegeben10,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AF16" s="13">
         <f>COUNTIF(nichtFreigegeben11,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AG16" s="13">
         <f>COUNTIF(nichtFreigegeben12,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AH16" s="13">
         <f>COUNTIF(nichtFreigegeben13,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <f>COUNTIF(nichtFreigegeben14,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AJ16" s="13">
         <f>COUNTIF(nichtFreigegeben15,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AK16" s="13">
         <f>COUNTIF(nichtFreigegeben16,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AL16" s="13">
         <f>COUNTIF(nichtFreigegeben17,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <f>COUNTIF(nichtFreigegeben18,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <f>COUNTIF(nichtFreigegeben19,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AO16" s="13">
         <f>COUNTIF(nichtFreigegeben20,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AO16" s="28"/>
       <c r="AP16" s="28"/>
-      <c r="AQ16" s="13">
+      <c r="AQ16" s="28"/>
+      <c r="AR16" s="13">
         <f>COUNTIF(nichtFreigegeben21,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <f>COUNTIF(nichtFreigegeben22,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <f>COUNTIF(nichtFreigegeben23,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <f>COUNTIF(nichtFreigegeben24,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <f>COUNTIF(nichtFreigegeben25,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <f>COUNTIF(nichtFreigegeben26,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <f>COUNTIF(nichtFreigegeben27,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <f>COUNTIF(nichtFreigegeben28,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <f>COUNTIF(nichtFreigegeben29,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <f>COUNTIF(nichtFreigegeben30,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <f>COUNTIF(nichtFreigegeben31,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <f>COUNTIF(nichtFreigegeben32,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <f>COUNTIF(nichtFreigegeben33,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <f>COUNTIF(nichtFreigegeben34,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <f>COUNTIF(nichtFreigegeben35,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <f>COUNTIF(nichtFreigegeben36,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <f>COUNTIF(nichtFreigegeben37,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <f>COUNTIF(nichtFreigegeben38,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <f>COUNTIF(nichtFreigegeben39,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <f>COUNTIF(nichtFreigegeben40,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BK16" s="28"/>
       <c r="BL16" s="28"/>
-      <c r="BM16" s="13">
+      <c r="BM16" s="28"/>
+      <c r="BN16" s="13">
         <f>COUNTIF(nichtFreigegeben41,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BO16" s="13">
         <f>COUNTIF(nichtFreigegeben42,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BO16" s="13">
+      <c r="BP16" s="13">
         <f>COUNTIF(nichtFreigegeben43,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BQ16" s="13">
         <f>COUNTIF(nichtFreigegeben44,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BQ16" s="13">
+      <c r="BR16" s="13">
         <f>COUNTIF(nichtFreigegeben45,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BR16" s="13">
+      <c r="BS16" s="13">
         <f>COUNTIF(nichtFreigegeben46,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BS16" s="13">
+      <c r="BT16" s="13">
         <f>COUNTIF(nichtFreigegeben47,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BT16" s="13">
+      <c r="BU16" s="13">
         <f>COUNTIF(nichtFreigegeben48,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BU16" s="13">
+      <c r="BV16" s="13">
         <f>COUNTIF(nichtFreigegeben49,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BV16" s="13">
+      <c r="BW16" s="13">
         <f>COUNTIF(nichtFreigegeben50,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BW16" s="13">
+      <c r="BX16" s="13">
         <f>COUNTIF(nichtFreigegeben51,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BX16" s="13">
+      <c r="BY16" s="13">
         <f>COUNTIF(nichtFreigegeben52,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BY16" s="13">
+      <c r="BZ16" s="13">
         <f>COUNTIF(nichtFreigegeben53,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="BZ16" s="13">
+      <c r="CA16" s="13">
         <f>COUNTIF(nichtFreigegeben54,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CA16" s="13">
+      <c r="CB16" s="13">
         <f>COUNTIF(nichtFreigegeben55,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CB16" s="13">
+      <c r="CC16" s="13">
         <f>COUNTIF(nichtFreigegeben56,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CC16" s="13">
+      <c r="CD16" s="13">
         <f>COUNTIF(nichtFreigegeben57,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CD16" s="13">
+      <c r="CE16" s="13">
         <f>COUNTIF(nichtFreigegeben58,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CE16" s="13">
+      <c r="CF16" s="13">
         <f>COUNTIF(nichtFreigegeben59,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CF16" s="13">
+      <c r="CG16" s="13">
         <f>COUNTIF(nichtFreigegeben60,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CG16" s="28"/>
       <c r="CH16" s="28"/>
-      <c r="CI16" s="13">
+      <c r="CI16" s="28"/>
+      <c r="CJ16" s="13">
         <f>COUNTIF(nichtFreigegeben61,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CJ16" s="13">
+      <c r="CK16" s="13">
         <f>COUNTIF(nichtFreigegeben62,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CK16" s="13">
+      <c r="CL16" s="13">
         <f>COUNTIF(nichtFreigegeben63,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CL16" s="13">
+      <c r="CM16" s="13">
         <f>COUNTIF(nichtFreigegeben64,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CM16" s="13">
+      <c r="CN16" s="13">
         <f>COUNTIF(nichtFreigegeben65,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CN16" s="13">
+      <c r="CO16" s="13">
         <f>COUNTIF(nichtFreigegeben66,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CO16" s="13">
+      <c r="CP16" s="13">
         <f>COUNTIF(nichtFreigegeben67,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CP16" s="13">
+      <c r="CQ16" s="13">
         <f>COUNTIF(nichtFreigegeben68,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CQ16" s="13">
+      <c r="CR16" s="13">
         <f>COUNTIF(nichtFreigegeben69,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CR16" s="13">
+      <c r="CS16" s="13">
         <f>COUNTIF(nichtFreigegeben70,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CS16" s="13">
+      <c r="CT16" s="13">
         <f>COUNTIF(nichtFreigegeben71,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CT16" s="13">
+      <c r="CU16" s="13">
         <f>COUNTIF(nichtFreigegeben72,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CU16" s="13">
+      <c r="CV16" s="13">
         <f>COUNTIF(nichtFreigegeben73,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CV16" s="13">
+      <c r="CW16" s="13">
         <f>COUNTIF(nichtFreigegeben74,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CW16" s="13">
+      <c r="CX16" s="13">
         <f>COUNTIF(nichtFreigegeben75,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CX16" s="13">
+      <c r="CY16" s="13">
         <f>COUNTIF(nichtFreigegeben76,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CY16" s="13">
+      <c r="CZ16" s="13">
         <f>COUNTIF(nichtFreigegeben77,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="CZ16" s="13">
+      <c r="DA16" s="13">
         <f>COUNTIF(nichtFreigegeben78,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DA16" s="13">
+      <c r="DB16" s="13">
         <f>COUNTIF(nichtFreigegeben79,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DB16" s="13">
+      <c r="DC16" s="13">
         <f>COUNTIF(nichtFreigegeben80,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DC16" s="28"/>
       <c r="DD16" s="28"/>
-      <c r="DE16" s="13">
+      <c r="DE16" s="28"/>
+      <c r="DF16" s="13">
         <f>COUNTIF(nichtFreigegeben81,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DF16" s="13">
+      <c r="DG16" s="13">
         <f>COUNTIF(nichtFreigegeben82,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DG16" s="13">
+      <c r="DH16" s="13">
         <f>COUNTIF(nichtFreigegeben83,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DH16" s="13">
+      <c r="DI16" s="13">
         <f>COUNTIF(nichtFreigegeben84,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DI16" s="13">
+      <c r="DJ16" s="13">
         <f>COUNTIF(nichtFreigegeben85,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DJ16" s="13">
+      <c r="DK16" s="13">
         <f>COUNTIF(nichtFreigegeben86,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DK16" s="13">
+      <c r="DL16" s="13">
         <f>COUNTIF(nichtFreigegeben87,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DL16" s="13">
+      <c r="DM16" s="13">
         <f>COUNTIF(nichtFreigegeben88,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DM16" s="13">
+      <c r="DN16" s="13">
         <f>COUNTIF(nichtFreigegeben89,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DN16" s="13">
+      <c r="DO16" s="13">
         <f>COUNTIF(nichtFreigegeben90,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DO16" s="13">
+      <c r="DP16" s="13">
         <f>COUNTIF(nichtFreigegeben91,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DP16" s="13">
+      <c r="DQ16" s="13">
         <f>COUNTIF(nichtFreigegeben92,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DQ16" s="13">
+      <c r="DR16" s="13">
         <f>COUNTIF(nichtFreigegeben93,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DR16" s="13">
+      <c r="DS16" s="13">
         <f>COUNTIF(nichtFreigegeben94,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DS16" s="13">
+      <c r="DT16" s="13">
         <f>COUNTIF(nichtFreigegeben95,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DT16" s="13">
+      <c r="DU16" s="13">
         <f>COUNTIF(nichtFreigegeben96,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DU16" s="13">
+      <c r="DV16" s="13">
         <f>COUNTIF(nichtFreigegeben97,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DV16" s="13">
+      <c r="DW16" s="13">
         <f>COUNTIF(nichtFreigegeben98,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DW16" s="13">
+      <c r="DX16" s="13">
         <f>COUNTIF(nichtFreigegeben99,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DX16" s="13">
+      <c r="DY16" s="13">
         <f>COUNTIF(nichtFreigegeben100,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="DY16" s="28"/>
       <c r="DZ16" s="28"/>
-      <c r="EA16" s="25"/>
-      <c r="EB16" s="38"/>
+      <c r="EA16" s="28"/>
+      <c r="EB16" s="25"/>
       <c r="EC16" s="38"/>
-      <c r="ED16" s="25"/>
-      <c r="EE16" s="38"/>
-      <c r="EF16" s="36"/>
+      <c r="ED16" s="38"/>
+      <c r="EE16" s="25"/>
+      <c r="EF16" s="38"/>
+      <c r="EG16" s="36"/>
     </row>
-    <row r="17" spans="1:132" x14ac:dyDescent="0.25">
-      <c r="AO17" s="29"/>
+    <row r="17" spans="1:133" x14ac:dyDescent="0.25">
       <c r="AP17" s="29"/>
-      <c r="BK17" s="29"/>
+      <c r="AQ17" s="29"/>
       <c r="BL17" s="29"/>
-      <c r="CG17" s="29"/>
+      <c r="BM17" s="29"/>
       <c r="CH17" s="29"/>
-      <c r="DC17" s="29"/>
+      <c r="CI17" s="29"/>
       <c r="DD17" s="29"/>
-      <c r="DY17" s="29"/>
+      <c r="DE17" s="29"/>
       <c r="DZ17" s="29"/>
       <c r="EA17" s="29"/>
       <c r="EB17" s="29"/>
+      <c r="EC17" s="29"/>
     </row>
-    <row r="18" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -5970,7 +6009,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5979,7 +6018,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="20" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -5988,7 +6027,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="21" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -5997,7 +6036,7 @@
         <v>ABGELEHNT</v>
       </c>
     </row>
-    <row r="22" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -6006,7 +6045,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="23" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -6015,7 +6054,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="24" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -6024,7 +6063,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="25" spans="1:132" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -6033,7 +6072,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="26" spans="1:132" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -6042,7 +6081,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="27" spans="1:132" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -6051,7 +6090,7 @@
         <v>ABGELEHNT</v>
       </c>
     </row>
-    <row r="28" spans="1:132" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -6060,7 +6099,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="29" spans="1:132" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -6069,8 +6108,8 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="30" spans="1:132" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:132" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:133" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -6078,7 +6117,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:132" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -6103,11 +6142,11 @@
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="57" t="s">
+      <c r="A36" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="58"/>
-      <c r="C36" s="59"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="95"/>
       <c r="D36" s="49"/>
       <c r="E36" s="49"/>
       <c r="F36" s="49"/>
@@ -6116,10 +6155,10 @@
       <c r="A37" s="22">
         <v>1</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="B37" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="63"/>
+      <c r="C37" s="96"/>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
@@ -6138,10 +6177,10 @@
       <c r="A38" s="22">
         <v>2</v>
       </c>
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="96" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="63"/>
+      <c r="C38" s="96"/>
       <c r="D38" s="34"/>
       <c r="E38" s="34"/>
       <c r="F38" s="34"/>
@@ -6160,10 +6199,10 @@
       <c r="A39" s="22">
         <v>3</v>
       </c>
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="63"/>
+      <c r="C39" s="96"/>
       <c r="D39" s="34"/>
       <c r="E39" s="34"/>
       <c r="F39" s="34"/>
@@ -6180,29 +6219,22 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="D7:F8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="EE15:EF15"/>
-    <mergeCell ref="EE7:EF10"/>
-    <mergeCell ref="EA7:EB7"/>
-    <mergeCell ref="EA8:EA10"/>
-    <mergeCell ref="EB8:EB10"/>
-    <mergeCell ref="ED7:ED10"/>
-    <mergeCell ref="EE11:EF11"/>
-    <mergeCell ref="DC8:DC10"/>
-    <mergeCell ref="DD8:DD10"/>
-    <mergeCell ref="DY8:DY10"/>
-    <mergeCell ref="DZ8:DZ10"/>
-    <mergeCell ref="DE7:DZ7"/>
-    <mergeCell ref="CI7:DD7"/>
-    <mergeCell ref="G7:K8"/>
-    <mergeCell ref="L7:P8"/>
-    <mergeCell ref="S7:S10"/>
-    <mergeCell ref="Q7:Q10"/>
-    <mergeCell ref="R7:R10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="AR7:BM7"/>
+    <mergeCell ref="BN7:CI7"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="BL8:BL10"/>
+    <mergeCell ref="BM8:BM10"/>
+    <mergeCell ref="CH8:CH10"/>
+    <mergeCell ref="CI8:CI10"/>
+    <mergeCell ref="AP8:AP10"/>
+    <mergeCell ref="AQ8:AQ10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="V7:AQ7"/>
+    <mergeCell ref="A16:R16"/>
+    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="A7:C8"/>
     <mergeCell ref="A13:R13"/>
     <mergeCell ref="A14:R14"/>
     <mergeCell ref="A9:A10"/>
@@ -6217,22 +6249,29 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="AQ7:BL7"/>
-    <mergeCell ref="BM7:CH7"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="BK8:BK10"/>
-    <mergeCell ref="BL8:BL10"/>
-    <mergeCell ref="CG8:CG10"/>
-    <mergeCell ref="CH8:CH10"/>
-    <mergeCell ref="AO8:AO10"/>
-    <mergeCell ref="AP8:AP10"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="U7:AP7"/>
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="A12:R12"/>
-    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="L7:P8"/>
+    <mergeCell ref="S7:S10"/>
+    <mergeCell ref="Q7:Q10"/>
+    <mergeCell ref="R7:R10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="EF15:EG15"/>
+    <mergeCell ref="EF7:EG10"/>
+    <mergeCell ref="EB7:EC7"/>
+    <mergeCell ref="EB8:EB10"/>
+    <mergeCell ref="EC8:EC10"/>
+    <mergeCell ref="EE7:EE10"/>
+    <mergeCell ref="EF11:EG11"/>
+    <mergeCell ref="DD8:DD10"/>
+    <mergeCell ref="DE8:DE10"/>
+    <mergeCell ref="DZ8:DZ10"/>
+    <mergeCell ref="EA8:EA10"/>
+    <mergeCell ref="DF7:EA7"/>
+    <mergeCell ref="CJ7:DE7"/>
+    <mergeCell ref="G7:K8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" r:id="rId1"/>

--- a/ebegu-server/src/main/resources/reporting/TagesschuleAnmeldungen.xlsx
+++ b/ebegu-server/src/main/resources/reporting/TagesschuleAnmeldungen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aese\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederic.nell/IdeaProjects/kibon-app/ebegu-server/src/main/resources/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C554214-8E04-4432-AE4F-0B2C48C31FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A327E1-8698-A74C-8BE6-5F940C8FC193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19940" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="94">
   <si>
     <t>{statusTitle}</t>
   </si>
@@ -412,17 +412,6 @@
     <t>{verpflegungskosten}</t>
   </si>
   <si>
-    <t>Woche</t>
-  </si>
-  <si>
-    <t>Summe
-Stunden</t>
-  </si>
-  <si>
-    <t>Summe
-Verpflegung</t>
-  </si>
-  <si>
     <t>{legendeVolleKosten}</t>
   </si>
   <si>
@@ -550,6 +539,9 @@
   </si>
   <si>
     <t>{planKlasseTitle}</t>
+  </si>
+  <si>
+    <t>{woche}</t>
   </si>
 </sst>
 </file>
@@ -953,112 +945,112 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{4D11B231-AAE6-44F9-843C-66A0D70C5328}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1433,28 +1425,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:EH39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="20.7109375"/>
-    <col min="3" max="16" width="17.42578125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="20.6640625"/>
+    <col min="3" max="16" width="17.5" style="1" customWidth="1"/>
     <col min="17" max="18" width="17"/>
-    <col min="19" max="20" width="33.140625" customWidth="1"/>
-    <col min="21" max="21" width="33.140625" hidden="1" customWidth="1"/>
-    <col min="22" max="26" width="13.28515625" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" customWidth="1"/>
-    <col min="28" max="41" width="10.42578125"/>
-    <col min="44" max="63" width="10.42578125"/>
-    <col min="66" max="85" width="10.42578125"/>
-    <col min="88" max="107" width="10.42578125"/>
-    <col min="110" max="128" width="10.42578125"/>
+    <col min="19" max="20" width="33.1640625" customWidth="1"/>
+    <col min="21" max="21" width="33.1640625" hidden="1" customWidth="1"/>
+    <col min="22" max="26" width="13.33203125" customWidth="1"/>
+    <col min="27" max="27" width="13.5" customWidth="1"/>
+    <col min="28" max="41" width="10.5"/>
+    <col min="44" max="63" width="10.5"/>
+    <col min="66" max="85" width="10.5"/>
+    <col min="88" max="107" width="10.5"/>
+    <col min="110" max="128" width="10.5"/>
     <col min="129" max="129" width="10" customWidth="1"/>
-    <col min="132" max="133" width="10.42578125"/>
+    <col min="132" max="133" width="10.5"/>
     <col min="134" max="134" width="50" customWidth="1"/>
-    <col min="135" max="135" width="22.7109375" customWidth="1"/>
-    <col min="138" max="994" width="10.42578125"/>
+    <col min="135" max="135" width="22.6640625" customWidth="1"/>
+    <col min="138" max="994" width="10.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:138" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:138" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1484,7 +1476,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1514,7 +1506,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -1542,7 +1534,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -1570,7 +1562,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:138" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:138" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>47</v>
       </c>
@@ -1707,7 +1699,7 @@
       <c r="DZ5" s="2"/>
       <c r="EA5" s="2"/>
     </row>
-    <row r="6" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
@@ -2023,200 +2015,200 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="63"/>
-      <c r="L7" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="63"/>
-      <c r="Q7" s="67" t="s">
+    <row r="7" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="73"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="72" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="R7" s="67" t="s">
-        <v>57</v>
-      </c>
-      <c r="S7" s="67" t="s">
+      <c r="R7" s="78" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7" s="78" t="s">
         <v>0</v>
       </c>
       <c r="T7" s="57" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="U7" s="14"/>
-      <c r="V7" s="87" t="s">
+      <c r="V7" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="W7" s="88"/>
-      <c r="X7" s="88"/>
-      <c r="Y7" s="88"/>
-      <c r="Z7" s="88"/>
-      <c r="AA7" s="88"/>
-      <c r="AB7" s="88"/>
-      <c r="AC7" s="88"/>
-      <c r="AD7" s="88"/>
-      <c r="AE7" s="88"/>
-      <c r="AF7" s="88"/>
-      <c r="AG7" s="88"/>
-      <c r="AH7" s="88"/>
-      <c r="AI7" s="88"/>
-      <c r="AJ7" s="88"/>
-      <c r="AK7" s="88"/>
-      <c r="AL7" s="88"/>
-      <c r="AM7" s="88"/>
-      <c r="AN7" s="88"/>
-      <c r="AO7" s="88"/>
-      <c r="AP7" s="88"/>
-      <c r="AQ7" s="89"/>
-      <c r="AR7" s="87" t="s">
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="65"/>
+      <c r="AE7" s="65"/>
+      <c r="AF7" s="65"/>
+      <c r="AG7" s="65"/>
+      <c r="AH7" s="65"/>
+      <c r="AI7" s="65"/>
+      <c r="AJ7" s="65"/>
+      <c r="AK7" s="65"/>
+      <c r="AL7" s="65"/>
+      <c r="AM7" s="65"/>
+      <c r="AN7" s="65"/>
+      <c r="AO7" s="65"/>
+      <c r="AP7" s="65"/>
+      <c r="AQ7" s="66"/>
+      <c r="AR7" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="AS7" s="88"/>
-      <c r="AT7" s="88"/>
-      <c r="AU7" s="88"/>
-      <c r="AV7" s="88"/>
-      <c r="AW7" s="88"/>
-      <c r="AX7" s="88"/>
-      <c r="AY7" s="88"/>
-      <c r="AZ7" s="88"/>
-      <c r="BA7" s="88"/>
-      <c r="BB7" s="88"/>
-      <c r="BC7" s="88"/>
-      <c r="BD7" s="88"/>
-      <c r="BE7" s="88"/>
-      <c r="BF7" s="88"/>
-      <c r="BG7" s="88"/>
-      <c r="BH7" s="88"/>
-      <c r="BI7" s="88"/>
-      <c r="BJ7" s="88"/>
-      <c r="BK7" s="88"/>
-      <c r="BL7" s="88"/>
-      <c r="BM7" s="89"/>
-      <c r="BN7" s="87" t="s">
+      <c r="AS7" s="65"/>
+      <c r="AT7" s="65"/>
+      <c r="AU7" s="65"/>
+      <c r="AV7" s="65"/>
+      <c r="AW7" s="65"/>
+      <c r="AX7" s="65"/>
+      <c r="AY7" s="65"/>
+      <c r="AZ7" s="65"/>
+      <c r="BA7" s="65"/>
+      <c r="BB7" s="65"/>
+      <c r="BC7" s="65"/>
+      <c r="BD7" s="65"/>
+      <c r="BE7" s="65"/>
+      <c r="BF7" s="65"/>
+      <c r="BG7" s="65"/>
+      <c r="BH7" s="65"/>
+      <c r="BI7" s="65"/>
+      <c r="BJ7" s="65"/>
+      <c r="BK7" s="65"/>
+      <c r="BL7" s="65"/>
+      <c r="BM7" s="66"/>
+      <c r="BN7" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="BO7" s="88"/>
-      <c r="BP7" s="88"/>
-      <c r="BQ7" s="88"/>
-      <c r="BR7" s="88"/>
-      <c r="BS7" s="88"/>
-      <c r="BT7" s="88"/>
-      <c r="BU7" s="88"/>
-      <c r="BV7" s="88"/>
-      <c r="BW7" s="88"/>
-      <c r="BX7" s="88"/>
-      <c r="BY7" s="88"/>
-      <c r="BZ7" s="88"/>
-      <c r="CA7" s="88"/>
-      <c r="CB7" s="88"/>
-      <c r="CC7" s="88"/>
-      <c r="CD7" s="88"/>
-      <c r="CE7" s="88"/>
-      <c r="CF7" s="88"/>
-      <c r="CG7" s="88"/>
-      <c r="CH7" s="88"/>
-      <c r="CI7" s="89"/>
-      <c r="CJ7" s="87" t="s">
+      <c r="BO7" s="65"/>
+      <c r="BP7" s="65"/>
+      <c r="BQ7" s="65"/>
+      <c r="BR7" s="65"/>
+      <c r="BS7" s="65"/>
+      <c r="BT7" s="65"/>
+      <c r="BU7" s="65"/>
+      <c r="BV7" s="65"/>
+      <c r="BW7" s="65"/>
+      <c r="BX7" s="65"/>
+      <c r="BY7" s="65"/>
+      <c r="BZ7" s="65"/>
+      <c r="CA7" s="65"/>
+      <c r="CB7" s="65"/>
+      <c r="CC7" s="65"/>
+      <c r="CD7" s="65"/>
+      <c r="CE7" s="65"/>
+      <c r="CF7" s="65"/>
+      <c r="CG7" s="65"/>
+      <c r="CH7" s="65"/>
+      <c r="CI7" s="66"/>
+      <c r="CJ7" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="CK7" s="88"/>
-      <c r="CL7" s="88"/>
-      <c r="CM7" s="88"/>
-      <c r="CN7" s="88"/>
-      <c r="CO7" s="88"/>
-      <c r="CP7" s="88"/>
-      <c r="CQ7" s="88"/>
-      <c r="CR7" s="88"/>
-      <c r="CS7" s="88"/>
-      <c r="CT7" s="88"/>
-      <c r="CU7" s="88"/>
-      <c r="CV7" s="88"/>
-      <c r="CW7" s="88"/>
-      <c r="CX7" s="88"/>
-      <c r="CY7" s="88"/>
-      <c r="CZ7" s="88"/>
-      <c r="DA7" s="88"/>
-      <c r="DB7" s="88"/>
-      <c r="DC7" s="88"/>
-      <c r="DD7" s="88"/>
-      <c r="DE7" s="89"/>
-      <c r="DF7" s="87" t="s">
+      <c r="CK7" s="65"/>
+      <c r="CL7" s="65"/>
+      <c r="CM7" s="65"/>
+      <c r="CN7" s="65"/>
+      <c r="CO7" s="65"/>
+      <c r="CP7" s="65"/>
+      <c r="CQ7" s="65"/>
+      <c r="CR7" s="65"/>
+      <c r="CS7" s="65"/>
+      <c r="CT7" s="65"/>
+      <c r="CU7" s="65"/>
+      <c r="CV7" s="65"/>
+      <c r="CW7" s="65"/>
+      <c r="CX7" s="65"/>
+      <c r="CY7" s="65"/>
+      <c r="CZ7" s="65"/>
+      <c r="DA7" s="65"/>
+      <c r="DB7" s="65"/>
+      <c r="DC7" s="65"/>
+      <c r="DD7" s="65"/>
+      <c r="DE7" s="66"/>
+      <c r="DF7" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="DG7" s="88"/>
-      <c r="DH7" s="88"/>
-      <c r="DI7" s="88"/>
-      <c r="DJ7" s="88"/>
-      <c r="DK7" s="88"/>
-      <c r="DL7" s="88"/>
-      <c r="DM7" s="88"/>
-      <c r="DN7" s="88"/>
-      <c r="DO7" s="88"/>
-      <c r="DP7" s="88"/>
-      <c r="DQ7" s="88"/>
-      <c r="DR7" s="88"/>
-      <c r="DS7" s="88"/>
-      <c r="DT7" s="88"/>
-      <c r="DU7" s="88"/>
-      <c r="DV7" s="88"/>
-      <c r="DW7" s="88"/>
-      <c r="DX7" s="88"/>
-      <c r="DY7" s="88"/>
-      <c r="DZ7" s="88"/>
-      <c r="EA7" s="89"/>
-      <c r="EB7" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="EC7" s="77"/>
+      <c r="DG7" s="65"/>
+      <c r="DH7" s="65"/>
+      <c r="DI7" s="65"/>
+      <c r="DJ7" s="65"/>
+      <c r="DK7" s="65"/>
+      <c r="DL7" s="65"/>
+      <c r="DM7" s="65"/>
+      <c r="DN7" s="65"/>
+      <c r="DO7" s="65"/>
+      <c r="DP7" s="65"/>
+      <c r="DQ7" s="65"/>
+      <c r="DR7" s="65"/>
+      <c r="DS7" s="65"/>
+      <c r="DT7" s="65"/>
+      <c r="DU7" s="65"/>
+      <c r="DV7" s="65"/>
+      <c r="DW7" s="65"/>
+      <c r="DX7" s="65"/>
+      <c r="DY7" s="65"/>
+      <c r="DZ7" s="65"/>
+      <c r="EA7" s="66"/>
+      <c r="EB7" s="92" t="s">
+        <v>93</v>
+      </c>
+      <c r="EC7" s="92"/>
       <c r="ED7" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="EE7" s="80" t="s">
-        <v>79</v>
-      </c>
-      <c r="EF7" s="71" t="s">
-        <v>78</v>
-      </c>
-      <c r="EG7" s="72"/>
+        <v>89</v>
+      </c>
+      <c r="EE7" s="93" t="s">
+        <v>76</v>
+      </c>
+      <c r="EF7" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="EG7" s="87"/>
       <c r="EH7" s="11"/>
     </row>
-    <row r="8" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="91"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="79"/>
-      <c r="R8" s="79"/>
-      <c r="S8" s="79"/>
+    <row r="8" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="75"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
       <c r="T8" s="59"/>
       <c r="U8" s="15"/>
       <c r="V8" s="4" t="s">
@@ -2279,10 +2271,10 @@
       <c r="AO8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AP8" s="78" t="s">
+      <c r="AP8" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="AQ8" s="78" t="s">
+      <c r="AQ8" s="68" t="s">
         <v>45</v>
       </c>
       <c r="AR8" s="4" t="s">
@@ -2345,10 +2337,10 @@
       <c r="BK8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BL8" s="78" t="s">
+      <c r="BL8" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="BM8" s="78" t="s">
+      <c r="BM8" s="68" t="s">
         <v>45</v>
       </c>
       <c r="BN8" s="4" t="s">
@@ -2411,10 +2403,10 @@
       <c r="CG8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="CH8" s="78" t="s">
+      <c r="CH8" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="CI8" s="78" t="s">
+      <c r="CI8" s="68" t="s">
         <v>45</v>
       </c>
       <c r="CJ8" s="4" t="s">
@@ -2477,10 +2469,10 @@
       <c r="DC8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="DD8" s="78" t="s">
+      <c r="DD8" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="DE8" s="78" t="s">
+      <c r="DE8" s="68" t="s">
         <v>45</v>
       </c>
       <c r="DF8" s="4" t="s">
@@ -2543,75 +2535,75 @@
       <c r="DY8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="DZ8" s="78" t="s">
+      <c r="DZ8" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="EA8" s="78" t="s">
+      <c r="EA8" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="EB8" s="78" t="s">
-        <v>51</v>
-      </c>
-      <c r="EC8" s="78" t="s">
-        <v>52</v>
+      <c r="EB8" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="EC8" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="ED8" s="53"/>
-      <c r="EE8" s="81"/>
-      <c r="EF8" s="73"/>
-      <c r="EG8" s="74"/>
+      <c r="EE8" s="94"/>
+      <c r="EF8" s="88"/>
+      <c r="EG8" s="89"/>
     </row>
-    <row r="9" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="67" t="s">
+    <row r="9" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="67" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="67" t="s">
+      <c r="J9" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="67" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="67" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="O9" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="P9" s="67" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="79"/>
-      <c r="R9" s="79"/>
-      <c r="S9" s="79"/>
+      <c r="O9" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
       <c r="T9" s="59"/>
       <c r="U9" s="15"/>
       <c r="V9" s="32" t="s">
@@ -2674,8 +2666,8 @@
       <c r="AO9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="AP9" s="85"/>
-      <c r="AQ9" s="85"/>
+      <c r="AP9" s="69"/>
+      <c r="AQ9" s="69"/>
       <c r="AR9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2736,8 +2728,8 @@
       <c r="BK9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="BL9" s="85"/>
-      <c r="BM9" s="85"/>
+      <c r="BL9" s="69"/>
+      <c r="BM9" s="69"/>
       <c r="BN9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2798,8 +2790,8 @@
       <c r="CG9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="CH9" s="85"/>
-      <c r="CI9" s="85"/>
+      <c r="CH9" s="69"/>
+      <c r="CI9" s="69"/>
       <c r="CJ9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2860,8 +2852,8 @@
       <c r="DC9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="DD9" s="85"/>
-      <c r="DE9" s="85"/>
+      <c r="DD9" s="69"/>
+      <c r="DE9" s="69"/>
       <c r="DF9" s="32" t="s">
         <v>46</v>
       </c>
@@ -2922,35 +2914,35 @@
       <c r="DY9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="DZ9" s="85"/>
-      <c r="EA9" s="85"/>
-      <c r="EB9" s="79"/>
-      <c r="EC9" s="79"/>
+      <c r="DZ9" s="69"/>
+      <c r="EA9" s="69"/>
+      <c r="EB9" s="69"/>
+      <c r="EC9" s="69"/>
       <c r="ED9" s="51"/>
-      <c r="EE9" s="81"/>
-      <c r="EF9" s="73"/>
-      <c r="EG9" s="74"/>
+      <c r="EE9" s="94"/>
+      <c r="EF9" s="88"/>
+      <c r="EG9" s="89"/>
     </row>
-    <row r="10" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="68"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="68"/>
-      <c r="Q10" s="68"/>
-      <c r="R10" s="68"/>
-      <c r="S10" s="68"/>
+    <row r="10" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="79"/>
+      <c r="B10" s="79"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="79"/>
+      <c r="O10" s="79"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="79"/>
+      <c r="R10" s="79"/>
+      <c r="S10" s="79"/>
       <c r="T10" s="58"/>
       <c r="U10" s="15"/>
       <c r="V10" s="16" t="s">
@@ -3013,8 +3005,8 @@
       <c r="AO10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="AP10" s="86"/>
-      <c r="AQ10" s="86"/>
+      <c r="AP10" s="70"/>
+      <c r="AQ10" s="70"/>
       <c r="AR10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3075,8 +3067,8 @@
       <c r="BK10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="BL10" s="86"/>
-      <c r="BM10" s="86"/>
+      <c r="BL10" s="70"/>
+      <c r="BM10" s="70"/>
       <c r="BN10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3137,8 +3129,8 @@
       <c r="CG10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="CH10" s="86"/>
-      <c r="CI10" s="86"/>
+      <c r="CH10" s="70"/>
+      <c r="CI10" s="70"/>
       <c r="CJ10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3199,8 +3191,8 @@
       <c r="DC10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="DD10" s="86"/>
-      <c r="DE10" s="86"/>
+      <c r="DD10" s="70"/>
+      <c r="DE10" s="70"/>
       <c r="DF10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3261,16 +3253,16 @@
       <c r="DY10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="DZ10" s="86"/>
-      <c r="EA10" s="86"/>
-      <c r="EB10" s="68"/>
-      <c r="EC10" s="68"/>
+      <c r="DZ10" s="70"/>
+      <c r="EA10" s="70"/>
+      <c r="EB10" s="70"/>
+      <c r="EC10" s="70"/>
       <c r="ED10" s="50"/>
-      <c r="EE10" s="82"/>
-      <c r="EF10" s="75"/>
-      <c r="EG10" s="76"/>
+      <c r="EE10" s="95"/>
+      <c r="EF10" s="90"/>
+      <c r="EG10" s="91"/>
     </row>
-    <row r="11" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>2</v>
       </c>
@@ -3281,55 +3273,55 @@
         <v>4</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="M11" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="N11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="O11" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="Q11" s="7" t="s">
         <v>3</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U11" s="6" t="e">
         <f>VLOOKUP(S11,$A$18:$B$29,2,FALSE)</f>
@@ -3699,40 +3691,40 @@
         <v>0</v>
       </c>
       <c r="ED11" s="21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="EE11" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="EF11" s="83" t="s">
         <v>77</v>
       </c>
-      <c r="EG11" s="84"/>
+      <c r="EF11" s="96" t="s">
+        <v>74</v>
+      </c>
+      <c r="EG11" s="97"/>
       <c r="EH11" s="35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:138" x14ac:dyDescent="0.25">
-      <c r="A12" s="93" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="94"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="95"/>
+    <row r="12" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A12" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62"/>
+      <c r="Q12" s="62"/>
+      <c r="R12" s="63"/>
       <c r="S12" s="13">
         <f>COUNTIF(statusKategorie,$B$33)</f>
         <v>0</v>
@@ -4192,27 +4184,27 @@
       <c r="EF12" s="39"/>
       <c r="EG12" s="40"/>
     </row>
-    <row r="13" spans="1:138" x14ac:dyDescent="0.25">
-      <c r="A13" s="93" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="95"/>
+    <row r="13" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A13" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="62"/>
+      <c r="R13" s="63"/>
       <c r="S13" s="13">
         <f>COUNTIF(statusKategorie,$B$32)</f>
         <v>0</v>
@@ -4672,27 +4664,27 @@
       <c r="EF13" s="28"/>
       <c r="EG13" s="44"/>
     </row>
-    <row r="14" spans="1:138" x14ac:dyDescent="0.25">
-      <c r="A14" s="93" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="94"/>
-      <c r="N14" s="94"/>
-      <c r="O14" s="94"/>
-      <c r="P14" s="94"/>
-      <c r="Q14" s="94"/>
-      <c r="R14" s="95"/>
+    <row r="14" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A14" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="63"/>
       <c r="S14" s="13">
         <f>COUNTIF(statusKategorie,$B$31)</f>
         <v>0</v>
@@ -5152,7 +5144,7 @@
       <c r="EF14" s="38"/>
       <c r="EG14" s="36"/>
     </row>
-    <row r="15" spans="1:138" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:138" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>2</v>
       </c>
@@ -5163,55 +5155,55 @@
         <v>4</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="M15" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="N15" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="O15" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>3</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>5</v>
       </c>
       <c r="T15" s="60" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U15" s="6" t="e">
         <f>VLOOKUP(S15,$A$18:$B$29,2,FALSE)</f>
@@ -5530,40 +5522,40 @@
       <c r="EB15" s="30"/>
       <c r="EC15" s="37"/>
       <c r="ED15" s="56" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="EE15" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="EF15" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="EG15" s="70"/>
+      <c r="EF15" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="EG15" s="85"/>
       <c r="EH15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:138" x14ac:dyDescent="0.25">
-      <c r="A16" s="97" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="97"/>
-      <c r="F16" s="97"/>
-      <c r="G16" s="97"/>
-      <c r="H16" s="97"/>
-      <c r="I16" s="97"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="97"/>
-      <c r="M16" s="97"/>
-      <c r="N16" s="97"/>
-      <c r="O16" s="97"/>
-      <c r="P16" s="97"/>
-      <c r="Q16" s="97"/>
-      <c r="R16" s="97"/>
+    <row r="16" spans="1:138" x14ac:dyDescent="0.2">
+      <c r="A16" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
       <c r="S16" s="13">
         <f>COUNTIF(freigegebenKategorie,$B$34)</f>
         <v>0</v>
@@ -5987,7 +5979,7 @@
       <c r="EF16" s="38"/>
       <c r="EG16" s="36"/>
     </row>
-    <row r="17" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:133" x14ac:dyDescent="0.2">
       <c r="AP17" s="29"/>
       <c r="AQ17" s="29"/>
       <c r="BL17" s="29"/>
@@ -6001,7 +5993,7 @@
       <c r="EB17" s="29"/>
       <c r="EC17" s="29"/>
     </row>
-    <row r="18" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -6009,7 +6001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -6018,7 +6010,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="20" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -6027,7 +6019,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="21" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -6036,7 +6028,7 @@
         <v>ABGELEHNT</v>
       </c>
     </row>
-    <row r="22" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -6045,7 +6037,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="23" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -6054,7 +6046,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="24" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -6063,7 +6055,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="25" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -6072,7 +6064,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="26" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -6081,7 +6073,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="27" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -6090,7 +6082,7 @@
         <v>ABGELEHNT</v>
       </c>
     </row>
-    <row r="28" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -6099,7 +6091,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="29" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -6108,8 +6100,8 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="30" spans="1:133" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:133" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -6117,7 +6109,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:133" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -6125,7 +6117,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -6133,7 +6125,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -6141,24 +6133,24 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="93" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="94"/>
-      <c r="C36" s="95"/>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="62"/>
+      <c r="C36" s="63"/>
       <c r="D36" s="49"/>
       <c r="E36" s="49"/>
       <c r="F36" s="49"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>1</v>
       </c>
-      <c r="B37" s="96" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="96"/>
+      <c r="B37" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="67"/>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
@@ -6173,14 +6165,14 @@
       <c r="O37" s="34"/>
       <c r="P37" s="34"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>2</v>
       </c>
-      <c r="B38" s="96" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="96"/>
+      <c r="B38" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="67"/>
       <c r="D38" s="34"/>
       <c r="E38" s="34"/>
       <c r="F38" s="34"/>
@@ -6195,14 +6187,14 @@
       <c r="O38" s="34"/>
       <c r="P38" s="34"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>3</v>
       </c>
-      <c r="B39" s="96" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="96"/>
+      <c r="B39" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="67"/>
       <c r="D39" s="34"/>
       <c r="E39" s="34"/>
       <c r="F39" s="34"/>
@@ -6219,6 +6211,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="EF15:EG15"/>
+    <mergeCell ref="EF7:EG10"/>
+    <mergeCell ref="EB7:EC7"/>
+    <mergeCell ref="EB8:EB10"/>
+    <mergeCell ref="EC8:EC10"/>
+    <mergeCell ref="EE7:EE10"/>
+    <mergeCell ref="EF11:EG11"/>
+    <mergeCell ref="DD8:DD10"/>
+    <mergeCell ref="DE8:DE10"/>
+    <mergeCell ref="DZ8:DZ10"/>
+    <mergeCell ref="EA8:EA10"/>
+    <mergeCell ref="DF7:EA7"/>
+    <mergeCell ref="CJ7:DE7"/>
+    <mergeCell ref="G7:K8"/>
+    <mergeCell ref="L7:P8"/>
+    <mergeCell ref="S7:S10"/>
+    <mergeCell ref="Q7:Q10"/>
+    <mergeCell ref="R7:R10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="A13:R13"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="AR7:BM7"/>
     <mergeCell ref="BN7:CI7"/>
@@ -6235,43 +6264,6 @@
     <mergeCell ref="A16:R16"/>
     <mergeCell ref="A12:R12"/>
     <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A13:R13"/>
-    <mergeCell ref="A14:R14"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L7:P8"/>
-    <mergeCell ref="S7:S10"/>
-    <mergeCell ref="Q7:Q10"/>
-    <mergeCell ref="R7:R10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="D7:F8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="EF15:EG15"/>
-    <mergeCell ref="EF7:EG10"/>
-    <mergeCell ref="EB7:EC7"/>
-    <mergeCell ref="EB8:EB10"/>
-    <mergeCell ref="EC8:EC10"/>
-    <mergeCell ref="EE7:EE10"/>
-    <mergeCell ref="EF11:EG11"/>
-    <mergeCell ref="DD8:DD10"/>
-    <mergeCell ref="DE8:DE10"/>
-    <mergeCell ref="DZ8:DZ10"/>
-    <mergeCell ref="EA8:EA10"/>
-    <mergeCell ref="DF7:EA7"/>
-    <mergeCell ref="CJ7:DE7"/>
-    <mergeCell ref="G7:K8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" r:id="rId1"/>

--- a/ebegu-server/src/main/resources/reporting/TagesschuleAnmeldungen.xlsx
+++ b/ebegu-server/src/main/resources/reporting/TagesschuleAnmeldungen.xlsx
@@ -1,246 +1,246 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederic.nell/IdeaProjects/kibon-app/ebegu-server/src/main/resources/reporting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java\kibon-app\ebegu-server\src\main\resources\reporting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A327E1-8698-A74C-8BE6-5F940C8FC193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BC2499-BE0F-46A2-9757-D8D8FE88A042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19940" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$8:$S$16</definedName>
-    <definedName name="angemeldet1">Data!$V$11</definedName>
-    <definedName name="angemeldet10">Data!$AE$11</definedName>
-    <definedName name="angemeldet100">Data!$DY$11</definedName>
-    <definedName name="angemeldet11">Data!$AF$11</definedName>
-    <definedName name="angemeldet12">Data!$AG$11</definedName>
-    <definedName name="angemeldet13">Data!$AH$11</definedName>
-    <definedName name="angemeldet14">Data!$AI$11</definedName>
-    <definedName name="angemeldet15">Data!$AJ$11</definedName>
-    <definedName name="angemeldet16">Data!$AK$11</definedName>
-    <definedName name="angemeldet17">Data!$AL$11</definedName>
-    <definedName name="angemeldet18">Data!$AM$11</definedName>
-    <definedName name="angemeldet19">Data!$AN$11</definedName>
-    <definedName name="angemeldet2">Data!$W$11</definedName>
-    <definedName name="angemeldet20">Data!$AO$11</definedName>
-    <definedName name="angemeldet21">Data!$AR$11</definedName>
-    <definedName name="angemeldet22">Data!$AS$11</definedName>
-    <definedName name="angemeldet23">Data!$AT$11</definedName>
-    <definedName name="angemeldet24">Data!$AU$11</definedName>
-    <definedName name="angemeldet25">Data!$AV$11</definedName>
-    <definedName name="angemeldet26">Data!$AW$11</definedName>
-    <definedName name="angemeldet27">Data!$AX$11</definedName>
-    <definedName name="angemeldet28">Data!$AY$11</definedName>
-    <definedName name="angemeldet29">Data!$AZ$11</definedName>
-    <definedName name="angemeldet3">Data!$X$11</definedName>
-    <definedName name="angemeldet30">Data!$BA$11</definedName>
-    <definedName name="angemeldet31">Data!$BB$11</definedName>
-    <definedName name="angemeldet32">Data!$BC$11</definedName>
-    <definedName name="angemeldet33">Data!$BD$11</definedName>
-    <definedName name="angemeldet34">Data!$BE$11</definedName>
-    <definedName name="angemeldet35">Data!$BF$11</definedName>
-    <definedName name="angemeldet36">Data!$BG$11</definedName>
-    <definedName name="angemeldet37">Data!$BH$11</definedName>
-    <definedName name="angemeldet38">Data!$BI$11</definedName>
-    <definedName name="angemeldet39">Data!$BJ$11</definedName>
-    <definedName name="angemeldet4">Data!$Y$11</definedName>
-    <definedName name="angemeldet40">Data!$BK$11</definedName>
-    <definedName name="angemeldet41">Data!$BN$11</definedName>
-    <definedName name="angemeldet42">Data!$BO$11</definedName>
-    <definedName name="angemeldet43">Data!$BP$11</definedName>
-    <definedName name="angemeldet44">Data!$BQ$11</definedName>
-    <definedName name="angemeldet45">Data!$BR$11</definedName>
-    <definedName name="angemeldet46">Data!$BS$11</definedName>
-    <definedName name="angemeldet47">Data!$BT$11</definedName>
-    <definedName name="angemeldet48">Data!$BU$11</definedName>
-    <definedName name="angemeldet49">Data!$BV$11</definedName>
-    <definedName name="angemeldet5">Data!$Z$11</definedName>
-    <definedName name="angemeldet50">Data!$BW$11</definedName>
-    <definedName name="angemeldet51">Data!$BX$11</definedName>
-    <definedName name="angemeldet52">Data!$BY$11</definedName>
-    <definedName name="angemeldet53">Data!$BZ$11</definedName>
-    <definedName name="angemeldet54">Data!$CA$11</definedName>
-    <definedName name="angemeldet55">Data!$CB$11</definedName>
-    <definedName name="angemeldet56">Data!$CC$11</definedName>
-    <definedName name="angemeldet57">Data!$CD$11</definedName>
-    <definedName name="angemeldet58">Data!$CE$11</definedName>
-    <definedName name="angemeldet59">Data!$CF$11</definedName>
-    <definedName name="angemeldet6">Data!$AA$11</definedName>
-    <definedName name="angemeldet60">Data!$CG$11</definedName>
-    <definedName name="angemeldet61">Data!$CJ$11</definedName>
-    <definedName name="angemeldet62">Data!$CK$11</definedName>
-    <definedName name="angemeldet63">Data!$CL$11</definedName>
-    <definedName name="angemeldet64">Data!$CM$11</definedName>
-    <definedName name="angemeldet65">Data!$CN$11</definedName>
-    <definedName name="angemeldet66">Data!$CO$11</definedName>
-    <definedName name="angemeldet67">Data!$CP$11</definedName>
-    <definedName name="angemeldet68">Data!$CQ$11</definedName>
-    <definedName name="angemeldet69">Data!$CR$11</definedName>
-    <definedName name="angemeldet7">Data!$AB$11</definedName>
-    <definedName name="angemeldet70">Data!$CS$11</definedName>
-    <definedName name="angemeldet71">Data!$CT$11</definedName>
-    <definedName name="angemeldet72">Data!$CU$11</definedName>
-    <definedName name="angemeldet73">Data!$CV$11</definedName>
-    <definedName name="angemeldet74">Data!$CW$11</definedName>
-    <definedName name="angemeldet75">Data!$CX$11</definedName>
-    <definedName name="angemeldet76">Data!$CY$11</definedName>
-    <definedName name="angemeldet77">Data!$CZ$11</definedName>
-    <definedName name="angemeldet78">Data!$DA$11</definedName>
-    <definedName name="angemeldet79">Data!$DB$11</definedName>
-    <definedName name="angemeldet8">Data!$AC$11</definedName>
-    <definedName name="angemeldet80">Data!$DC$11</definedName>
-    <definedName name="angemeldet81">Data!$DF$11</definedName>
-    <definedName name="angemeldet82">Data!$DG$11</definedName>
-    <definedName name="angemeldet83">Data!$DH$11</definedName>
-    <definedName name="angemeldet84">Data!$DI$11</definedName>
-    <definedName name="angemeldet85">Data!$DJ$11</definedName>
-    <definedName name="angemeldet86">Data!$DK$11</definedName>
-    <definedName name="angemeldet87">Data!$DL$11</definedName>
-    <definedName name="angemeldet88">Data!$DM$11</definedName>
-    <definedName name="angemeldet89">Data!$DN$11</definedName>
-    <definedName name="angemeldet9">Data!$AD$11</definedName>
-    <definedName name="angemeldet90">Data!$DO$11</definedName>
-    <definedName name="angemeldet91">Data!$DP$11</definedName>
-    <definedName name="angemeldet92">Data!$DQ$11</definedName>
-    <definedName name="angemeldet93">Data!$DR$11</definedName>
-    <definedName name="angemeldet94">Data!$DS$11</definedName>
-    <definedName name="angemeldet95">Data!$DT$11</definedName>
-    <definedName name="angemeldet96">Data!$DU$11</definedName>
-    <definedName name="angemeldet97">Data!$DV$11</definedName>
-    <definedName name="angemeldet98">Data!$DW$11</definedName>
-    <definedName name="angemeldet99">Data!$DX$11</definedName>
-    <definedName name="freigegebenKategorie">Data!$U$15</definedName>
-    <definedName name="nichtFreigegeben1">Data!$V$15</definedName>
-    <definedName name="nichtFreigegeben10">Data!$AE$15</definedName>
-    <definedName name="nichtFreigegeben100">Data!$DY$15</definedName>
-    <definedName name="nichtFreigegeben11">Data!$AF$15</definedName>
-    <definedName name="nichtFreigegeben12">Data!$AG$15</definedName>
-    <definedName name="nichtFreigegeben13">Data!$AH$15</definedName>
-    <definedName name="nichtFreigegeben14">Data!$AI$15</definedName>
-    <definedName name="nichtFreigegeben15">Data!$AJ$15</definedName>
-    <definedName name="nichtFreigegeben16">Data!$AK$15</definedName>
-    <definedName name="nichtFreigegeben17">Data!$AL$15</definedName>
-    <definedName name="nichtFreigegeben18">Data!$AM$15</definedName>
-    <definedName name="nichtFreigegeben19">Data!$AN$15</definedName>
-    <definedName name="nichtFreigegeben2">Data!$W$15</definedName>
-    <definedName name="nichtFreigegeben20">Data!$AO$15</definedName>
-    <definedName name="nichtFreigegeben21">Data!$AR$15</definedName>
-    <definedName name="nichtFreigegeben22">Data!$AS$15</definedName>
-    <definedName name="nichtFreigegeben23">Data!$AT$15</definedName>
-    <definedName name="nichtFreigegeben24">Data!$AU$15</definedName>
-    <definedName name="nichtFreigegeben25">Data!$AV$15</definedName>
-    <definedName name="nichtFreigegeben26">Data!$AW$15</definedName>
-    <definedName name="nichtFreigegeben27">Data!$AX$15</definedName>
-    <definedName name="nichtFreigegeben28">Data!$AY$15</definedName>
-    <definedName name="nichtFreigegeben29">Data!$AZ$15</definedName>
-    <definedName name="nichtFreigegeben3">Data!$X$15</definedName>
-    <definedName name="nichtFreigegeben30">Data!$BA$15</definedName>
-    <definedName name="nichtFreigegeben31">Data!$BB$15</definedName>
-    <definedName name="nichtFreigegeben32">Data!$BC$15</definedName>
-    <definedName name="nichtFreigegeben33">Data!$BD$15</definedName>
-    <definedName name="nichtFreigegeben34">Data!$BE$15</definedName>
-    <definedName name="nichtFreigegeben35">Data!$BF$15</definedName>
-    <definedName name="nichtFreigegeben36">Data!$BG$15</definedName>
-    <definedName name="nichtFreigegeben37">Data!$BH$15</definedName>
-    <definedName name="nichtFreigegeben38">Data!$BI$15</definedName>
-    <definedName name="nichtFreigegeben39">Data!$BJ$15</definedName>
-    <definedName name="nichtFreigegeben4">Data!$Y$15</definedName>
-    <definedName name="nichtFreigegeben40">Data!$BK$15</definedName>
-    <definedName name="nichtFreigegeben41">Data!$BN$15</definedName>
-    <definedName name="nichtFreigegeben42">Data!$BO$15</definedName>
-    <definedName name="nichtFreigegeben43">Data!$BP$15</definedName>
-    <definedName name="nichtFreigegeben44">Data!$BQ$15</definedName>
-    <definedName name="nichtFreigegeben45">Data!$BR$15</definedName>
-    <definedName name="nichtFreigegeben46">Data!$BS$15</definedName>
-    <definedName name="nichtFreigegeben47">Data!$BT$15</definedName>
-    <definedName name="nichtFreigegeben48">Data!$BU$15</definedName>
-    <definedName name="nichtFreigegeben49">Data!$BV$15</definedName>
-    <definedName name="nichtFreigegeben5">Data!$Z$15</definedName>
-    <definedName name="nichtFreigegeben50">Data!$BW$15</definedName>
-    <definedName name="nichtFreigegeben51">Data!$BX$15</definedName>
-    <definedName name="nichtFreigegeben52">Data!$BY$15</definedName>
-    <definedName name="nichtFreigegeben53">Data!$BZ$15</definedName>
-    <definedName name="nichtFreigegeben54">Data!$CA$15</definedName>
-    <definedName name="nichtFreigegeben55">Data!$CB$15</definedName>
-    <definedName name="nichtFreigegeben56">Data!$CC$15</definedName>
-    <definedName name="nichtFreigegeben57">Data!$CD$15</definedName>
-    <definedName name="nichtFreigegeben58">Data!$CE$15</definedName>
-    <definedName name="nichtFreigegeben59">Data!$CF$15</definedName>
-    <definedName name="nichtFreigegeben6">Data!$AA$15</definedName>
-    <definedName name="nichtFreigegeben60">Data!$CG$15</definedName>
-    <definedName name="nichtFreigegeben61">Data!$CJ$15</definedName>
-    <definedName name="nichtFreigegeben62">Data!$CK$15</definedName>
-    <definedName name="nichtFreigegeben63">Data!$CL$15</definedName>
-    <definedName name="nichtFreigegeben64">Data!$CM$15</definedName>
-    <definedName name="nichtFreigegeben65">Data!$CN$15</definedName>
-    <definedName name="nichtFreigegeben66">Data!$CO$15</definedName>
-    <definedName name="nichtFreigegeben67">Data!$CP$15</definedName>
-    <definedName name="nichtFreigegeben68">Data!$CQ$15</definedName>
-    <definedName name="nichtFreigegeben69">Data!$CR$15</definedName>
-    <definedName name="nichtFreigegeben7">Data!$AB$15</definedName>
-    <definedName name="nichtFreigegeben70">Data!$CS$15</definedName>
-    <definedName name="nichtFreigegeben71">Data!$CT$15</definedName>
-    <definedName name="nichtFreigegeben72">Data!$CU$15</definedName>
-    <definedName name="nichtFreigegeben73">Data!$CV$15</definedName>
-    <definedName name="nichtFreigegeben74">Data!$CW$15</definedName>
-    <definedName name="nichtFreigegeben75">Data!$CX$15</definedName>
-    <definedName name="nichtFreigegeben76">Data!$CY$15</definedName>
-    <definedName name="nichtFreigegeben77">Data!$CZ$15</definedName>
-    <definedName name="nichtFreigegeben78">Data!$DA$15</definedName>
-    <definedName name="nichtFreigegeben79">Data!$DB$15</definedName>
-    <definedName name="nichtFreigegeben8">Data!$AC$15</definedName>
-    <definedName name="nichtFreigegeben80">Data!$DC$15</definedName>
-    <definedName name="nichtFreigegeben81">Data!$DF$15</definedName>
-    <definedName name="nichtFreigegeben82">Data!$DG$15</definedName>
-    <definedName name="nichtFreigegeben83">Data!$DH$15</definedName>
-    <definedName name="nichtFreigegeben84">Data!$DI$15</definedName>
-    <definedName name="nichtFreigegeben85">Data!$DJ$15</definedName>
-    <definedName name="nichtFreigegeben86">Data!$DK$15</definedName>
-    <definedName name="nichtFreigegeben87">Data!$DL$15</definedName>
-    <definedName name="nichtFreigegeben88">Data!$DM$15</definedName>
-    <definedName name="nichtFreigegeben89">Data!$DN$15</definedName>
-    <definedName name="nichtFreigegeben9">Data!$AD$15</definedName>
-    <definedName name="nichtFreigegeben90">Data!$DO$15</definedName>
-    <definedName name="nichtFreigegeben91">Data!$DP$15</definedName>
-    <definedName name="nichtFreigegeben92">Data!$DQ$15</definedName>
-    <definedName name="nichtFreigegeben93">Data!$DR$15</definedName>
-    <definedName name="nichtFreigegeben94">Data!$DS$15</definedName>
-    <definedName name="nichtFreigegeben95">Data!$DT$15</definedName>
-    <definedName name="nichtFreigegeben96">Data!$DU$15</definedName>
-    <definedName name="nichtFreigegeben97">Data!$DV$15</definedName>
-    <definedName name="nichtFreigegeben98">Data!$DW$15</definedName>
-    <definedName name="nichtFreigegeben99">Data!$DX$15</definedName>
-    <definedName name="statusKategorie">Data!$U$11</definedName>
-    <definedName name="summeStundenDi">Data!$BL$11</definedName>
-    <definedName name="summeStundenDo">Data!$DD$11</definedName>
-    <definedName name="summeStundenFr">Data!$DZ$11</definedName>
-    <definedName name="summeStundenMi">Data!$CH$11</definedName>
-    <definedName name="summeStundenMo">Data!$AP$11</definedName>
-    <definedName name="summeStundenWoche">Data!$EB$11</definedName>
-    <definedName name="summeVerpflegungDi">Data!$BM$11</definedName>
-    <definedName name="summeVerpflegungDo">Data!$DE$11</definedName>
-    <definedName name="summeVerpflegungFr">Data!$EA$11</definedName>
-    <definedName name="summeVerpflegungMi">Data!$CI$11</definedName>
-    <definedName name="summeVerpflegungMo">Data!$AQ$11</definedName>
-    <definedName name="summeVerpflegungNF1">Data!$AQ$15</definedName>
-    <definedName name="summeVerpflegungNF2">Data!$BM$15</definedName>
-    <definedName name="summeVerpflegungNF3">Data!$CI$15</definedName>
-    <definedName name="summeVerpflegungNF4">Data!$DE$15</definedName>
-    <definedName name="summeVerpflegungNF5">Data!$EA$15</definedName>
-    <definedName name="summeVerpflegungWoche">Data!$EC$11</definedName>
-    <definedName name="summStundenNF1">Data!$AP$15</definedName>
-    <definedName name="summStundenNF2">Data!$BL$15</definedName>
-    <definedName name="summStundenNF3">Data!$CH$15</definedName>
-    <definedName name="summStundenNF4">Data!$DD$15</definedName>
-    <definedName name="summStundenNF5">Data!$DZ$15</definedName>
+    <definedName name="angemeldet1" localSheetId="0">Data!$V$11</definedName>
+    <definedName name="angemeldet10" localSheetId="0">Data!$AE$11</definedName>
+    <definedName name="angemeldet100" localSheetId="0">Data!$DY$11</definedName>
+    <definedName name="angemeldet11" localSheetId="0">Data!$AF$11</definedName>
+    <definedName name="angemeldet12" localSheetId="0">Data!$AG$11</definedName>
+    <definedName name="angemeldet13" localSheetId="0">Data!$AH$11</definedName>
+    <definedName name="angemeldet14" localSheetId="0">Data!$AI$11</definedName>
+    <definedName name="angemeldet15" localSheetId="0">Data!$AJ$11</definedName>
+    <definedName name="angemeldet16" localSheetId="0">Data!$AK$11</definedName>
+    <definedName name="angemeldet17" localSheetId="0">Data!$AL$11</definedName>
+    <definedName name="angemeldet18" localSheetId="0">Data!$AM$11</definedName>
+    <definedName name="angemeldet19" localSheetId="0">Data!$AN$11</definedName>
+    <definedName name="angemeldet2" localSheetId="0">Data!$W$11</definedName>
+    <definedName name="angemeldet20" localSheetId="0">Data!$AO$11</definedName>
+    <definedName name="angemeldet21" localSheetId="0">Data!$AR$11</definedName>
+    <definedName name="angemeldet22" localSheetId="0">Data!$AS$11</definedName>
+    <definedName name="angemeldet23" localSheetId="0">Data!$AT$11</definedName>
+    <definedName name="angemeldet24" localSheetId="0">Data!$AU$11</definedName>
+    <definedName name="angemeldet25" localSheetId="0">Data!$AV$11</definedName>
+    <definedName name="angemeldet26" localSheetId="0">Data!$AW$11</definedName>
+    <definedName name="angemeldet27" localSheetId="0">Data!$AX$11</definedName>
+    <definedName name="angemeldet28" localSheetId="0">Data!$AY$11</definedName>
+    <definedName name="angemeldet29" localSheetId="0">Data!$AZ$11</definedName>
+    <definedName name="angemeldet3" localSheetId="0">Data!$X$11</definedName>
+    <definedName name="angemeldet30" localSheetId="0">Data!$BA$11</definedName>
+    <definedName name="angemeldet31" localSheetId="0">Data!$BB$11</definedName>
+    <definedName name="angemeldet32" localSheetId="0">Data!$BC$11</definedName>
+    <definedName name="angemeldet33" localSheetId="0">Data!$BD$11</definedName>
+    <definedName name="angemeldet34" localSheetId="0">Data!$BE$11</definedName>
+    <definedName name="angemeldet35" localSheetId="0">Data!$BF$11</definedName>
+    <definedName name="angemeldet36" localSheetId="0">Data!$BG$11</definedName>
+    <definedName name="angemeldet37" localSheetId="0">Data!$BH$11</definedName>
+    <definedName name="angemeldet38" localSheetId="0">Data!$BI$11</definedName>
+    <definedName name="angemeldet39" localSheetId="0">Data!$BJ$11</definedName>
+    <definedName name="angemeldet4" localSheetId="0">Data!$Y$11</definedName>
+    <definedName name="angemeldet40" localSheetId="0">Data!$BK$11</definedName>
+    <definedName name="angemeldet41" localSheetId="0">Data!$BN$11</definedName>
+    <definedName name="angemeldet42" localSheetId="0">Data!$BO$11</definedName>
+    <definedName name="angemeldet43" localSheetId="0">Data!$BP$11</definedName>
+    <definedName name="angemeldet44" localSheetId="0">Data!$BQ$11</definedName>
+    <definedName name="angemeldet45" localSheetId="0">Data!$BR$11</definedName>
+    <definedName name="angemeldet46" localSheetId="0">Data!$BS$11</definedName>
+    <definedName name="angemeldet47" localSheetId="0">Data!$BT$11</definedName>
+    <definedName name="angemeldet48" localSheetId="0">Data!$BU$11</definedName>
+    <definedName name="angemeldet49" localSheetId="0">Data!$BV$11</definedName>
+    <definedName name="angemeldet5" localSheetId="0">Data!$Z$11</definedName>
+    <definedName name="angemeldet50" localSheetId="0">Data!$BW$11</definedName>
+    <definedName name="angemeldet51" localSheetId="0">Data!$BX$11</definedName>
+    <definedName name="angemeldet52" localSheetId="0">Data!$BY$11</definedName>
+    <definedName name="angemeldet53" localSheetId="0">Data!$BZ$11</definedName>
+    <definedName name="angemeldet54" localSheetId="0">Data!$CA$11</definedName>
+    <definedName name="angemeldet55" localSheetId="0">Data!$CB$11</definedName>
+    <definedName name="angemeldet56" localSheetId="0">Data!$CC$11</definedName>
+    <definedName name="angemeldet57" localSheetId="0">Data!$CD$11</definedName>
+    <definedName name="angemeldet58" localSheetId="0">Data!$CE$11</definedName>
+    <definedName name="angemeldet59" localSheetId="0">Data!$CF$11</definedName>
+    <definedName name="angemeldet6" localSheetId="0">Data!$AA$11</definedName>
+    <definedName name="angemeldet60" localSheetId="0">Data!$CG$11</definedName>
+    <definedName name="angemeldet61" localSheetId="0">Data!$CJ$11</definedName>
+    <definedName name="angemeldet62" localSheetId="0">Data!$CK$11</definedName>
+    <definedName name="angemeldet63" localSheetId="0">Data!$CL$11</definedName>
+    <definedName name="angemeldet64" localSheetId="0">Data!$CM$11</definedName>
+    <definedName name="angemeldet65" localSheetId="0">Data!$CN$11</definedName>
+    <definedName name="angemeldet66" localSheetId="0">Data!$CO$11</definedName>
+    <definedName name="angemeldet67" localSheetId="0">Data!$CP$11</definedName>
+    <definedName name="angemeldet68" localSheetId="0">Data!$CQ$11</definedName>
+    <definedName name="angemeldet69" localSheetId="0">Data!$CR$11</definedName>
+    <definedName name="angemeldet7" localSheetId="0">Data!$AB$11</definedName>
+    <definedName name="angemeldet70" localSheetId="0">Data!$CS$11</definedName>
+    <definedName name="angemeldet71" localSheetId="0">Data!$CT$11</definedName>
+    <definedName name="angemeldet72" localSheetId="0">Data!$CU$11</definedName>
+    <definedName name="angemeldet73" localSheetId="0">Data!$CV$11</definedName>
+    <definedName name="angemeldet74" localSheetId="0">Data!$CW$11</definedName>
+    <definedName name="angemeldet75" localSheetId="0">Data!$CX$11</definedName>
+    <definedName name="angemeldet76" localSheetId="0">Data!$CY$11</definedName>
+    <definedName name="angemeldet77" localSheetId="0">Data!$CZ$11</definedName>
+    <definedName name="angemeldet78" localSheetId="0">Data!$DA$11</definedName>
+    <definedName name="angemeldet79" localSheetId="0">Data!$DB$11</definedName>
+    <definedName name="angemeldet8" localSheetId="0">Data!$AC$11</definedName>
+    <definedName name="angemeldet80" localSheetId="0">Data!$DC$11</definedName>
+    <definedName name="angemeldet81" localSheetId="0">Data!$DF$11</definedName>
+    <definedName name="angemeldet82" localSheetId="0">Data!$DG$11</definedName>
+    <definedName name="angemeldet83" localSheetId="0">Data!$DH$11</definedName>
+    <definedName name="angemeldet84" localSheetId="0">Data!$DI$11</definedName>
+    <definedName name="angemeldet85" localSheetId="0">Data!$DJ$11</definedName>
+    <definedName name="angemeldet86" localSheetId="0">Data!$DK$11</definedName>
+    <definedName name="angemeldet87" localSheetId="0">Data!$DL$11</definedName>
+    <definedName name="angemeldet88" localSheetId="0">Data!$DM$11</definedName>
+    <definedName name="angemeldet89" localSheetId="0">Data!$DN$11</definedName>
+    <definedName name="angemeldet9" localSheetId="0">Data!$AD$11</definedName>
+    <definedName name="angemeldet90" localSheetId="0">Data!$DO$11</definedName>
+    <definedName name="angemeldet91" localSheetId="0">Data!$DP$11</definedName>
+    <definedName name="angemeldet92" localSheetId="0">Data!$DQ$11</definedName>
+    <definedName name="angemeldet93" localSheetId="0">Data!$DR$11</definedName>
+    <definedName name="angemeldet94" localSheetId="0">Data!$DS$11</definedName>
+    <definedName name="angemeldet95" localSheetId="0">Data!$DT$11</definedName>
+    <definedName name="angemeldet96" localSheetId="0">Data!$DU$11</definedName>
+    <definedName name="angemeldet97" localSheetId="0">Data!$DV$11</definedName>
+    <definedName name="angemeldet98" localSheetId="0">Data!$DW$11</definedName>
+    <definedName name="angemeldet99" localSheetId="0">Data!$DX$11</definedName>
+    <definedName name="freigegebenKategorie" localSheetId="0">Data!$U$15</definedName>
+    <definedName name="nichtFreigegeben1" localSheetId="0">Data!$V$15</definedName>
+    <definedName name="nichtFreigegeben10" localSheetId="0">Data!$AE$15</definedName>
+    <definedName name="nichtFreigegeben100" localSheetId="0">Data!$DY$15</definedName>
+    <definedName name="nichtFreigegeben11" localSheetId="0">Data!$AF$15</definedName>
+    <definedName name="nichtFreigegeben12" localSheetId="0">Data!$AG$15</definedName>
+    <definedName name="nichtFreigegeben13" localSheetId="0">Data!$AH$15</definedName>
+    <definedName name="nichtFreigegeben14" localSheetId="0">Data!$AI$15</definedName>
+    <definedName name="nichtFreigegeben15" localSheetId="0">Data!$AJ$15</definedName>
+    <definedName name="nichtFreigegeben16" localSheetId="0">Data!$AK$15</definedName>
+    <definedName name="nichtFreigegeben17" localSheetId="0">Data!$AL$15</definedName>
+    <definedName name="nichtFreigegeben18" localSheetId="0">Data!$AM$15</definedName>
+    <definedName name="nichtFreigegeben19" localSheetId="0">Data!$AN$15</definedName>
+    <definedName name="nichtFreigegeben2" localSheetId="0">Data!$W$15</definedName>
+    <definedName name="nichtFreigegeben20" localSheetId="0">Data!$AO$15</definedName>
+    <definedName name="nichtFreigegeben21" localSheetId="0">Data!$AR$15</definedName>
+    <definedName name="nichtFreigegeben22" localSheetId="0">Data!$AS$15</definedName>
+    <definedName name="nichtFreigegeben23" localSheetId="0">Data!$AT$15</definedName>
+    <definedName name="nichtFreigegeben24" localSheetId="0">Data!$AU$15</definedName>
+    <definedName name="nichtFreigegeben25" localSheetId="0">Data!$AV$15</definedName>
+    <definedName name="nichtFreigegeben26" localSheetId="0">Data!$AW$15</definedName>
+    <definedName name="nichtFreigegeben27" localSheetId="0">Data!$AX$15</definedName>
+    <definedName name="nichtFreigegeben28" localSheetId="0">Data!$AY$15</definedName>
+    <definedName name="nichtFreigegeben29" localSheetId="0">Data!$AZ$15</definedName>
+    <definedName name="nichtFreigegeben3" localSheetId="0">Data!$X$15</definedName>
+    <definedName name="nichtFreigegeben30" localSheetId="0">Data!$BA$15</definedName>
+    <definedName name="nichtFreigegeben31" localSheetId="0">Data!$BB$15</definedName>
+    <definedName name="nichtFreigegeben32" localSheetId="0">Data!$BC$15</definedName>
+    <definedName name="nichtFreigegeben33" localSheetId="0">Data!$BD$15</definedName>
+    <definedName name="nichtFreigegeben34" localSheetId="0">Data!$BE$15</definedName>
+    <definedName name="nichtFreigegeben35" localSheetId="0">Data!$BF$15</definedName>
+    <definedName name="nichtFreigegeben36" localSheetId="0">Data!$BG$15</definedName>
+    <definedName name="nichtFreigegeben37" localSheetId="0">Data!$BH$15</definedName>
+    <definedName name="nichtFreigegeben38" localSheetId="0">Data!$BI$15</definedName>
+    <definedName name="nichtFreigegeben39" localSheetId="0">Data!$BJ$15</definedName>
+    <definedName name="nichtFreigegeben4" localSheetId="0">Data!$Y$15</definedName>
+    <definedName name="nichtFreigegeben40" localSheetId="0">Data!$BK$15</definedName>
+    <definedName name="nichtFreigegeben41" localSheetId="0">Data!$BN$15</definedName>
+    <definedName name="nichtFreigegeben42" localSheetId="0">Data!$BO$15</definedName>
+    <definedName name="nichtFreigegeben43" localSheetId="0">Data!$BP$15</definedName>
+    <definedName name="nichtFreigegeben44" localSheetId="0">Data!$BQ$15</definedName>
+    <definedName name="nichtFreigegeben45" localSheetId="0">Data!$BR$15</definedName>
+    <definedName name="nichtFreigegeben46" localSheetId="0">Data!$BS$15</definedName>
+    <definedName name="nichtFreigegeben47" localSheetId="0">Data!$BT$15</definedName>
+    <definedName name="nichtFreigegeben48" localSheetId="0">Data!$BU$15</definedName>
+    <definedName name="nichtFreigegeben49" localSheetId="0">Data!$BV$15</definedName>
+    <definedName name="nichtFreigegeben5" localSheetId="0">Data!$Z$15</definedName>
+    <definedName name="nichtFreigegeben50" localSheetId="0">Data!$BW$15</definedName>
+    <definedName name="nichtFreigegeben51" localSheetId="0">Data!$BX$15</definedName>
+    <definedName name="nichtFreigegeben52" localSheetId="0">Data!$BY$15</definedName>
+    <definedName name="nichtFreigegeben53" localSheetId="0">Data!$BZ$15</definedName>
+    <definedName name="nichtFreigegeben54" localSheetId="0">Data!$CA$15</definedName>
+    <definedName name="nichtFreigegeben55" localSheetId="0">Data!$CB$15</definedName>
+    <definedName name="nichtFreigegeben56" localSheetId="0">Data!$CC$15</definedName>
+    <definedName name="nichtFreigegeben57" localSheetId="0">Data!$CD$15</definedName>
+    <definedName name="nichtFreigegeben58" localSheetId="0">Data!$CE$15</definedName>
+    <definedName name="nichtFreigegeben59" localSheetId="0">Data!$CF$15</definedName>
+    <definedName name="nichtFreigegeben6" localSheetId="0">Data!$AA$15</definedName>
+    <definedName name="nichtFreigegeben60" localSheetId="0">Data!$CG$15</definedName>
+    <definedName name="nichtFreigegeben61" localSheetId="0">Data!$CJ$15</definedName>
+    <definedName name="nichtFreigegeben62" localSheetId="0">Data!$CK$15</definedName>
+    <definedName name="nichtFreigegeben63" localSheetId="0">Data!$CL$15</definedName>
+    <definedName name="nichtFreigegeben64" localSheetId="0">Data!$CM$15</definedName>
+    <definedName name="nichtFreigegeben65" localSheetId="0">Data!$CN$15</definedName>
+    <definedName name="nichtFreigegeben66" localSheetId="0">Data!$CO$15</definedName>
+    <definedName name="nichtFreigegeben67" localSheetId="0">Data!$CP$15</definedName>
+    <definedName name="nichtFreigegeben68" localSheetId="0">Data!$CQ$15</definedName>
+    <definedName name="nichtFreigegeben69" localSheetId="0">Data!$CR$15</definedName>
+    <definedName name="nichtFreigegeben7" localSheetId="0">Data!$AB$15</definedName>
+    <definedName name="nichtFreigegeben70" localSheetId="0">Data!$CS$15</definedName>
+    <definedName name="nichtFreigegeben71" localSheetId="0">Data!$CT$15</definedName>
+    <definedName name="nichtFreigegeben72" localSheetId="0">Data!$CU$15</definedName>
+    <definedName name="nichtFreigegeben73" localSheetId="0">Data!$CV$15</definedName>
+    <definedName name="nichtFreigegeben74" localSheetId="0">Data!$CW$15</definedName>
+    <definedName name="nichtFreigegeben75" localSheetId="0">Data!$CX$15</definedName>
+    <definedName name="nichtFreigegeben76" localSheetId="0">Data!$CY$15</definedName>
+    <definedName name="nichtFreigegeben77" localSheetId="0">Data!$CZ$15</definedName>
+    <definedName name="nichtFreigegeben78" localSheetId="0">Data!$DA$15</definedName>
+    <definedName name="nichtFreigegeben79" localSheetId="0">Data!$DB$15</definedName>
+    <definedName name="nichtFreigegeben8" localSheetId="0">Data!$AC$15</definedName>
+    <definedName name="nichtFreigegeben80" localSheetId="0">Data!$DC$15</definedName>
+    <definedName name="nichtFreigegeben81" localSheetId="0">Data!$DF$15</definedName>
+    <definedName name="nichtFreigegeben82" localSheetId="0">Data!$DG$15</definedName>
+    <definedName name="nichtFreigegeben83" localSheetId="0">Data!$DH$15</definedName>
+    <definedName name="nichtFreigegeben84" localSheetId="0">Data!$DI$15</definedName>
+    <definedName name="nichtFreigegeben85" localSheetId="0">Data!$DJ$15</definedName>
+    <definedName name="nichtFreigegeben86" localSheetId="0">Data!$DK$15</definedName>
+    <definedName name="nichtFreigegeben87" localSheetId="0">Data!$DL$15</definedName>
+    <definedName name="nichtFreigegeben88" localSheetId="0">Data!$DM$15</definedName>
+    <definedName name="nichtFreigegeben89" localSheetId="0">Data!$DN$15</definedName>
+    <definedName name="nichtFreigegeben9" localSheetId="0">Data!$AD$15</definedName>
+    <definedName name="nichtFreigegeben90" localSheetId="0">Data!$DO$15</definedName>
+    <definedName name="nichtFreigegeben91" localSheetId="0">Data!$DP$15</definedName>
+    <definedName name="nichtFreigegeben92" localSheetId="0">Data!$DQ$15</definedName>
+    <definedName name="nichtFreigegeben93" localSheetId="0">Data!$DR$15</definedName>
+    <definedName name="nichtFreigegeben94" localSheetId="0">Data!$DS$15</definedName>
+    <definedName name="nichtFreigegeben95" localSheetId="0">Data!$DT$15</definedName>
+    <definedName name="nichtFreigegeben96" localSheetId="0">Data!$DU$15</definedName>
+    <definedName name="nichtFreigegeben97" localSheetId="0">Data!$DV$15</definedName>
+    <definedName name="nichtFreigegeben98" localSheetId="0">Data!$DW$15</definedName>
+    <definedName name="nichtFreigegeben99" localSheetId="0">Data!$DX$15</definedName>
+    <definedName name="statusKategorie" localSheetId="0">Data!$U$11</definedName>
+    <definedName name="summeStundenDi" localSheetId="0">Data!$BL$11</definedName>
+    <definedName name="summeStundenDo" localSheetId="0">Data!$DD$11</definedName>
+    <definedName name="summeStundenFr" localSheetId="0">Data!$DZ$11</definedName>
+    <definedName name="summeStundenMi" localSheetId="0">Data!$CH$11</definedName>
+    <definedName name="summeStundenMo" localSheetId="0">Data!$AP$11</definedName>
+    <definedName name="summeStundenWoche" localSheetId="0">Data!$EB$11</definedName>
+    <definedName name="summeVerpflegungDi" localSheetId="0">Data!$BM$11</definedName>
+    <definedName name="summeVerpflegungDo" localSheetId="0">Data!$DE$11</definedName>
+    <definedName name="summeVerpflegungFr" localSheetId="0">Data!$EA$11</definedName>
+    <definedName name="summeVerpflegungMi" localSheetId="0">Data!$CI$11</definedName>
+    <definedName name="summeVerpflegungMo" localSheetId="0">Data!$AQ$11</definedName>
+    <definedName name="summeVerpflegungNF1" localSheetId="0">Data!$AQ$15</definedName>
+    <definedName name="summeVerpflegungNF2" localSheetId="0">Data!$BM$15</definedName>
+    <definedName name="summeVerpflegungNF3" localSheetId="0">Data!$CI$15</definedName>
+    <definedName name="summeVerpflegungNF4" localSheetId="0">Data!$DE$15</definedName>
+    <definedName name="summeVerpflegungNF5" localSheetId="0">Data!$EA$15</definedName>
+    <definedName name="summeVerpflegungWoche" localSheetId="0">Data!$EC$11</definedName>
+    <definedName name="summStundenNF1" localSheetId="0">Data!$AP$15</definedName>
+    <definedName name="summStundenNF2" localSheetId="0">Data!$BL$15</definedName>
+    <definedName name="summStundenNF3" localSheetId="0">Data!$CH$15</definedName>
+    <definedName name="summStundenNF4" localSheetId="0">Data!$DD$15</definedName>
+    <definedName name="summStundenNF5" localSheetId="0">Data!$DZ$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -805,7 +805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -874,9 +874,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -893,9 +890,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
@@ -930,9 +924,6 @@
     <xf numFmtId="166" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -944,6 +935,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1050,7 +1056,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{4D11B231-AAE6-44F9-843C-66A0D70C5328}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1425,28 +1431,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:EH39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.6640625"/>
-    <col min="3" max="16" width="17.5" style="1" customWidth="1"/>
+    <col min="3" max="16" width="17.44140625" style="1" customWidth="1"/>
     <col min="17" max="18" width="17"/>
-    <col min="19" max="20" width="33.1640625" customWidth="1"/>
-    <col min="21" max="21" width="33.1640625" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="33.109375" customWidth="1"/>
+    <col min="21" max="21" width="33.109375" hidden="1" customWidth="1"/>
     <col min="22" max="26" width="13.33203125" customWidth="1"/>
-    <col min="27" max="27" width="13.5" customWidth="1"/>
-    <col min="28" max="41" width="10.5"/>
-    <col min="44" max="63" width="10.5"/>
-    <col min="66" max="85" width="10.5"/>
-    <col min="88" max="107" width="10.5"/>
-    <col min="110" max="128" width="10.5"/>
+    <col min="27" max="27" width="13.44140625" customWidth="1"/>
+    <col min="28" max="41" width="10.44140625"/>
+    <col min="44" max="63" width="10.44140625"/>
+    <col min="66" max="85" width="10.44140625"/>
+    <col min="88" max="107" width="10.44140625"/>
+    <col min="110" max="128" width="10.44140625"/>
     <col min="129" max="129" width="10" customWidth="1"/>
-    <col min="132" max="133" width="10.5"/>
+    <col min="132" max="133" width="10.44140625"/>
     <col min="134" max="134" width="50" customWidth="1"/>
     <col min="135" max="135" width="22.6640625" customWidth="1"/>
-    <col min="138" max="994" width="10.5"/>
+    <col min="138" max="994" width="10.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:138" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:138" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1476,7 +1482,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1506,7 +1512,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:138" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -1534,7 +1540,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -1562,7 +1568,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:138" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:138" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="17" t="s">
         <v>47</v>
       </c>
@@ -1699,7 +1705,7 @@
       <c r="DZ5" s="2"/>
       <c r="EA5" s="2"/>
     </row>
-    <row r="6" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
@@ -2015,201 +2021,201 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="72" t="s">
+    <row r="7" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="72" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="73"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="72" t="s">
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="72" t="s">
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="78" t="s">
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="76"/>
+      <c r="Q7" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R7" s="78" t="s">
+      <c r="R7" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="S7" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="T7" s="57" t="s">
+      <c r="S7" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" s="54" t="s">
         <v>92</v>
       </c>
       <c r="U7" s="14"/>
-      <c r="V7" s="64" t="s">
+      <c r="V7" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="W7" s="65"/>
-      <c r="X7" s="65"/>
-      <c r="Y7" s="65"/>
-      <c r="Z7" s="65"/>
-      <c r="AA7" s="65"/>
-      <c r="AB7" s="65"/>
-      <c r="AC7" s="65"/>
-      <c r="AD7" s="65"/>
-      <c r="AE7" s="65"/>
-      <c r="AF7" s="65"/>
-      <c r="AG7" s="65"/>
-      <c r="AH7" s="65"/>
-      <c r="AI7" s="65"/>
-      <c r="AJ7" s="65"/>
-      <c r="AK7" s="65"/>
-      <c r="AL7" s="65"/>
-      <c r="AM7" s="65"/>
-      <c r="AN7" s="65"/>
-      <c r="AO7" s="65"/>
-      <c r="AP7" s="65"/>
-      <c r="AQ7" s="66"/>
-      <c r="AR7" s="64" t="s">
+      <c r="W7" s="67"/>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="67"/>
+      <c r="Z7" s="67"/>
+      <c r="AA7" s="67"/>
+      <c r="AB7" s="67"/>
+      <c r="AC7" s="67"/>
+      <c r="AD7" s="67"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="67"/>
+      <c r="AL7" s="67"/>
+      <c r="AM7" s="67"/>
+      <c r="AN7" s="67"/>
+      <c r="AO7" s="67"/>
+      <c r="AP7" s="67"/>
+      <c r="AQ7" s="68"/>
+      <c r="AR7" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="AS7" s="65"/>
-      <c r="AT7" s="65"/>
-      <c r="AU7" s="65"/>
-      <c r="AV7" s="65"/>
-      <c r="AW7" s="65"/>
-      <c r="AX7" s="65"/>
-      <c r="AY7" s="65"/>
-      <c r="AZ7" s="65"/>
-      <c r="BA7" s="65"/>
-      <c r="BB7" s="65"/>
-      <c r="BC7" s="65"/>
-      <c r="BD7" s="65"/>
-      <c r="BE7" s="65"/>
-      <c r="BF7" s="65"/>
-      <c r="BG7" s="65"/>
-      <c r="BH7" s="65"/>
-      <c r="BI7" s="65"/>
-      <c r="BJ7" s="65"/>
-      <c r="BK7" s="65"/>
-      <c r="BL7" s="65"/>
-      <c r="BM7" s="66"/>
-      <c r="BN7" s="64" t="s">
+      <c r="AS7" s="67"/>
+      <c r="AT7" s="67"/>
+      <c r="AU7" s="67"/>
+      <c r="AV7" s="67"/>
+      <c r="AW7" s="67"/>
+      <c r="AX7" s="67"/>
+      <c r="AY7" s="67"/>
+      <c r="AZ7" s="67"/>
+      <c r="BA7" s="67"/>
+      <c r="BB7" s="67"/>
+      <c r="BC7" s="67"/>
+      <c r="BD7" s="67"/>
+      <c r="BE7" s="67"/>
+      <c r="BF7" s="67"/>
+      <c r="BG7" s="67"/>
+      <c r="BH7" s="67"/>
+      <c r="BI7" s="67"/>
+      <c r="BJ7" s="67"/>
+      <c r="BK7" s="67"/>
+      <c r="BL7" s="67"/>
+      <c r="BM7" s="68"/>
+      <c r="BN7" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="BO7" s="65"/>
-      <c r="BP7" s="65"/>
-      <c r="BQ7" s="65"/>
-      <c r="BR7" s="65"/>
-      <c r="BS7" s="65"/>
-      <c r="BT7" s="65"/>
-      <c r="BU7" s="65"/>
-      <c r="BV7" s="65"/>
-      <c r="BW7" s="65"/>
-      <c r="BX7" s="65"/>
-      <c r="BY7" s="65"/>
-      <c r="BZ7" s="65"/>
-      <c r="CA7" s="65"/>
-      <c r="CB7" s="65"/>
-      <c r="CC7" s="65"/>
-      <c r="CD7" s="65"/>
-      <c r="CE7" s="65"/>
-      <c r="CF7" s="65"/>
-      <c r="CG7" s="65"/>
-      <c r="CH7" s="65"/>
-      <c r="CI7" s="66"/>
-      <c r="CJ7" s="64" t="s">
+      <c r="BO7" s="67"/>
+      <c r="BP7" s="67"/>
+      <c r="BQ7" s="67"/>
+      <c r="BR7" s="67"/>
+      <c r="BS7" s="67"/>
+      <c r="BT7" s="67"/>
+      <c r="BU7" s="67"/>
+      <c r="BV7" s="67"/>
+      <c r="BW7" s="67"/>
+      <c r="BX7" s="67"/>
+      <c r="BY7" s="67"/>
+      <c r="BZ7" s="67"/>
+      <c r="CA7" s="67"/>
+      <c r="CB7" s="67"/>
+      <c r="CC7" s="67"/>
+      <c r="CD7" s="67"/>
+      <c r="CE7" s="67"/>
+      <c r="CF7" s="67"/>
+      <c r="CG7" s="67"/>
+      <c r="CH7" s="67"/>
+      <c r="CI7" s="68"/>
+      <c r="CJ7" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="CK7" s="65"/>
-      <c r="CL7" s="65"/>
-      <c r="CM7" s="65"/>
-      <c r="CN7" s="65"/>
-      <c r="CO7" s="65"/>
-      <c r="CP7" s="65"/>
-      <c r="CQ7" s="65"/>
-      <c r="CR7" s="65"/>
-      <c r="CS7" s="65"/>
-      <c r="CT7" s="65"/>
-      <c r="CU7" s="65"/>
-      <c r="CV7" s="65"/>
-      <c r="CW7" s="65"/>
-      <c r="CX7" s="65"/>
-      <c r="CY7" s="65"/>
-      <c r="CZ7" s="65"/>
-      <c r="DA7" s="65"/>
-      <c r="DB7" s="65"/>
-      <c r="DC7" s="65"/>
-      <c r="DD7" s="65"/>
-      <c r="DE7" s="66"/>
-      <c r="DF7" s="64" t="s">
+      <c r="CK7" s="67"/>
+      <c r="CL7" s="67"/>
+      <c r="CM7" s="67"/>
+      <c r="CN7" s="67"/>
+      <c r="CO7" s="67"/>
+      <c r="CP7" s="67"/>
+      <c r="CQ7" s="67"/>
+      <c r="CR7" s="67"/>
+      <c r="CS7" s="67"/>
+      <c r="CT7" s="67"/>
+      <c r="CU7" s="67"/>
+      <c r="CV7" s="67"/>
+      <c r="CW7" s="67"/>
+      <c r="CX7" s="67"/>
+      <c r="CY7" s="67"/>
+      <c r="CZ7" s="67"/>
+      <c r="DA7" s="67"/>
+      <c r="DB7" s="67"/>
+      <c r="DC7" s="67"/>
+      <c r="DD7" s="67"/>
+      <c r="DE7" s="68"/>
+      <c r="DF7" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="DG7" s="65"/>
-      <c r="DH7" s="65"/>
-      <c r="DI7" s="65"/>
-      <c r="DJ7" s="65"/>
-      <c r="DK7" s="65"/>
-      <c r="DL7" s="65"/>
-      <c r="DM7" s="65"/>
-      <c r="DN7" s="65"/>
-      <c r="DO7" s="65"/>
-      <c r="DP7" s="65"/>
-      <c r="DQ7" s="65"/>
-      <c r="DR7" s="65"/>
-      <c r="DS7" s="65"/>
-      <c r="DT7" s="65"/>
-      <c r="DU7" s="65"/>
-      <c r="DV7" s="65"/>
-      <c r="DW7" s="65"/>
-      <c r="DX7" s="65"/>
-      <c r="DY7" s="65"/>
-      <c r="DZ7" s="65"/>
-      <c r="EA7" s="66"/>
-      <c r="EB7" s="92" t="s">
+      <c r="DG7" s="67"/>
+      <c r="DH7" s="67"/>
+      <c r="DI7" s="67"/>
+      <c r="DJ7" s="67"/>
+      <c r="DK7" s="67"/>
+      <c r="DL7" s="67"/>
+      <c r="DM7" s="67"/>
+      <c r="DN7" s="67"/>
+      <c r="DO7" s="67"/>
+      <c r="DP7" s="67"/>
+      <c r="DQ7" s="67"/>
+      <c r="DR7" s="67"/>
+      <c r="DS7" s="67"/>
+      <c r="DT7" s="67"/>
+      <c r="DU7" s="67"/>
+      <c r="DV7" s="67"/>
+      <c r="DW7" s="67"/>
+      <c r="DX7" s="67"/>
+      <c r="DY7" s="67"/>
+      <c r="DZ7" s="67"/>
+      <c r="EA7" s="68"/>
+      <c r="EB7" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="EC7" s="92"/>
-      <c r="ED7" s="52" t="s">
+      <c r="EC7" s="94"/>
+      <c r="ED7" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="EE7" s="93" t="s">
+      <c r="EE7" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="EF7" s="86" t="s">
+      <c r="EF7" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="EG7" s="87"/>
+      <c r="EG7" s="89"/>
       <c r="EH7" s="11"/>
     </row>
-    <row r="8" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="75"/>
-      <c r="B8" s="76"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="82"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="59"/>
+    <row r="8" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="77"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="84"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="56"/>
       <c r="U8" s="15"/>
       <c r="V8" s="4" t="s">
         <v>6</v>
@@ -2271,10 +2277,10 @@
       <c r="AO8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AP8" s="68" t="s">
+      <c r="AP8" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="AQ8" s="68" t="s">
+      <c r="AQ8" s="70" t="s">
         <v>45</v>
       </c>
       <c r="AR8" s="4" t="s">
@@ -2337,10 +2343,10 @@
       <c r="BK8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BL8" s="68" t="s">
+      <c r="BL8" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="BM8" s="68" t="s">
+      <c r="BM8" s="70" t="s">
         <v>45</v>
       </c>
       <c r="BN8" s="4" t="s">
@@ -2403,10 +2409,10 @@
       <c r="CG8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="CH8" s="68" t="s">
+      <c r="CH8" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="CI8" s="68" t="s">
+      <c r="CI8" s="70" t="s">
         <v>45</v>
       </c>
       <c r="CJ8" s="4" t="s">
@@ -2469,10 +2475,10 @@
       <c r="DC8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="DD8" s="68" t="s">
+      <c r="DD8" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="DE8" s="68" t="s">
+      <c r="DE8" s="70" t="s">
         <v>45</v>
       </c>
       <c r="DF8" s="4" t="s">
@@ -2535,415 +2541,415 @@
       <c r="DY8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="DZ8" s="68" t="s">
+      <c r="DZ8" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="EA8" s="68" t="s">
+      <c r="EA8" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="EB8" s="68" t="s">
+      <c r="EB8" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="EC8" s="68" t="s">
+      <c r="EC8" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="ED8" s="53"/>
-      <c r="EE8" s="94"/>
-      <c r="EF8" s="88"/>
-      <c r="EG8" s="89"/>
+      <c r="ED8" s="51"/>
+      <c r="EE8" s="96"/>
+      <c r="EF8" s="90"/>
+      <c r="EG8" s="91"/>
     </row>
-    <row r="9" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="78" t="s">
+    <row r="9" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="78" t="s">
+      <c r="D9" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="78" t="s">
+      <c r="F9" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="78" t="s">
+      <c r="G9" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="78" t="s">
+      <c r="H9" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="78" t="s">
+      <c r="I9" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="78" t="s">
+      <c r="J9" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="78" t="s">
+      <c r="K9" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="78" t="s">
+      <c r="L9" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="78" t="s">
+      <c r="M9" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="N9" s="78" t="s">
+      <c r="N9" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="78" t="s">
+      <c r="O9" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="P9" s="78" t="s">
+      <c r="P9" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="59"/>
+      <c r="Q9" s="85"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="85"/>
+      <c r="T9" s="56"/>
       <c r="U9" s="15"/>
-      <c r="V9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="W9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="X9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AK9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AL9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AM9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AN9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AO9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AP9" s="69"/>
-      <c r="AQ9" s="69"/>
-      <c r="AR9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AS9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AU9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AW9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AX9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AY9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AZ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BA9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BB9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BC9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BD9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BE9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BF9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BG9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BI9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BJ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BK9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BL9" s="69"/>
-      <c r="BM9" s="69"/>
-      <c r="BN9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BO9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BP9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BQ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BR9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BS9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BT9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BU9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BV9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BW9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BX9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BY9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BZ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CA9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CB9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CC9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CD9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CE9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CF9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CG9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CH9" s="69"/>
-      <c r="CI9" s="69"/>
-      <c r="CJ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CK9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CL9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CM9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CN9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CO9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CP9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CQ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CR9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CS9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CT9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CU9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CV9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CW9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CX9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CY9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="CZ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DA9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DB9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DC9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DD9" s="69"/>
-      <c r="DE9" s="69"/>
-      <c r="DF9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DG9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DH9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DI9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DJ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DK9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DL9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DM9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DN9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DO9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DP9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DQ9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DR9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DS9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DT9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DU9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DV9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DW9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DX9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DY9" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="DZ9" s="69"/>
-      <c r="EA9" s="69"/>
-      <c r="EB9" s="69"/>
-      <c r="EC9" s="69"/>
-      <c r="ED9" s="51"/>
-      <c r="EE9" s="94"/>
-      <c r="EF9" s="88"/>
-      <c r="EG9" s="89"/>
+      <c r="V9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="W9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="X9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AN9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AO9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP9" s="71"/>
+      <c r="AQ9" s="71"/>
+      <c r="AR9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AX9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AY9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="AZ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BA9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BB9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BC9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BD9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BE9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BF9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BG9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BH9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BI9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BJ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BK9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BL9" s="71"/>
+      <c r="BM9" s="71"/>
+      <c r="BN9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BO9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BP9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BQ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BR9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BS9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BT9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BU9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BV9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BW9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BX9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BY9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="BZ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CA9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CB9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CC9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CD9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CE9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CF9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CG9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CH9" s="71"/>
+      <c r="CI9" s="71"/>
+      <c r="CJ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CK9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CL9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CM9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CN9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CO9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CP9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CQ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CR9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CS9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CT9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CU9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CV9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CW9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CX9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CY9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="CZ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DA9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DB9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DC9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DD9" s="71"/>
+      <c r="DE9" s="71"/>
+      <c r="DF9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DG9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DH9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DI9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DJ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DK9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DL9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DM9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DN9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DO9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DP9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DQ9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DR9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DS9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DT9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DU9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DV9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DW9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DX9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DY9" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="DZ9" s="71"/>
+      <c r="EA9" s="71"/>
+      <c r="EB9" s="71"/>
+      <c r="EC9" s="71"/>
+      <c r="ED9" s="49"/>
+      <c r="EE9" s="96"/>
+      <c r="EF9" s="90"/>
+      <c r="EG9" s="91"/>
     </row>
-    <row r="10" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="79"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79"/>
-      <c r="Q10" s="79"/>
-      <c r="R10" s="79"/>
-      <c r="S10" s="79"/>
-      <c r="T10" s="58"/>
+    <row r="10" spans="1:138" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="81"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
+      <c r="O10" s="81"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="55"/>
       <c r="U10" s="15"/>
       <c r="V10" s="16" t="s">
         <v>49</v>
@@ -3005,8 +3011,8 @@
       <c r="AO10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="AP10" s="70"/>
-      <c r="AQ10" s="70"/>
+      <c r="AP10" s="72"/>
+      <c r="AQ10" s="72"/>
       <c r="AR10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3067,8 +3073,8 @@
       <c r="BK10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="BL10" s="70"/>
-      <c r="BM10" s="70"/>
+      <c r="BL10" s="72"/>
+      <c r="BM10" s="72"/>
       <c r="BN10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3129,8 +3135,8 @@
       <c r="CG10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="CH10" s="70"/>
-      <c r="CI10" s="70"/>
+      <c r="CH10" s="72"/>
+      <c r="CI10" s="72"/>
       <c r="CJ10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3191,8 +3197,8 @@
       <c r="DC10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="DD10" s="70"/>
-      <c r="DE10" s="70"/>
+      <c r="DD10" s="72"/>
+      <c r="DE10" s="72"/>
       <c r="DF10" s="16" t="s">
         <v>49</v>
       </c>
@@ -3253,16 +3259,16 @@
       <c r="DY10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="DZ10" s="70"/>
-      <c r="EA10" s="70"/>
-      <c r="EB10" s="70"/>
-      <c r="EC10" s="70"/>
-      <c r="ED10" s="50"/>
-      <c r="EE10" s="95"/>
-      <c r="EF10" s="90"/>
-      <c r="EG10" s="91"/>
+      <c r="DZ10" s="72"/>
+      <c r="EA10" s="72"/>
+      <c r="EB10" s="72"/>
+      <c r="EC10" s="72"/>
+      <c r="ED10" s="48"/>
+      <c r="EE10" s="97"/>
+      <c r="EF10" s="92"/>
+      <c r="EG10" s="93"/>
     </row>
-    <row r="11" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:138" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>2</v>
       </c>
@@ -3387,7 +3393,7 @@
       <c r="AO11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="AP11" s="31">
+      <c r="AP11" s="30">
         <f>SUMIF(V11:AO11,1,V$9:AO$9)
 +SUMIF(V11:AO11,2,V$9:AO$9)*0.5
 +SUMIF(V11:AO11,3,V$9:AO$9)</f>
@@ -3458,7 +3464,7 @@
       <c r="BK11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="BL11" s="31">
+      <c r="BL11" s="30">
         <f>SUMIF(AR11:BK11,1,AR$9:BK$9)
 +SUMIF(AR11:BK11,2,AR$9:BK$9)*0.5
 +SUMIF(AR11:BK11,3,AR$9:BK$9)</f>
@@ -3529,7 +3535,7 @@
       <c r="CG11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="CH11" s="31">
+      <c r="CH11" s="30">
         <f>SUMIF(BN11:CG11,1,BN$9:CG$9)
 +SUMIF(BN11:CG11,2,BN$9:CG$9)*0.5
 +SUMIF(BN11:CG11,3,BN$9:CG$9)</f>
@@ -3600,7 +3606,7 @@
       <c r="DC11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="DD11" s="31">
+      <c r="DD11" s="30">
         <f>SUMIF(CJ11:DC11,1,CJ$9:DC$9)
 +SUMIF(CJ11:DC11,2,CJ$9:DC$9)*0.5
 +SUMIF(CJ11:DC11,3,CJ$9:DC$9)</f>
@@ -3671,7 +3677,7 @@
       <c r="DY11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="DZ11" s="31">
+      <c r="DZ11" s="30">
         <f>SUMIF(DF11:DY11,1,DF$9:DY$9)
 +SUMIF(DF11:DY11,2,DF$9:DY$9)*0.5
 +SUMIF(DF11:DY11,3,DF$9:DY$9)</f>
@@ -3682,7 +3688,7 @@
 +SUMIF(DF11:DY11,2,DF$10:DY$10)*0.5</f>
         <v>0</v>
       </c>
-      <c r="EB11" s="31">
+      <c r="EB11" s="30">
         <f>SUM(DZ11,AP11,BL11,CH11,DD11)</f>
         <v>0</v>
       </c>
@@ -3693,38 +3699,38 @@
       <c r="ED11" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="EE11" s="48" t="s">
+      <c r="EE11" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="EF11" s="96" t="s">
+      <c r="EF11" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="EG11" s="97"/>
-      <c r="EH11" s="35" t="s">
+      <c r="EG11" s="99"/>
+      <c r="EH11" s="34" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:138" x14ac:dyDescent="0.2">
-      <c r="A12" s="61" t="s">
+    <row r="12" spans="1:138" x14ac:dyDescent="0.3">
+      <c r="A12" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
-      <c r="P12" s="62"/>
-      <c r="Q12" s="62"/>
-      <c r="R12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="65"/>
       <c r="S12" s="13">
         <f>COUNTIF(statusKategorie,$B$33)</f>
         <v>0</v>
@@ -3811,7 +3817,7 @@
         <f>COUNTIFS(angemeldet20,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="AP12" s="32">
+      <c r="AP12" s="31">
         <f>SUMIFS(summeStundenMo,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
@@ -3899,7 +3905,7 @@
         <f>COUNTIFS(angemeldet40,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="BL12" s="32">
+      <c r="BL12" s="31">
         <f>SUMIFS(summeStundenDi,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
@@ -3987,7 +3993,7 @@
         <f>COUNTIFS(angemeldet60,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="CH12" s="32">
+      <c r="CH12" s="31">
         <f>SUMIFS(summeStundenMi,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
@@ -4075,7 +4081,7 @@
         <f>COUNTIFS(angemeldet80,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DD12" s="32">
+      <c r="DD12" s="31">
         <f>SUMIFS(summeStundenDo,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
@@ -4163,7 +4169,7 @@
         <f>COUNTIFS(angemeldet100,"&gt;0",statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="DZ12" s="32">
+      <c r="DZ12" s="31">
         <f>SUMIFS(summeStundenFr,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
@@ -4171,40 +4177,40 @@
         <f>SUMIFS(summeVerpflegungFr,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="EB12" s="32">
+      <c r="EB12" s="31">
         <f>SUMIFS(summeStundenWoche,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="EC12" s="41">
+      <c r="EC12" s="39">
         <f>SUMIFS(summeVerpflegungWoche,statusKategorie,$B$33)</f>
         <v>0</v>
       </c>
-      <c r="ED12" s="54"/>
-      <c r="EE12" s="45"/>
-      <c r="EF12" s="39"/>
-      <c r="EG12" s="40"/>
+      <c r="ED12" s="52"/>
+      <c r="EE12" s="43"/>
+      <c r="EF12" s="37"/>
+      <c r="EG12" s="38"/>
     </row>
-    <row r="13" spans="1:138" x14ac:dyDescent="0.2">
-      <c r="A13" s="61" t="s">
+    <row r="13" spans="1:138" x14ac:dyDescent="0.3">
+      <c r="A13" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="65"/>
       <c r="S13" s="13">
         <f>COUNTIF(statusKategorie,$B$32)</f>
         <v>0</v>
@@ -4291,7 +4297,7 @@
         <f>COUNTIFS(angemeldet20,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="AP13" s="32">
+      <c r="AP13" s="31">
         <f>SUMIFS(summeStundenMo,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
@@ -4379,7 +4385,7 @@
         <f>COUNTIFS(angemeldet40,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="BL13" s="32">
+      <c r="BL13" s="31">
         <f>SUMIFS(summeStundenDi,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
@@ -4467,7 +4473,7 @@
         <f>COUNTIFS(angemeldet60,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="CH13" s="32">
+      <c r="CH13" s="31">
         <f>SUMIFS(summeStundenMi,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
@@ -4555,7 +4561,7 @@
         <f>COUNTIFS(angemeldet80,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DD13" s="32">
+      <c r="DD13" s="31">
         <f>SUMIFS(summeStundenDo,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
@@ -4643,7 +4649,7 @@
         <f>COUNTIFS(angemeldet100,"&gt;0",statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="DZ13" s="32">
+      <c r="DZ13" s="31">
         <f>SUMIFS(summeStundenFr,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
@@ -4651,40 +4657,40 @@
         <f>SUMIFS(summeVerpflegungFr,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="EB13" s="32">
+      <c r="EB13" s="31">
         <f>SUMIFS(summeStundenWoche,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="EC13" s="42">
+      <c r="EC13" s="40">
         <f>SUMIFS(summeVerpflegungWoche,statusKategorie,$B$32)</f>
         <v>0</v>
       </c>
-      <c r="ED13" s="55"/>
-      <c r="EE13" s="46"/>
+      <c r="ED13" s="53"/>
+      <c r="EE13" s="44"/>
       <c r="EF13" s="28"/>
-      <c r="EG13" s="44"/>
+      <c r="EG13" s="42"/>
     </row>
-    <row r="14" spans="1:138" x14ac:dyDescent="0.2">
-      <c r="A14" s="61" t="s">
+    <row r="14" spans="1:138" x14ac:dyDescent="0.3">
+      <c r="A14" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="63"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="65"/>
       <c r="S14" s="13">
         <f>COUNTIF(statusKategorie,$B$31)</f>
         <v>0</v>
@@ -4771,7 +4777,7 @@
         <f>COUNTIFS(angemeldet20,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="AP14" s="33">
+      <c r="AP14" s="32">
         <f>SUMIFS(summeStundenMo,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
@@ -4859,7 +4865,7 @@
         <f>COUNTIFS(angemeldet40,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="BL14" s="33">
+      <c r="BL14" s="32">
         <f>SUMIFS(summeStundenDi,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
@@ -4947,7 +4953,7 @@
         <f>COUNTIFS(angemeldet60,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="CH14" s="33">
+      <c r="CH14" s="32">
         <f>SUMIFS(summeStundenMi,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
@@ -5035,7 +5041,7 @@
         <f>COUNTIFS(angemeldet80,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DD14" s="33">
+      <c r="DD14" s="32">
         <f>SUMIFS(summeStundenDo,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
@@ -5123,7 +5129,7 @@
         <f>COUNTIFS(angemeldet100,"&gt;0",statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="DZ14" s="33">
+      <c r="DZ14" s="32">
         <f>SUMIFS(summeStundenFr,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
@@ -5131,20 +5137,20 @@
         <f>SUMIFS(summeVerpflegungFr,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="EB14" s="33">
+      <c r="EB14" s="32">
         <f>SUMIFS(summeStundenWoche,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="EC14" s="43">
+      <c r="EC14" s="41">
         <f>SUMIFS(summeVerpflegungWoche,statusKategorie,$B$31)</f>
         <v>0</v>
       </c>
-      <c r="ED14" s="42"/>
-      <c r="EE14" s="47"/>
-      <c r="EF14" s="38"/>
-      <c r="EG14" s="36"/>
+      <c r="ED14" s="40"/>
+      <c r="EE14" s="45"/>
+      <c r="EF14" s="36"/>
+      <c r="EG14" s="35"/>
     </row>
-    <row r="15" spans="1:138" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:138" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>2</v>
       </c>
@@ -5202,7 +5208,7 @@
       <c r="S15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="T15" s="60" t="s">
+      <c r="T15" s="57" t="s">
         <v>91</v>
       </c>
       <c r="U15" s="6" t="e">
@@ -5519,43 +5525,43 @@
       </c>
       <c r="DZ15" s="26"/>
       <c r="EA15" s="27"/>
-      <c r="EB15" s="30"/>
-      <c r="EC15" s="37"/>
-      <c r="ED15" s="56" t="s">
+      <c r="EB15" s="59"/>
+      <c r="EC15" s="60"/>
+      <c r="ED15" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="EE15" s="48" t="s">
+      <c r="EE15" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="EF15" s="84" t="s">
+      <c r="EF15" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="EG15" s="85"/>
+      <c r="EG15" s="87"/>
       <c r="EH15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:138" x14ac:dyDescent="0.2">
-      <c r="A16" s="71" t="s">
+    <row r="16" spans="1:138" x14ac:dyDescent="0.3">
+      <c r="A16" s="73" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="73"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="73"/>
+      <c r="R16" s="73"/>
       <c r="S16" s="13">
         <f>COUNTIF(freigegebenKategorie,$B$34)</f>
         <v>0</v>
@@ -5972,14 +5978,14 @@
       </c>
       <c r="DZ16" s="28"/>
       <c r="EA16" s="28"/>
-      <c r="EB16" s="25"/>
-      <c r="EC16" s="38"/>
-      <c r="ED16" s="38"/>
+      <c r="EB16" s="61"/>
+      <c r="EC16" s="62"/>
+      <c r="ED16" s="36"/>
       <c r="EE16" s="25"/>
-      <c r="EF16" s="38"/>
-      <c r="EG16" s="36"/>
+      <c r="EF16" s="36"/>
+      <c r="EG16" s="35"/>
     </row>
-    <row r="17" spans="1:133" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:133" x14ac:dyDescent="0.3">
       <c r="AP17" s="29"/>
       <c r="AQ17" s="29"/>
       <c r="BL17" s="29"/>
@@ -5993,7 +5999,7 @@
       <c r="EB17" s="29"/>
       <c r="EC17" s="29"/>
     </row>
-    <row r="18" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -6001,7 +6007,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -6010,7 +6016,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="20" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -6019,7 +6025,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="21" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -6028,7 +6034,7 @@
         <v>ABGELEHNT</v>
       </c>
     </row>
-    <row r="22" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -6037,7 +6043,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="23" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -6046,7 +6052,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="24" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -6055,7 +6061,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="25" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:133" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -6064,7 +6070,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="26" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:133" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -6073,7 +6079,7 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="27" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:133" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -6082,7 +6088,7 @@
         <v>ABGELEHNT</v>
       </c>
     </row>
-    <row r="28" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:133" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -6091,7 +6097,7 @@
         <v>OFFEN</v>
       </c>
     </row>
-    <row r="29" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:133" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -6100,8 +6106,8 @@
         <v>BESTÄTIGT</v>
       </c>
     </row>
-    <row r="30" spans="1:133" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:133" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:133" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -6109,7 +6115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:133" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:133" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -6117,7 +6123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -6125,7 +6131,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -6133,84 +6139,84 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A36" s="61" t="s">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="62"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="22">
         <v>1</v>
       </c>
-      <c r="B37" s="67" t="s">
+      <c r="B37" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="67"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="22">
         <v>2</v>
       </c>
-      <c r="B38" s="67" t="s">
+      <c r="B38" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="67"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="22">
         <v>3</v>
       </c>
-      <c r="B39" s="67" t="s">
+      <c r="B39" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="67"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="54">
     <mergeCell ref="D7:F8"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="EF15:EG15"/>
@@ -6227,13 +6233,13 @@
     <mergeCell ref="DF7:EA7"/>
     <mergeCell ref="CJ7:DE7"/>
     <mergeCell ref="G7:K8"/>
-    <mergeCell ref="L7:P8"/>
     <mergeCell ref="S7:S10"/>
     <mergeCell ref="Q7:Q10"/>
     <mergeCell ref="R7:R10"/>
     <mergeCell ref="N9:N10"/>
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="P9:P10"/>
+    <mergeCell ref="A7:C8"/>
     <mergeCell ref="A13:R13"/>
     <mergeCell ref="A14:R14"/>
     <mergeCell ref="A9:A10"/>
@@ -6248,6 +6254,8 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L7:P8"/>
+    <mergeCell ref="EB15:EC16"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="AR7:BM7"/>
     <mergeCell ref="BN7:CI7"/>
@@ -6263,7 +6271,6 @@
     <mergeCell ref="V7:AQ7"/>
     <mergeCell ref="A16:R16"/>
     <mergeCell ref="A12:R12"/>
-    <mergeCell ref="A7:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" r:id="rId1"/>
